--- a/artfynd/A 47880-2025 artfynd.xlsx
+++ b/artfynd/A 47880-2025 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129627353</v>
+        <v>129629020</v>
       </c>
       <c r="B4" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +890,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>425377</v>
+        <v>425596</v>
       </c>
       <c r="R4" t="n">
-        <v>7049766</v>
+        <v>7049885</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +965,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>250 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,28 +974,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129628994</v>
+        <v>129627353</v>
       </c>
       <c r="B5" t="n">
-        <v>79515</v>
+        <v>80150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1797</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>425704</v>
+        <v>425377</v>
       </c>
       <c r="R5" t="n">
-        <v>7050007</v>
+        <v>7049766</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1068,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal död gran i gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,22 +1083,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129629020</v>
+        <v>129628994</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79515</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,45 +1106,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1797</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>425596</v>
+        <v>425704</v>
       </c>
       <c r="R6" t="n">
-        <v>7049885</v>
+        <v>7050007</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,7 +1170,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>250 bålar på gammal levande gran i gammal granskog</t>
+          <t>På bark vid basen av gammal död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,7 +1179,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1197,45 +1197,56 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129627370</v>
+        <v>129627355</v>
       </c>
       <c r="B7" t="n">
-        <v>78057</v>
+        <v>79203</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>1249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>425453</v>
+        <v>425715</v>
       </c>
       <c r="R7" t="n">
-        <v>7049864</v>
+        <v>7050107</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,17 +1281,13 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>på gammal gran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1299,32 +1306,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129627341</v>
+        <v>129628998</v>
       </c>
       <c r="B8" t="n">
-        <v>92271</v>
+        <v>79515</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>1797</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1334,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>425495</v>
+        <v>425339</v>
       </c>
       <c r="R8" t="n">
-        <v>7049796</v>
+        <v>7049780</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,6 +1379,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På grov gren på gammal levande gran i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1384,42 +1396,46 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129627377</v>
+        <v>129627341</v>
       </c>
       <c r="B9" t="n">
-        <v>91573</v>
+        <v>92271</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1427,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>425701</v>
+        <v>425495</v>
       </c>
       <c r="R9" t="n">
-        <v>7050250</v>
+        <v>7049796</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,11 +1479,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På granhögstubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,56 +1505,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129627355</v>
+        <v>129627370</v>
       </c>
       <c r="B10" t="n">
-        <v>79203</v>
+        <v>78057</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1249</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>425715</v>
+        <v>425453</v>
       </c>
       <c r="R10" t="n">
-        <v>7050107</v>
+        <v>7049864</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1578,13 +1578,17 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>på gammal gran</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1603,10 +1607,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129628998</v>
+        <v>129627377</v>
       </c>
       <c r="B11" t="n">
-        <v>79515</v>
+        <v>91573</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,23 +1618,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1797</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>425339</v>
+        <v>425701</v>
       </c>
       <c r="R11" t="n">
-        <v>7049780</v>
+        <v>7050250</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På grov gren på gammal levande gran i gammal granskog</t>
+          <t>På granhögstubbe</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,12 +1693,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2113,45 +2113,56 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129628957</v>
+        <v>129627356</v>
       </c>
       <c r="B16" t="n">
-        <v>91553</v>
+        <v>79203</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1249</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>425661</v>
+        <v>425723</v>
       </c>
       <c r="R16" t="n">
-        <v>7049950</v>
+        <v>7050083</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,85 +2197,70 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129627356</v>
+        <v>129628977</v>
       </c>
       <c r="B17" t="n">
-        <v>79203</v>
+        <v>75033</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1249</v>
+        <v>6428</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>425723</v>
+        <v>425488</v>
       </c>
       <c r="R17" t="n">
-        <v>7050083</v>
+        <v>7049835</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2299,57 +2295,61 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På bark vid basen av gammal levande gran i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129628977</v>
+        <v>129628957</v>
       </c>
       <c r="B18" t="n">
-        <v>75033</v>
+        <v>91553</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6428</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>425488</v>
+        <v>425661</v>
       </c>
       <c r="R18" t="n">
-        <v>7049835</v>
+        <v>7049950</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,56 +2528,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129627361</v>
+        <v>129628997</v>
       </c>
       <c r="B20" t="n">
-        <v>79203</v>
+        <v>79515</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1249</v>
+        <v>1797</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>425570</v>
+        <v>425393</v>
       </c>
       <c r="R20" t="n">
-        <v>7049933</v>
+        <v>7049812</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2614,7 +2603,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2623,29 +2612,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129628997</v>
+        <v>129627375</v>
       </c>
       <c r="B21" t="n">
-        <v>79515</v>
+        <v>91549</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2653,21 +2641,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1797</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2677,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>425393</v>
+        <v>425697</v>
       </c>
       <c r="R21" t="n">
-        <v>7049812</v>
+        <v>7050004</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2717,7 +2705,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2732,57 +2720,68 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129629009</v>
+        <v>129627361</v>
       </c>
       <c r="B22" t="n">
-        <v>91549</v>
+        <v>79203</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>1249</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>425707</v>
+        <v>425570</v>
       </c>
       <c r="R22" t="n">
-        <v>7050031</v>
+        <v>7049933</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2819,7 +2818,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2828,25 +2827,26 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129627375</v>
+        <v>129629009</v>
       </c>
       <c r="B23" t="n">
         <v>91549</v>
@@ -2881,10 +2881,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>425697</v>
+        <v>425707</v>
       </c>
       <c r="R23" t="n">
-        <v>7050004</v>
+        <v>7050031</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2936,44 +2936,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129628984</v>
+        <v>129628992</v>
       </c>
       <c r="B24" t="n">
-        <v>80177</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>425327</v>
+        <v>425721</v>
       </c>
       <c r="R24" t="n">
-        <v>7049709</v>
+        <v>7050017</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>20 bålar på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3050,32 +3050,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129628992</v>
+        <v>129628984</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>80177</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>425721</v>
+        <v>425327</v>
       </c>
       <c r="R25" t="n">
-        <v>7050017</v>
+        <v>7049709</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>20 bålar på gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3254,32 +3254,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129628988</v>
+        <v>129627342</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>92271</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>425724</v>
+        <v>425473</v>
       </c>
       <c r="R27" t="n">
-        <v>7050035</v>
+        <v>7049830</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3338,50 +3338,51 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129629025</v>
+        <v>129628988</v>
       </c>
       <c r="B28" t="n">
-        <v>82995</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3391,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>425717</v>
+        <v>425724</v>
       </c>
       <c r="R28" t="n">
-        <v>7050119</v>
+        <v>7050035</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3431,7 +3432,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På ved i hålighet vid basen av gammal död gran</t>
+          <t>på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3458,32 +3459,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129629010</v>
+        <v>129629025</v>
       </c>
       <c r="B29" t="n">
-        <v>83010</v>
+        <v>82995</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6486</v>
+        <v>6439</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3493,10 +3494,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>425698</v>
+        <v>425717</v>
       </c>
       <c r="R29" t="n">
-        <v>7049997</v>
+        <v>7050119</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3533,7 +3534,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande grov gran i gammal fuktig granskog</t>
+          <t>På ved i hålighet vid basen av gammal död gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3560,32 +3561,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129628999</v>
+        <v>129629028</v>
       </c>
       <c r="B30" t="n">
-        <v>97644</v>
+        <v>83007</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221063</v>
+        <v>310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3595,10 +3596,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>425716</v>
+        <v>425332</v>
       </c>
       <c r="R30" t="n">
-        <v>7050162</v>
+        <v>7049768</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3635,7 +3636,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På marken i rikare källflöde i gammal granskog</t>
+          <t>På bark på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3662,42 +3663,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129627342</v>
+        <v>129627363</v>
       </c>
       <c r="B31" t="n">
-        <v>92271</v>
+        <v>79203</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>1249</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>425473</v>
+        <v>425428</v>
       </c>
       <c r="R31" t="n">
         <v>7049830</v>
@@ -3737,7 +3749,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>på gran i gammal granskog</t>
+          <t>vid västsluttning och vattenkälla</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3765,10 +3777,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129627363</v>
+        <v>129629010</v>
       </c>
       <c r="B32" t="n">
-        <v>79203</v>
+        <v>83010</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3776,45 +3788,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1249</v>
+        <v>6486</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>425428</v>
+        <v>425698</v>
       </c>
       <c r="R32" t="n">
-        <v>7049830</v>
+        <v>7049997</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3851,7 +3852,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>vid västsluttning och vattenkälla</t>
+          <t>På bark i hålighet vid basen av gammal levande grov gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3860,51 +3861,50 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129629028</v>
+        <v>129628999</v>
       </c>
       <c r="B33" t="n">
-        <v>83007</v>
+        <v>97644</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>310</v>
+        <v>221063</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>425332</v>
+        <v>425716</v>
       </c>
       <c r="R33" t="n">
-        <v>7049768</v>
+        <v>7050162</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På bark på björkhögstubbe i gammal granskog</t>
+          <t>På marken i rikare källflöde i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3981,56 +3981,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129627347</v>
+        <v>129628980</v>
       </c>
       <c r="B34" t="n">
-        <v>92508</v>
+        <v>78057</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4769</v>
+        <v>228579</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>425707</v>
+        <v>425716</v>
       </c>
       <c r="R34" t="n">
-        <v>7050150</v>
+        <v>7050121</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4065,25 +4054,29 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>på gammal levande gran</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4187,10 +4180,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627336</v>
+        <v>129628971</v>
       </c>
       <c r="B36" t="n">
-        <v>83012</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4198,21 +4191,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4222,10 +4215,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>425710</v>
+        <v>425704</v>
       </c>
       <c r="R36" t="n">
-        <v>7050275</v>
+        <v>7050246</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4262,7 +4255,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4277,44 +4270,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129628956</v>
+        <v>129628982</v>
       </c>
       <c r="B37" t="n">
-        <v>83012</v>
+        <v>79203</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4324,10 +4317,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>425268</v>
+        <v>425718</v>
       </c>
       <c r="R37" t="n">
-        <v>7049748</v>
+        <v>7050119</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4364,7 +4357,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Två mycket stora bålar på grova grenar på gammal levande gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4373,7 +4366,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4392,45 +4384,56 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129628971</v>
+        <v>129627347</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>92508</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>425704</v>
+        <v>425707</v>
       </c>
       <c r="R38" t="n">
-        <v>7050246</v>
+        <v>7050150</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4465,61 +4468,57 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>på gammal gran i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129628965</v>
+        <v>129627336</v>
       </c>
       <c r="B39" t="n">
-        <v>83010</v>
+        <v>83012</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6486</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4529,10 +4528,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>425510</v>
+        <v>425710</v>
       </c>
       <c r="R39" t="n">
-        <v>7049849</v>
+        <v>7050275</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4569,7 +4568,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande grov gran i gammal fuktig granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4584,19 +4583,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129628979</v>
+        <v>129628956</v>
       </c>
       <c r="B40" t="n">
         <v>83012</v>
@@ -4631,10 +4630,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>425716</v>
+        <v>425268</v>
       </c>
       <c r="R40" t="n">
-        <v>7050121</v>
+        <v>7049748</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4671,7 +4670,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>på gammal levande gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4680,6 +4679,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4698,10 +4698,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129628982</v>
+        <v>129628965</v>
       </c>
       <c r="B41" t="n">
-        <v>79203</v>
+        <v>83010</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4709,21 +4709,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1249</v>
+        <v>6486</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>425718</v>
+        <v>425510</v>
       </c>
       <c r="R41" t="n">
-        <v>7050119</v>
+        <v>7049849</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Två mycket stora bålar på grova grenar på gammal levande gran</t>
+          <t>På bark i hålighet vid basen av gammal levande grov gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4800,10 +4800,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129628980</v>
+        <v>129628979</v>
       </c>
       <c r="B42" t="n">
-        <v>78057</v>
+        <v>83012</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4811,21 +4811,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4902,32 +4902,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129627338</v>
+        <v>129627378</v>
       </c>
       <c r="B43" t="n">
-        <v>92271</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4937,10 +4937,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>425585</v>
+        <v>425710</v>
       </c>
       <c r="R43" t="n">
-        <v>7050170</v>
+        <v>7050152</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>150 bålar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5004,10 +5004,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129629007</v>
+        <v>129629014</v>
       </c>
       <c r="B44" t="n">
-        <v>79125</v>
+        <v>91549</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5015,21 +5015,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>283</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>425720</v>
+        <v>425660</v>
       </c>
       <c r="R44" t="n">
-        <v>7050011</v>
+        <v>7049963</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal levande senvuxen undertryckt gran i gammal fuktig granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5317,32 +5317,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129629035</v>
+        <v>129629007</v>
       </c>
       <c r="B47" t="n">
-        <v>75154</v>
+        <v>79125</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1776</v>
+        <v>283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5352,10 +5352,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>425578</v>
+        <v>425720</v>
       </c>
       <c r="R47" t="n">
-        <v>7049878</v>
+        <v>7050011</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På tunna döda kvistar på ca 200 år gammal gran i gammal granskog</t>
+          <t>På tunna kvistar på gammal levande senvuxen undertryckt gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5419,32 +5419,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129629011</v>
+        <v>129629035</v>
       </c>
       <c r="B48" t="n">
-        <v>79515</v>
+        <v>75154</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1797</v>
+        <v>1776</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5454,10 +5454,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>425698</v>
+        <v>425578</v>
       </c>
       <c r="R48" t="n">
-        <v>7049997</v>
+        <v>7049878</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På tunna döda kvistar på ca 200 år gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5521,10 +5521,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129629014</v>
+        <v>129629011</v>
       </c>
       <c r="B49" t="n">
-        <v>91549</v>
+        <v>79515</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5532,21 +5532,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1108</v>
+        <v>1797</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5556,10 +5556,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>425660</v>
+        <v>425698</v>
       </c>
       <c r="R49" t="n">
-        <v>7049963</v>
+        <v>7049997</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5623,32 +5623,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129627378</v>
+        <v>129627338</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>92271</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5658,10 +5658,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>425710</v>
+        <v>425585</v>
       </c>
       <c r="R50" t="n">
-        <v>7050152</v>
+        <v>7050170</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>150 bålar</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5932,32 +5932,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129628983</v>
+        <v>129628948</v>
       </c>
       <c r="B53" t="n">
-        <v>79203</v>
+        <v>97644</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1249</v>
+        <v>221063</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5967,10 +5967,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>425721</v>
+        <v>425719</v>
       </c>
       <c r="R53" t="n">
-        <v>7050017</v>
+        <v>7050208</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På gren på gammal död gran i gammal granskog</t>
+          <t>På marken i källflöde i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6034,32 +6034,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129628948</v>
+        <v>129628983</v>
       </c>
       <c r="B54" t="n">
-        <v>97644</v>
+        <v>79203</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221063</v>
+        <v>1249</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>425719</v>
+        <v>425721</v>
       </c>
       <c r="R54" t="n">
-        <v>7050208</v>
+        <v>7050017</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På marken i källflöde i gammal granskog</t>
+          <t>På gren på gammal död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6442,56 +6442,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129627360</v>
+        <v>129628974</v>
       </c>
       <c r="B58" t="n">
-        <v>79203</v>
+        <v>83017</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1249</v>
+        <v>1467</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>425573</v>
+        <v>425457</v>
       </c>
       <c r="R58" t="n">
-        <v>7049926</v>
+        <v>7049826</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6528,7 +6517,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>långt ner på gammal gran, fuktigt</t>
+          <t>På bark vid basen av gammal levande gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6537,29 +6526,28 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129628974</v>
+        <v>129629026</v>
       </c>
       <c r="B59" t="n">
-        <v>83017</v>
+        <v>83004</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6567,21 +6555,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1467</v>
+        <v>308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6591,10 +6579,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>425457</v>
+        <v>425717</v>
       </c>
       <c r="R59" t="n">
-        <v>7049826</v>
+        <v>7050119</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6631,7 +6619,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran</t>
+          <t>På ved i hålighet vid basen av gammal död gran, även gulnål</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6658,10 +6646,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129629026</v>
+        <v>129629008</v>
       </c>
       <c r="B60" t="n">
-        <v>83004</v>
+        <v>79125</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6669,21 +6657,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6693,10 +6681,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>425717</v>
+        <v>425267</v>
       </c>
       <c r="R60" t="n">
-        <v>7050119</v>
+        <v>7049748</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6733,7 +6721,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På ved i hålighet vid basen av gammal död gran, även gulnål</t>
+          <t>På tunna kvistar på levande klen gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6760,45 +6748,56 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129629008</v>
+        <v>129627360</v>
       </c>
       <c r="B61" t="n">
-        <v>79125</v>
+        <v>79203</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>425267</v>
+        <v>425573</v>
       </c>
       <c r="R61" t="n">
-        <v>7049748</v>
+        <v>7049926</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6835,7 +6834,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På tunna kvistar på levande klen gammal gran i gammal granskog</t>
+          <t>långt ner på gammal gran, fuktigt</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6844,18 +6843,19 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7168,10 +7168,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129629030</v>
+        <v>129627379</v>
       </c>
       <c r="B65" t="n">
-        <v>83004</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7179,21 +7179,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7203,10 +7203,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>425332</v>
+        <v>425501</v>
       </c>
       <c r="R65" t="n">
-        <v>7049768</v>
+        <v>7049848</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På ved på björkhögstubbe i gammal granskog, även gulnål och nordlig nållav på barken</t>
+          <t>100 bålar</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7258,12 +7258,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7571,10 +7571,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129628985</v>
+        <v>129629030</v>
       </c>
       <c r="B69" t="n">
-        <v>83012</v>
+        <v>83004</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7582,21 +7582,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>425529</v>
+        <v>425332</v>
       </c>
       <c r="R69" t="n">
-        <v>7049841</v>
+        <v>7049768</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7646,7 +7646,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal sälg i gammal granskog</t>
+          <t>På ved på björkhögstubbe i gammal granskog, även gulnål och nordlig nållav på barken</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7673,10 +7673,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129627379</v>
+        <v>129628985</v>
       </c>
       <c r="B70" t="n">
-        <v>79044</v>
+        <v>83012</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7684,21 +7684,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7708,10 +7708,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>425501</v>
+        <v>425529</v>
       </c>
       <c r="R70" t="n">
-        <v>7049848</v>
+        <v>7049841</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>100 bålar</t>
+          <t>På bark på stam av död gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7763,12 +7763,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7979,32 +7979,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129628959</v>
+        <v>129629003</v>
       </c>
       <c r="B73" t="n">
-        <v>92271</v>
+        <v>78057</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>425626</v>
+        <v>425395</v>
       </c>
       <c r="R73" t="n">
-        <v>7050243</v>
+        <v>7049812</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8081,56 +8081,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129627364</v>
+        <v>129628993</v>
       </c>
       <c r="B74" t="n">
-        <v>79203</v>
+        <v>79515</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1249</v>
+        <v>1797</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>425392</v>
+        <v>425721</v>
       </c>
       <c r="R74" t="n">
-        <v>7049820</v>
+        <v>7050017</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8167,7 +8156,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8176,51 +8165,50 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129628993</v>
+        <v>129628959</v>
       </c>
       <c r="B75" t="n">
-        <v>79515</v>
+        <v>92271</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1797</v>
+        <v>3298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8230,10 +8218,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>425721</v>
+        <v>425626</v>
       </c>
       <c r="R75" t="n">
-        <v>7050017</v>
+        <v>7050243</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8270,7 +8258,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8399,45 +8387,56 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129629003</v>
+        <v>129627364</v>
       </c>
       <c r="B77" t="n">
-        <v>78057</v>
+        <v>79203</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228579</v>
+        <v>1249</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>425395</v>
+        <v>425392</v>
       </c>
       <c r="R77" t="n">
-        <v>7049812</v>
+        <v>7049820</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8474,7 +8473,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8483,50 +8482,51 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129627339</v>
+        <v>129627380</v>
       </c>
       <c r="B78" t="n">
-        <v>92271</v>
+        <v>82878</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8536,10 +8536,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>425702</v>
+        <v>425713</v>
       </c>
       <c r="R78" t="n">
-        <v>7050007</v>
+        <v>7050121</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8572,6 +8572,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8598,7 +8603,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129627357</v>
+        <v>129627358</v>
       </c>
       <c r="B79" t="n">
         <v>79203</v>
@@ -8644,10 +8649,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>425721</v>
+        <v>425715</v>
       </c>
       <c r="R79" t="n">
-        <v>7050057</v>
+        <v>7050016</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8712,10 +8717,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129627380</v>
+        <v>129629021</v>
       </c>
       <c r="B80" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8723,21 +8728,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8747,10 +8752,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>425713</v>
+        <v>425518</v>
       </c>
       <c r="R80" t="n">
-        <v>7050121</v>
+        <v>7049851</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8787,7 +8792,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8802,44 +8807,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129629015</v>
+        <v>129627339</v>
       </c>
       <c r="B81" t="n">
-        <v>91549</v>
+        <v>92271</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8849,10 +8854,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>425619</v>
+        <v>425702</v>
       </c>
       <c r="R81" t="n">
-        <v>7050217</v>
+        <v>7050007</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8887,11 +8892,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På död gammal gran i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -8904,68 +8904,57 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129627358</v>
+        <v>129628976</v>
       </c>
       <c r="B82" t="n">
-        <v>79203</v>
+        <v>75033</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1249</v>
+        <v>6428</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>425715</v>
+        <v>425609</v>
       </c>
       <c r="R82" t="n">
-        <v>7050016</v>
+        <v>7050175</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9002,7 +8991,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>På grankvist I gammal granskog</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9011,51 +9000,50 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129627376</v>
+        <v>129627349</v>
       </c>
       <c r="B83" t="n">
-        <v>91549</v>
+        <v>80178</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9065,10 +9053,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>425618</v>
+        <v>425382</v>
       </c>
       <c r="R83" t="n">
-        <v>7049908</v>
+        <v>7049760</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9105,7 +9093,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>på gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9132,32 +9120,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129629021</v>
+        <v>129627366</v>
       </c>
       <c r="B84" t="n">
-        <v>79044</v>
+        <v>80177</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9167,10 +9155,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>425518</v>
+        <v>425552</v>
       </c>
       <c r="R84" t="n">
-        <v>7049851</v>
+        <v>7049855</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9205,11 +9193,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9222,44 +9205,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129628976</v>
+        <v>129627376</v>
       </c>
       <c r="B85" t="n">
-        <v>75033</v>
+        <v>91549</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6428</v>
+        <v>1108</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9269,10 +9252,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>425609</v>
+        <v>425618</v>
       </c>
       <c r="R85" t="n">
-        <v>7050175</v>
+        <v>7049908</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9309,7 +9292,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På grankvist I gammal granskog</t>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9324,44 +9307,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129627349</v>
+        <v>129629015</v>
       </c>
       <c r="B86" t="n">
-        <v>80178</v>
+        <v>91549</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9371,10 +9354,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>425382</v>
+        <v>425619</v>
       </c>
       <c r="R86" t="n">
-        <v>7049760</v>
+        <v>7050217</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9411,7 +9394,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9426,57 +9409,68 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129627366</v>
+        <v>129627357</v>
       </c>
       <c r="B87" t="n">
-        <v>80177</v>
+        <v>79203</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6461</v>
+        <v>1249</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>425552</v>
+        <v>425721</v>
       </c>
       <c r="R87" t="n">
-        <v>7049855</v>
+        <v>7050057</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9511,12 +9505,18 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>på gammal gran</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9637,10 +9637,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129627373</v>
+        <v>129627381</v>
       </c>
       <c r="B89" t="n">
-        <v>79125</v>
+        <v>82878</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9648,21 +9648,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>283</v>
+        <v>1312</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>425608</v>
+        <v>425617</v>
       </c>
       <c r="R89" t="n">
-        <v>7049894</v>
+        <v>7049903</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>på tunna kvistar</t>
+          <t>Tillsammans med gammelgranslav</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9739,10 +9739,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129629005</v>
+        <v>129628978</v>
       </c>
       <c r="B90" t="n">
-        <v>79125</v>
+        <v>79044</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9750,21 +9750,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9774,10 +9774,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>425718</v>
+        <v>425716</v>
       </c>
       <c r="R90" t="n">
-        <v>7050118</v>
+        <v>7050121</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På senvuxen undertryckt klen gran i gammal granskog</t>
+          <t>på gammal levande gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9841,10 +9841,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129627381</v>
+        <v>129629005</v>
       </c>
       <c r="B91" t="n">
-        <v>82878</v>
+        <v>79125</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9852,21 +9852,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1312</v>
+        <v>283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9876,10 +9876,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>425617</v>
+        <v>425718</v>
       </c>
       <c r="R91" t="n">
-        <v>7049903</v>
+        <v>7050118</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Tillsammans med gammelgranslav</t>
+          <t>På senvuxen undertryckt klen gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9931,12 +9931,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10147,10 +10147,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129628978</v>
+        <v>129627373</v>
       </c>
       <c r="B94" t="n">
-        <v>79044</v>
+        <v>79125</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10158,21 +10158,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10182,10 +10182,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>425716</v>
+        <v>425608</v>
       </c>
       <c r="R94" t="n">
-        <v>7050121</v>
+        <v>7049894</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10222,7 +10222,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>på gammal levande gran</t>
+          <t>på tunna kvistar</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10237,44 +10237,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129628952</v>
+        <v>129628963</v>
       </c>
       <c r="B95" t="n">
-        <v>78057</v>
+        <v>92508</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228579</v>
+        <v>4769</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10284,10 +10284,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>425660</v>
+        <v>425275</v>
       </c>
       <c r="R95" t="n">
-        <v>7050271</v>
+        <v>7049745</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10351,32 +10351,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129628963</v>
+        <v>129628952</v>
       </c>
       <c r="B96" t="n">
-        <v>92508</v>
+        <v>78057</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4769</v>
+        <v>228579</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10386,10 +10386,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>425275</v>
+        <v>425660</v>
       </c>
       <c r="R96" t="n">
-        <v>7049745</v>
+        <v>7050271</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10453,10 +10453,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129628953</v>
+        <v>129629033</v>
       </c>
       <c r="B97" t="n">
-        <v>83012</v>
+        <v>78057</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10464,21 +10464,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10488,10 +10488,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>425660</v>
+        <v>425685</v>
       </c>
       <c r="R97" t="n">
-        <v>7050271</v>
+        <v>7050259</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10528,7 +10528,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>på gammal levande gran i gammal granskog vid rikkärr vid sjö</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10657,10 +10657,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129627343</v>
+        <v>129628953</v>
       </c>
       <c r="B99" t="n">
-        <v>57727</v>
+        <v>83012</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10668,42 +10668,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>425384</v>
+        <v>425660</v>
       </c>
       <c r="R99" t="n">
-        <v>7049814</v>
+        <v>7050271</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10740,7 +10732,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>ringhack på gran</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10755,22 +10747,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129629033</v>
+        <v>129627343</v>
       </c>
       <c r="B100" t="n">
-        <v>78057</v>
+        <v>57727</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10778,34 +10770,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>425685</v>
+        <v>425384</v>
       </c>
       <c r="R100" t="n">
-        <v>7050259</v>
+        <v>7049814</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>på gammal levande gran i gammal granskog vid rikkärr vid sjö</t>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10857,44 +10857,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129628958</v>
+        <v>129627392</v>
       </c>
       <c r="B101" t="n">
-        <v>91553</v>
+        <v>75154</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>1776</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10904,10 +10904,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>425674</v>
+        <v>425617</v>
       </c>
       <c r="R101" t="n">
-        <v>7049982</v>
+        <v>7049900</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10959,44 +10959,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129627392</v>
+        <v>129629032</v>
       </c>
       <c r="B102" t="n">
-        <v>75154</v>
+        <v>79300</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1776</v>
+        <v>6459</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11006,10 +11006,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>425617</v>
+        <v>425674</v>
       </c>
       <c r="R102" t="n">
-        <v>7049900</v>
+        <v>7049976</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11046,7 +11046,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11061,44 +11061,44 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129629032</v>
+        <v>129628958</v>
       </c>
       <c r="B103" t="n">
-        <v>79300</v>
+        <v>91553</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6459</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11111,7 +11111,7 @@
         <v>425674</v>
       </c>
       <c r="R103" t="n">
-        <v>7049976</v>
+        <v>7049982</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11148,7 +11148,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11175,7 +11175,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129627367</v>
+        <v>129628991</v>
       </c>
       <c r="B104" t="n">
         <v>79515</v>
@@ -11210,10 +11210,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>425618</v>
+        <v>425724</v>
       </c>
       <c r="R104" t="n">
-        <v>7049902</v>
+        <v>7050035</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På två gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11265,22 +11265,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129628991</v>
+        <v>129629012</v>
       </c>
       <c r="B105" t="n">
-        <v>79515</v>
+        <v>91549</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11288,21 +11288,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1797</v>
+        <v>1108</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11312,10 +11312,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>425724</v>
+        <v>425698</v>
       </c>
       <c r="R105" t="n">
-        <v>7050035</v>
+        <v>7049997</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På två gamla granar i gammal granskog</t>
+          <t>På död och levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11379,10 +11379,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129629012</v>
+        <v>129627367</v>
       </c>
       <c r="B106" t="n">
-        <v>91549</v>
+        <v>79515</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11390,21 +11390,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1108</v>
+        <v>1797</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11414,10 +11414,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>425698</v>
+        <v>425618</v>
       </c>
       <c r="R106" t="n">
-        <v>7049997</v>
+        <v>7049902</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>På död och levande gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11469,12 +11469,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -11583,10 +11583,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129633399</v>
+        <v>129633479</v>
       </c>
       <c r="B108" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11594,23 +11594,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -11618,10 +11614,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>425574</v>
+        <v>425579</v>
       </c>
       <c r="R108" t="n">
-        <v>7049900</v>
+        <v>7049866</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11654,11 +11650,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11685,10 +11676,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129633479</v>
+        <v>129633399</v>
       </c>
       <c r="B109" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11696,19 +11687,23 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -11716,10 +11711,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>425579</v>
+        <v>425574</v>
       </c>
       <c r="R109" t="n">
-        <v>7049866</v>
+        <v>7049900</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11752,6 +11747,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11778,10 +11778,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129633408</v>
+        <v>129633458</v>
       </c>
       <c r="B110" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11789,21 +11789,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11813,10 +11813,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>425784</v>
+        <v>425678</v>
       </c>
       <c r="R110" t="n">
-        <v>7050165</v>
+        <v>7050015</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11849,11 +11849,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11880,10 +11875,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129633458</v>
+        <v>129633424</v>
       </c>
       <c r="B111" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11891,21 +11886,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11915,10 +11910,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>425678</v>
+        <v>425413</v>
       </c>
       <c r="R111" t="n">
-        <v>7050015</v>
+        <v>7049880</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11951,6 +11946,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12079,7 +12079,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129633442</v>
+        <v>129633408</v>
       </c>
       <c r="B113" t="n">
         <v>57727</v>
@@ -12114,10 +12114,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>425406</v>
+        <v>425784</v>
       </c>
       <c r="R113" t="n">
-        <v>7050149</v>
+        <v>7050165</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12181,7 +12181,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129633424</v>
+        <v>129633442</v>
       </c>
       <c r="B114" t="n">
         <v>57727</v>
@@ -12216,10 +12216,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>425413</v>
+        <v>425406</v>
       </c>
       <c r="R114" t="n">
-        <v>7049880</v>
+        <v>7050149</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12283,10 +12283,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129633440</v>
+        <v>129633478</v>
       </c>
       <c r="B115" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12294,23 +12294,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -12318,10 +12314,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>425382</v>
+        <v>425811</v>
       </c>
       <c r="R115" t="n">
-        <v>7050178</v>
+        <v>7050246</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12354,11 +12350,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12487,10 +12478,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129633478</v>
+        <v>129633402</v>
       </c>
       <c r="B117" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12498,19 +12489,23 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -12518,10 +12513,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>425811</v>
+        <v>425645</v>
       </c>
       <c r="R117" t="n">
-        <v>7050246</v>
+        <v>7050096</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12554,6 +12549,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12580,7 +12580,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129633402</v>
+        <v>129633440</v>
       </c>
       <c r="B118" t="n">
         <v>57727</v>
@@ -12615,10 +12615,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>425645</v>
+        <v>425382</v>
       </c>
       <c r="R118" t="n">
-        <v>7050096</v>
+        <v>7050178</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12655,7 +12655,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12682,32 +12682,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129633444</v>
+        <v>129633456</v>
       </c>
       <c r="B119" t="n">
-        <v>57727</v>
+        <v>79203</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>1249</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12717,10 +12717,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>425419</v>
+        <v>425675</v>
       </c>
       <c r="R119" t="n">
-        <v>7050137</v>
+        <v>7050020</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12753,11 +12753,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12988,10 +12983,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129633476</v>
+        <v>129633444</v>
       </c>
       <c r="B122" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12999,19 +12994,23 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -13019,10 +13018,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>425617</v>
+        <v>425419</v>
       </c>
       <c r="R122" t="n">
-        <v>7050214</v>
+        <v>7050137</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13055,6 +13054,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13081,34 +13085,30 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129633456</v>
+        <v>129633476</v>
       </c>
       <c r="B123" t="n">
-        <v>79203</v>
+        <v>91573</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1249</v>
+        <v>5432</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13116,10 +13116,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>425675</v>
+        <v>425617</v>
       </c>
       <c r="R123" t="n">
-        <v>7050020</v>
+        <v>7050214</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13271,10 +13271,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129633460</v>
+        <v>129633420</v>
       </c>
       <c r="B125" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13282,21 +13282,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13306,10 +13306,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>425741</v>
+        <v>425481</v>
       </c>
       <c r="R125" t="n">
-        <v>7050015</v>
+        <v>7049835</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13342,6 +13342,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13368,32 +13373,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129633420</v>
+        <v>129633389</v>
       </c>
       <c r="B126" t="n">
-        <v>57727</v>
+        <v>92271</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13403,10 +13408,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>425481</v>
+        <v>425870</v>
       </c>
       <c r="R126" t="n">
-        <v>7049835</v>
+        <v>7050232</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13439,11 +13444,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13470,32 +13470,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129633389</v>
+        <v>129633460</v>
       </c>
       <c r="B127" t="n">
-        <v>92271</v>
+        <v>91549</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13505,10 +13505,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>425870</v>
+        <v>425741</v>
       </c>
       <c r="R127" t="n">
-        <v>7050232</v>
+        <v>7050015</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13761,10 +13761,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129633404</v>
+        <v>129633471</v>
       </c>
       <c r="B130" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13772,21 +13772,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13796,10 +13796,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>425682</v>
+        <v>425534</v>
       </c>
       <c r="R130" t="n">
-        <v>7050073</v>
+        <v>7050039</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13832,11 +13832,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13863,7 +13858,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129633471</v>
+        <v>129633466</v>
       </c>
       <c r="B131" t="n">
         <v>91549</v>
@@ -13898,10 +13893,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>425534</v>
+        <v>426016</v>
       </c>
       <c r="R131" t="n">
-        <v>7050039</v>
+        <v>7050154</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13960,7 +13955,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129633439</v>
+        <v>129633413</v>
       </c>
       <c r="B132" t="n">
         <v>57727</v>
@@ -13995,10 +13990,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>425357</v>
+        <v>425870</v>
       </c>
       <c r="R132" t="n">
-        <v>7050155</v>
+        <v>7050230</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14062,10 +14057,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129633466</v>
+        <v>129633447</v>
       </c>
       <c r="B133" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14073,21 +14068,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14097,10 +14092,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>426016</v>
+        <v>425526</v>
       </c>
       <c r="R133" t="n">
-        <v>7050154</v>
+        <v>7050117</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14133,6 +14128,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14159,7 +14159,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129633447</v>
+        <v>129633404</v>
       </c>
       <c r="B134" t="n">
         <v>57727</v>
@@ -14194,10 +14194,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>425526</v>
+        <v>425682</v>
       </c>
       <c r="R134" t="n">
-        <v>7050117</v>
+        <v>7050073</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14261,7 +14261,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129633413</v>
+        <v>129633439</v>
       </c>
       <c r="B135" t="n">
         <v>57727</v>
@@ -14296,10 +14296,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>425870</v>
+        <v>425357</v>
       </c>
       <c r="R135" t="n">
-        <v>7050230</v>
+        <v>7050155</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14363,7 +14363,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129633419</v>
+        <v>129633403</v>
       </c>
       <c r="B136" t="n">
         <v>57727</v>
@@ -14398,10 +14398,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>425609</v>
+        <v>425668</v>
       </c>
       <c r="R136" t="n">
-        <v>7049867</v>
+        <v>7050116</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14438,7 +14438,7 @@
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14465,10 +14465,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129633468</v>
+        <v>129633419</v>
       </c>
       <c r="B137" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14476,21 +14476,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14500,10 +14500,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>425549</v>
+        <v>425609</v>
       </c>
       <c r="R137" t="n">
-        <v>7050165</v>
+        <v>7049867</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14536,6 +14536,11 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14562,10 +14567,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129633403</v>
+        <v>129633468</v>
       </c>
       <c r="B138" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14573,21 +14578,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14597,10 +14602,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>425668</v>
+        <v>425549</v>
       </c>
       <c r="R138" t="n">
-        <v>7050116</v>
+        <v>7050165</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14633,11 +14638,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14664,10 +14664,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129627372</v>
+        <v>129633386</v>
       </c>
       <c r="B139" t="n">
-        <v>95384</v>
+        <v>92271</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14675,38 +14675,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2412</v>
+        <v>3298</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
+          <t>Stor-grässjön s, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>425708</v>
+        <v>425587</v>
       </c>
       <c r="R139" t="n">
-        <v>7050205</v>
+        <v>7050138</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14741,40 +14737,34 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>på marken i kärr</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129633394</v>
+        <v>129627372</v>
       </c>
       <c r="B140" t="n">
-        <v>92271</v>
+        <v>95384</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14782,34 +14772,38 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3298</v>
+        <v>2412</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Stor-grässjön s, Jmt</t>
+          <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>425325</v>
+        <v>425708</v>
       </c>
       <c r="R140" t="n">
-        <v>7049857</v>
+        <v>7050205</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14844,56 +14838,62 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>på marken i kärr</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129633421</v>
+        <v>129633394</v>
       </c>
       <c r="B141" t="n">
-        <v>57727</v>
+        <v>92271</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14903,10 +14903,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>425262</v>
+        <v>425325</v>
       </c>
       <c r="R141" t="n">
-        <v>7049782</v>
+        <v>7049857</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14939,11 +14939,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14970,7 +14965,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129633415</v>
+        <v>129633416</v>
       </c>
       <c r="B142" t="n">
         <v>57727</v>
@@ -15005,10 +15000,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>426074</v>
+        <v>425828</v>
       </c>
       <c r="R142" t="n">
-        <v>7050193</v>
+        <v>7050054</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15045,7 +15040,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15072,7 +15067,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129633416</v>
+        <v>129633415</v>
       </c>
       <c r="B143" t="n">
         <v>57727</v>
@@ -15107,10 +15102,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>425828</v>
+        <v>426074</v>
       </c>
       <c r="R143" t="n">
-        <v>7050054</v>
+        <v>7050193</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15147,7 +15142,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15174,32 +15169,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129633386</v>
+        <v>129633436</v>
       </c>
       <c r="B144" t="n">
-        <v>92271</v>
+        <v>57727</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15209,10 +15204,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>425587</v>
+        <v>425329</v>
       </c>
       <c r="R144" t="n">
-        <v>7050138</v>
+        <v>7050182</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15245,6 +15240,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15271,7 +15271,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129633436</v>
+        <v>129633421</v>
       </c>
       <c r="B145" t="n">
         <v>57727</v>
@@ -15306,10 +15306,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>425329</v>
+        <v>425262</v>
       </c>
       <c r="R145" t="n">
-        <v>7050182</v>
+        <v>7049782</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15346,7 +15346,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15373,10 +15373,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129633429</v>
+        <v>129633483</v>
       </c>
       <c r="B146" t="n">
-        <v>57727</v>
+        <v>88952</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15384,21 +15384,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15408,10 +15408,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>425508</v>
+        <v>425789</v>
       </c>
       <c r="R146" t="n">
-        <v>7050208</v>
+        <v>7050109</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15444,11 +15444,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15475,32 +15470,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129633449</v>
+        <v>129633396</v>
       </c>
       <c r="B147" t="n">
-        <v>57727</v>
+        <v>92271</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15510,10 +15505,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>425515</v>
+        <v>425537</v>
       </c>
       <c r="R147" t="n">
-        <v>7050097</v>
+        <v>7050007</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15546,11 +15541,6 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15577,32 +15567,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129633396</v>
+        <v>129633457</v>
       </c>
       <c r="B148" t="n">
-        <v>92271</v>
+        <v>79203</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>3298</v>
+        <v>1249</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15612,10 +15602,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>425537</v>
+        <v>425579</v>
       </c>
       <c r="R148" t="n">
-        <v>7050007</v>
+        <v>7049866</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15674,32 +15664,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129633457</v>
+        <v>129633449</v>
       </c>
       <c r="B149" t="n">
-        <v>79203</v>
+        <v>57727</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1249</v>
+        <v>100109</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15709,10 +15699,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>425579</v>
+        <v>425515</v>
       </c>
       <c r="R149" t="n">
-        <v>7049866</v>
+        <v>7050097</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15745,6 +15735,11 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15771,10 +15766,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129633483</v>
+        <v>129633429</v>
       </c>
       <c r="B150" t="n">
-        <v>88952</v>
+        <v>57727</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15782,21 +15777,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15806,10 +15801,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>425789</v>
+        <v>425508</v>
       </c>
       <c r="R150" t="n">
-        <v>7050109</v>
+        <v>7050208</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15842,6 +15837,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16262,32 +16262,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129633463</v>
+        <v>129633383</v>
       </c>
       <c r="B155" t="n">
-        <v>91549</v>
+        <v>92271</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16297,10 +16297,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>425838</v>
+        <v>425676</v>
       </c>
       <c r="R155" t="n">
-        <v>7050241</v>
+        <v>7050147</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16359,32 +16359,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129633405</v>
+        <v>129633388</v>
       </c>
       <c r="B156" t="n">
-        <v>57727</v>
+        <v>92271</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16394,10 +16394,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>425721</v>
+        <v>425864</v>
       </c>
       <c r="R156" t="n">
-        <v>7050005</v>
+        <v>7050235</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16430,11 +16430,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16461,10 +16456,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129633446</v>
+        <v>129633463</v>
       </c>
       <c r="B157" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16472,21 +16467,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16496,10 +16491,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>425520</v>
+        <v>425838</v>
       </c>
       <c r="R157" t="n">
-        <v>7050128</v>
+        <v>7050241</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16532,11 +16527,6 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16563,32 +16553,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129633383</v>
+        <v>129633461</v>
       </c>
       <c r="B158" t="n">
-        <v>92271</v>
+        <v>91549</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16598,10 +16588,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>425676</v>
+        <v>425741</v>
       </c>
       <c r="R158" t="n">
-        <v>7050147</v>
+        <v>7050070</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16660,32 +16650,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129633388</v>
+        <v>129633405</v>
       </c>
       <c r="B159" t="n">
-        <v>92271</v>
+        <v>57727</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16695,10 +16685,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>425864</v>
+        <v>425721</v>
       </c>
       <c r="R159" t="n">
-        <v>7050235</v>
+        <v>7050005</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16731,6 +16721,11 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16757,10 +16752,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129633461</v>
+        <v>129633446</v>
       </c>
       <c r="B160" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16768,21 +16763,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16792,10 +16787,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>425741</v>
+        <v>425520</v>
       </c>
       <c r="R160" t="n">
-        <v>7050070</v>
+        <v>7050128</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16828,6 +16823,11 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16854,32 +16854,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129633427</v>
+        <v>129633392</v>
       </c>
       <c r="B161" t="n">
-        <v>57727</v>
+        <v>92271</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16889,10 +16889,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>425572</v>
+        <v>425789</v>
       </c>
       <c r="R161" t="n">
-        <v>7049987</v>
+        <v>7050048</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16925,11 +16925,6 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16956,32 +16951,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129633392</v>
+        <v>129633427</v>
       </c>
       <c r="B162" t="n">
-        <v>92271</v>
+        <v>57727</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16991,10 +16986,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>425789</v>
+        <v>425572</v>
       </c>
       <c r="R162" t="n">
-        <v>7050048</v>
+        <v>7049987</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17027,6 +17022,11 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17451,7 +17451,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129633414</v>
+        <v>129633451</v>
       </c>
       <c r="B167" t="n">
         <v>57727</v>
@@ -17486,10 +17486,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>426002</v>
+        <v>425266</v>
       </c>
       <c r="R167" t="n">
-        <v>7050197</v>
+        <v>7049914</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17526,7 +17526,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17553,10 +17553,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129633473</v>
+        <v>129633414</v>
       </c>
       <c r="B168" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17564,21 +17564,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17588,10 +17588,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>425218</v>
+        <v>426002</v>
       </c>
       <c r="R168" t="n">
-        <v>7049873</v>
+        <v>7050197</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17624,6 +17624,11 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17650,10 +17655,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129633484</v>
+        <v>129633480</v>
       </c>
       <c r="B169" t="n">
-        <v>88952</v>
+        <v>91573</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17661,23 +17666,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
@@ -17685,10 +17686,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>425629</v>
+        <v>425454</v>
       </c>
       <c r="R169" t="n">
-        <v>7050220</v>
+        <v>7050178</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17747,10 +17748,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129633480</v>
+        <v>129633473</v>
       </c>
       <c r="B170" t="n">
-        <v>91573</v>
+        <v>91549</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17758,19 +17759,23 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
@@ -17778,10 +17783,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>425454</v>
+        <v>425218</v>
       </c>
       <c r="R170" t="n">
-        <v>7050178</v>
+        <v>7049873</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17840,10 +17845,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129633451</v>
+        <v>129633484</v>
       </c>
       <c r="B171" t="n">
-        <v>57727</v>
+        <v>88952</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17851,21 +17856,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17875,10 +17880,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>425266</v>
+        <v>425629</v>
       </c>
       <c r="R171" t="n">
-        <v>7049914</v>
+        <v>7050220</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17911,11 +17916,6 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18044,10 +18044,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129633425</v>
+        <v>129633472</v>
       </c>
       <c r="B173" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18055,21 +18055,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18079,10 +18079,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>425535</v>
+        <v>425559</v>
       </c>
       <c r="R173" t="n">
-        <v>7049914</v>
+        <v>7050001</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18115,11 +18115,6 @@
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18146,32 +18141,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129633390</v>
+        <v>129633412</v>
       </c>
       <c r="B174" t="n">
-        <v>92271</v>
+        <v>57727</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18181,10 +18176,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>426060</v>
+        <v>425867</v>
       </c>
       <c r="R174" t="n">
-        <v>7050187</v>
+        <v>7050236</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18217,6 +18212,11 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18243,7 +18243,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129633412</v>
+        <v>129633425</v>
       </c>
       <c r="B175" t="n">
         <v>57727</v>
@@ -18278,10 +18278,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>425867</v>
+        <v>425535</v>
       </c>
       <c r="R175" t="n">
-        <v>7050236</v>
+        <v>7049914</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18345,7 +18345,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129633395</v>
+        <v>129633390</v>
       </c>
       <c r="B176" t="n">
         <v>92271</v>
@@ -18380,10 +18380,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>425561</v>
+        <v>426060</v>
       </c>
       <c r="R176" t="n">
-        <v>7050121</v>
+        <v>7050187</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18442,32 +18442,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129633472</v>
+        <v>129633395</v>
       </c>
       <c r="B177" t="n">
-        <v>91549</v>
+        <v>92271</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18477,10 +18477,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>425559</v>
+        <v>425561</v>
       </c>
       <c r="R177" t="n">
-        <v>7050001</v>
+        <v>7050121</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18641,10 +18641,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129633410</v>
+        <v>129633455</v>
       </c>
       <c r="B179" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18652,21 +18652,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18676,10 +18676,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>425574</v>
+        <v>425628</v>
       </c>
       <c r="R179" t="n">
-        <v>7050154</v>
+        <v>7050057</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18712,11 +18712,6 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -18743,7 +18738,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129633438</v>
+        <v>129633407</v>
       </c>
       <c r="B180" t="n">
         <v>57727</v>
@@ -18778,10 +18773,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>425374</v>
+        <v>425770</v>
       </c>
       <c r="R180" t="n">
-        <v>7050144</v>
+        <v>7050089</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18818,7 +18813,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -18845,10 +18840,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129633455</v>
+        <v>129633441</v>
       </c>
       <c r="B181" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18856,21 +18851,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18880,10 +18875,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>425628</v>
+        <v>425396</v>
       </c>
       <c r="R181" t="n">
-        <v>7050057</v>
+        <v>7050117</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18916,6 +18911,11 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -18942,7 +18942,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129633423</v>
+        <v>129633417</v>
       </c>
       <c r="B182" t="n">
         <v>57727</v>
@@ -18977,10 +18977,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>425400</v>
+        <v>425822</v>
       </c>
       <c r="R182" t="n">
-        <v>7049888</v>
+        <v>7050023</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19044,7 +19044,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129633417</v>
+        <v>129633438</v>
       </c>
       <c r="B183" t="n">
         <v>57727</v>
@@ -19079,10 +19079,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>425822</v>
+        <v>425374</v>
       </c>
       <c r="R183" t="n">
-        <v>7050023</v>
+        <v>7050144</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19119,7 +19119,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19350,7 +19350,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129633441</v>
+        <v>129633423</v>
       </c>
       <c r="B186" t="n">
         <v>57727</v>
@@ -19385,10 +19385,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>425396</v>
+        <v>425400</v>
       </c>
       <c r="R186" t="n">
-        <v>7050117</v>
+        <v>7049888</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19452,7 +19452,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129633407</v>
+        <v>129633410</v>
       </c>
       <c r="B187" t="n">
         <v>57727</v>
@@ -19487,10 +19487,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>425770</v>
+        <v>425574</v>
       </c>
       <c r="R187" t="n">
-        <v>7050089</v>
+        <v>7050154</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19554,32 +19554,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129633474</v>
+        <v>129633391</v>
       </c>
       <c r="B188" t="n">
-        <v>91567</v>
+        <v>92271</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19589,10 +19589,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>425916</v>
+        <v>426028</v>
       </c>
       <c r="R188" t="n">
-        <v>7050154</v>
+        <v>7050169</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19651,10 +19651,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129633433</v>
+        <v>129633474</v>
       </c>
       <c r="B189" t="n">
-        <v>57727</v>
+        <v>91567</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19662,21 +19662,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19686,10 +19686,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>425345</v>
+        <v>425916</v>
       </c>
       <c r="R189" t="n">
-        <v>7050197</v>
+        <v>7050154</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19722,11 +19722,6 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -19753,10 +19748,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129633401</v>
+        <v>129633485</v>
       </c>
       <c r="B190" t="n">
-        <v>57727</v>
+        <v>88952</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19764,21 +19759,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19788,10 +19783,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>425620</v>
+        <v>425211</v>
       </c>
       <c r="R190" t="n">
-        <v>7049978</v>
+        <v>7049786</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19824,11 +19819,6 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -19855,32 +19845,32 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129633391</v>
+        <v>129633467</v>
       </c>
       <c r="B191" t="n">
-        <v>92271</v>
+        <v>91549</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19890,10 +19880,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>426028</v>
+        <v>425215</v>
       </c>
       <c r="R191" t="n">
-        <v>7050169</v>
+        <v>7049827</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19952,7 +19942,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129633485</v>
+        <v>129633482</v>
       </c>
       <c r="B192" t="n">
         <v>88952</v>
@@ -19987,10 +19977,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>425211</v>
+        <v>425677</v>
       </c>
       <c r="R192" t="n">
-        <v>7049786</v>
+        <v>7050049</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20049,7 +20039,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129633418</v>
+        <v>129633433</v>
       </c>
       <c r="B193" t="n">
         <v>57727</v>
@@ -20084,10 +20074,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>425785</v>
+        <v>425345</v>
       </c>
       <c r="R193" t="n">
-        <v>7050033</v>
+        <v>7050197</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20124,7 +20114,7 @@
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20151,7 +20141,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129633432</v>
+        <v>129633422</v>
       </c>
       <c r="B194" t="n">
         <v>57727</v>
@@ -20186,10 +20176,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>425434</v>
+        <v>425222</v>
       </c>
       <c r="R194" t="n">
-        <v>7050220</v>
+        <v>7049839</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20226,7 +20216,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20253,10 +20243,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129633467</v>
+        <v>129633401</v>
       </c>
       <c r="B195" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20264,21 +20254,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20288,10 +20278,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>425215</v>
+        <v>425620</v>
       </c>
       <c r="R195" t="n">
-        <v>7049827</v>
+        <v>7049978</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20324,6 +20314,11 @@
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20350,7 +20345,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129633422</v>
+        <v>129633432</v>
       </c>
       <c r="B196" t="n">
         <v>57727</v>
@@ -20385,10 +20380,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>425222</v>
+        <v>425434</v>
       </c>
       <c r="R196" t="n">
-        <v>7049839</v>
+        <v>7050220</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20425,7 +20420,7 @@
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20452,10 +20447,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129633482</v>
+        <v>129633418</v>
       </c>
       <c r="B197" t="n">
-        <v>88952</v>
+        <v>57727</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20463,21 +20458,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20487,10 +20482,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>425677</v>
+        <v>425785</v>
       </c>
       <c r="R197" t="n">
-        <v>7050049</v>
+        <v>7050033</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20523,6 +20518,11 @@
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20549,32 +20549,32 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129633470</v>
+        <v>129633475</v>
       </c>
       <c r="B198" t="n">
-        <v>91549</v>
+        <v>91926</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1108</v>
+        <v>2063</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20584,10 +20584,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>425383</v>
+        <v>425690</v>
       </c>
       <c r="R198" t="n">
-        <v>7050135</v>
+        <v>7050235</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20646,10 +20646,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129633400</v>
+        <v>129633470</v>
       </c>
       <c r="B199" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20657,21 +20657,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20681,10 +20681,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>425596</v>
+        <v>425383</v>
       </c>
       <c r="R199" t="n">
-        <v>7049933</v>
+        <v>7050135</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20717,11 +20717,6 @@
       <c r="AA199" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -20748,32 +20743,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129633475</v>
+        <v>129633462</v>
       </c>
       <c r="B200" t="n">
-        <v>91926</v>
+        <v>91549</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>2063</v>
+        <v>1108</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20783,10 +20778,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>425690</v>
+        <v>425779</v>
       </c>
       <c r="R200" t="n">
-        <v>7050235</v>
+        <v>7050242</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20947,10 +20942,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129633462</v>
+        <v>129633437</v>
       </c>
       <c r="B202" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20958,21 +20953,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20982,10 +20977,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>425779</v>
+        <v>425347</v>
       </c>
       <c r="R202" t="n">
-        <v>7050242</v>
+        <v>7050132</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21018,6 +21013,11 @@
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21044,7 +21044,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129633437</v>
+        <v>129633400</v>
       </c>
       <c r="B203" t="n">
         <v>57727</v>
@@ -21079,10 +21079,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>425347</v>
+        <v>425596</v>
       </c>
       <c r="R203" t="n">
-        <v>7050132</v>
+        <v>7049933</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21119,7 +21119,7 @@
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21146,10 +21146,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129633434</v>
+        <v>129633469</v>
       </c>
       <c r="B204" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21157,21 +21157,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -21181,10 +21181,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>425344</v>
+        <v>425533</v>
       </c>
       <c r="R204" t="n">
-        <v>7050202</v>
+        <v>7050194</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21217,11 +21217,6 @@
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21350,10 +21345,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129633469</v>
+        <v>129633434</v>
       </c>
       <c r="B206" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21361,21 +21356,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21385,10 +21380,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>425533</v>
+        <v>425344</v>
       </c>
       <c r="R206" t="n">
-        <v>7050194</v>
+        <v>7050202</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21421,6 +21416,11 @@
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD206" t="b">

--- a/artfynd/A 47880-2025 artfynd.xlsx
+++ b/artfynd/A 47880-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129628994</v>
+        <v>129627353</v>
       </c>
       <c r="B2" t="n">
-        <v>79541</v>
+        <v>80176</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1797</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>425704</v>
+        <v>425377</v>
       </c>
       <c r="R2" t="n">
-        <v>7050007</v>
+        <v>7049766</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal död gran i gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129628949</v>
+        <v>129629020</v>
       </c>
       <c r="B3" t="n">
-        <v>78094</v>
+        <v>79070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +788,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>425719</v>
+        <v>425596</v>
       </c>
       <c r="R3" t="n">
-        <v>7050208</v>
+        <v>7049885</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +863,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran vid källflöde i gammal granskog, även trådfräken</t>
+          <t>250 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,6 +872,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,32 +891,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129628981</v>
+        <v>129628994</v>
       </c>
       <c r="B4" t="n">
-        <v>79229</v>
+        <v>79541</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1249</v>
+        <v>1797</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>425716</v>
+        <v>425704</v>
       </c>
       <c r="R4" t="n">
-        <v>7050121</v>
+        <v>7050007</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +966,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2 stora bålar på gammal levande gran</t>
+          <t>På bark vid basen av gammal död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129627353</v>
+        <v>129628949</v>
       </c>
       <c r="B5" t="n">
-        <v>80176</v>
+        <v>78094</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>425377</v>
+        <v>425719</v>
       </c>
       <c r="R5" t="n">
-        <v>7049766</v>
+        <v>7050208</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1068,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På bark på undersidan av död gren på gammal levande gran vid källflöde i gammal granskog, även trådfräken</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,68 +1083,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129629020</v>
+        <v>129628981</v>
       </c>
       <c r="B6" t="n">
-        <v>79070</v>
+        <v>79229</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>425596</v>
+        <v>425716</v>
       </c>
       <c r="R6" t="n">
-        <v>7049885</v>
+        <v>7050121</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,7 +1170,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>250 bålar på gammal levande gran i gammal granskog</t>
+          <t>2 stora bålar på gammal levande gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,7 +1179,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129628961</v>
+        <v>129627370</v>
       </c>
       <c r="B11" t="n">
-        <v>57730</v>
+        <v>78083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>425479</v>
+        <v>425453</v>
       </c>
       <c r="R11" t="n">
-        <v>7049837</v>
+        <v>7049864</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gammal levande gran i gammal granskog, även på rötter</t>
+          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,22 +1693,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129627370</v>
+        <v>129628961</v>
       </c>
       <c r="B12" t="n">
-        <v>78083</v>
+        <v>57730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>425453</v>
+        <v>425479</v>
       </c>
       <c r="R12" t="n">
-        <v>7049864</v>
+        <v>7049837</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>Äldre ringhack på gammal levande gran i gammal granskog, även på rötter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,12 +1795,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2426,10 +2426,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129628954</v>
+        <v>129627375</v>
       </c>
       <c r="B19" t="n">
-        <v>83039</v>
+        <v>91577</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2437,21 +2437,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>425469</v>
+        <v>425697</v>
       </c>
       <c r="R19" t="n">
-        <v>7049817</v>
+        <v>7050004</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,44 +2516,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129628984</v>
+        <v>129628997</v>
       </c>
       <c r="B20" t="n">
-        <v>80203</v>
+        <v>79541</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>1797</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>425327</v>
+        <v>425393</v>
       </c>
       <c r="R20" t="n">
-        <v>7049709</v>
+        <v>7049812</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2630,45 +2630,56 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129628992</v>
+        <v>129627361</v>
       </c>
       <c r="B21" t="n">
-        <v>79070</v>
+        <v>79229</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>425721</v>
+        <v>425570</v>
       </c>
       <c r="R21" t="n">
-        <v>7050017</v>
+        <v>7049933</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2705,7 +2716,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>20 bålar på gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2714,28 +2725,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129627375</v>
+        <v>129627369</v>
       </c>
       <c r="B22" t="n">
-        <v>91577</v>
+        <v>79541</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2743,21 +2755,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>1797</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2767,10 +2779,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>425697</v>
+        <v>425420</v>
       </c>
       <c r="R22" t="n">
-        <v>7050004</v>
+        <v>7049825</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2807,7 +2819,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2834,10 +2846,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129628997</v>
+        <v>129629009</v>
       </c>
       <c r="B23" t="n">
-        <v>79541</v>
+        <v>91577</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2845,21 +2857,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1797</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2869,10 +2881,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>425393</v>
+        <v>425707</v>
       </c>
       <c r="R23" t="n">
-        <v>7049812</v>
+        <v>7050031</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2909,7 +2921,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2936,56 +2948,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129627361</v>
+        <v>129628954</v>
       </c>
       <c r="B24" t="n">
-        <v>79229</v>
+        <v>83039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1249</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>425570</v>
+        <v>425469</v>
       </c>
       <c r="R24" t="n">
-        <v>7049933</v>
+        <v>7049817</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3022,7 +3023,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3031,51 +3032,50 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129627369</v>
+        <v>129628984</v>
       </c>
       <c r="B25" t="n">
-        <v>79541</v>
+        <v>80203</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1797</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>425420</v>
+        <v>425327</v>
       </c>
       <c r="R25" t="n">
-        <v>7049825</v>
+        <v>7049709</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3140,22 +3140,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129629009</v>
+        <v>129628992</v>
       </c>
       <c r="B26" t="n">
-        <v>91577</v>
+        <v>79070</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3163,21 +3163,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>425707</v>
+        <v>425721</v>
       </c>
       <c r="R26" t="n">
-        <v>7050031</v>
+        <v>7050017</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>20 bålar på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3981,10 +3981,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129628980</v>
+        <v>129628979</v>
       </c>
       <c r="B34" t="n">
-        <v>78083</v>
+        <v>83039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3992,21 +3992,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4083,32 +4083,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129628965</v>
+        <v>129628956</v>
       </c>
       <c r="B35" t="n">
-        <v>83037</v>
+        <v>83039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6486</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4118,10 +4118,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>425510</v>
+        <v>425268</v>
       </c>
       <c r="R35" t="n">
-        <v>7049849</v>
+        <v>7049748</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande grov gran i gammal fuktig granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4167,6 +4167,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4185,56 +4186,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627347</v>
+        <v>129627336</v>
       </c>
       <c r="B36" t="n">
-        <v>92536</v>
+        <v>83039</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4769</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>425707</v>
+        <v>425710</v>
       </c>
       <c r="R36" t="n">
-        <v>7050150</v>
+        <v>7050275</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4269,13 +4259,17 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4294,32 +4288,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129628979</v>
+        <v>129627337</v>
       </c>
       <c r="B37" t="n">
-        <v>83039</v>
+        <v>91545</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4329,10 +4323,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>425716</v>
+        <v>425649</v>
       </c>
       <c r="R37" t="n">
-        <v>7050121</v>
+        <v>7049974</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4367,11 +4361,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>på gammal levande gran</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4384,22 +4373,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129628956</v>
+        <v>129628971</v>
       </c>
       <c r="B38" t="n">
-        <v>83039</v>
+        <v>79070</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4407,21 +4396,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4431,10 +4420,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>425268</v>
+        <v>425704</v>
       </c>
       <c r="R38" t="n">
-        <v>7049748</v>
+        <v>7050246</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4471,7 +4460,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4480,7 +4469,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4499,10 +4487,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129627336</v>
+        <v>129628980</v>
       </c>
       <c r="B39" t="n">
-        <v>83039</v>
+        <v>78083</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4510,21 +4498,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4534,10 +4522,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>425710</v>
+        <v>425716</v>
       </c>
       <c r="R39" t="n">
-        <v>7050275</v>
+        <v>7050121</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4574,7 +4562,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>på gammal levande gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4589,44 +4577,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129627337</v>
+        <v>129628965</v>
       </c>
       <c r="B40" t="n">
-        <v>91545</v>
+        <v>83037</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6486</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4636,10 +4624,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>425649</v>
+        <v>425510</v>
       </c>
       <c r="R40" t="n">
-        <v>7049974</v>
+        <v>7049849</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4674,6 +4662,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På bark i hålighet vid basen av gammal levande grov gran i gammal fuktig granskog</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4686,57 +4679,68 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129628971</v>
+        <v>129627347</v>
       </c>
       <c r="B41" t="n">
-        <v>79070</v>
+        <v>92536</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>425704</v>
+        <v>425707</v>
       </c>
       <c r="R41" t="n">
-        <v>7050246</v>
+        <v>7050150</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4771,29 +4775,25 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>på gammal gran i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5623,45 +5623,53 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129627338</v>
+        <v>129627345</v>
       </c>
       <c r="B50" t="n">
-        <v>92299</v>
+        <v>57890</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>425585</v>
+        <v>425507</v>
       </c>
       <c r="R50" t="n">
-        <v>7050170</v>
+        <v>7049861</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5694,11 +5702,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5725,53 +5728,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129627345</v>
+        <v>129627338</v>
       </c>
       <c r="B51" t="n">
-        <v>57890</v>
+        <v>92299</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>425507</v>
+        <v>425585</v>
       </c>
       <c r="R51" t="n">
-        <v>7049861</v>
+        <v>7050170</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5804,6 +5799,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7168,32 +7168,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129629004</v>
+        <v>129629030</v>
       </c>
       <c r="B65" t="n">
-        <v>96187</v>
+        <v>83031</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2682</v>
+        <v>308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kärrkammossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Helodium blandowii</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7203,10 +7203,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>425685</v>
+        <v>425332</v>
       </c>
       <c r="R65" t="n">
-        <v>7050259</v>
+        <v>7049768</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På marken i rikkärr</t>
+          <t>På ved på björkhögstubbe i gammal granskog, även gulnål och nordlig nållav på barken</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7270,32 +7270,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129628989</v>
+        <v>129629004</v>
       </c>
       <c r="B66" t="n">
-        <v>83039</v>
+        <v>96187</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>2682</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kärrkammossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Helodium blandowii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7305,10 +7305,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>425724</v>
+        <v>425685</v>
       </c>
       <c r="R66" t="n">
-        <v>7050035</v>
+        <v>7050259</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>på gran i gammal granskog</t>
+          <t>På marken i rikkärr</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7372,7 +7372,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129628985</v>
+        <v>129628989</v>
       </c>
       <c r="B67" t="n">
         <v>83039</v>
@@ -7407,10 +7407,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>425529</v>
+        <v>425724</v>
       </c>
       <c r="R67" t="n">
-        <v>7049841</v>
+        <v>7050035</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal sälg i gammal granskog</t>
+          <t>på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7474,10 +7474,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129627379</v>
+        <v>129628985</v>
       </c>
       <c r="B68" t="n">
-        <v>79070</v>
+        <v>83039</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7485,21 +7485,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>425501</v>
+        <v>425529</v>
       </c>
       <c r="R68" t="n">
-        <v>7049848</v>
+        <v>7049841</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>100 bålar</t>
+          <t>På bark på stam av död gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7564,44 +7564,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129627365</v>
+        <v>129627379</v>
       </c>
       <c r="B69" t="n">
-        <v>80203</v>
+        <v>79070</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7611,10 +7611,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>425720</v>
+        <v>425501</v>
       </c>
       <c r="R69" t="n">
-        <v>7050056</v>
+        <v>7049848</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7649,6 +7649,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>100 bålar</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7666,39 +7671,39 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129629030</v>
+        <v>129627365</v>
       </c>
       <c r="B70" t="n">
-        <v>83031</v>
+        <v>80203</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>308</v>
+        <v>6461</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7708,10 +7713,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>425332</v>
+        <v>425720</v>
       </c>
       <c r="R70" t="n">
-        <v>7049768</v>
+        <v>7050056</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7746,11 +7751,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På ved på björkhögstubbe i gammal granskog, även gulnål och nordlig nållav på barken</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7763,12 +7763,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -9336,32 +9336,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129629021</v>
+        <v>129627339</v>
       </c>
       <c r="B86" t="n">
-        <v>79070</v>
+        <v>92299</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>425518</v>
+        <v>425702</v>
       </c>
       <c r="R86" t="n">
-        <v>7049851</v>
+        <v>7050007</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9409,11 +9409,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9426,44 +9421,44 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129627339</v>
+        <v>129629021</v>
       </c>
       <c r="B87" t="n">
-        <v>92299</v>
+        <v>79070</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9473,10 +9468,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>425702</v>
+        <v>425518</v>
       </c>
       <c r="R87" t="n">
-        <v>7050007</v>
+        <v>7049851</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9511,6 +9506,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Rikligt på gamla granar i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -9523,12 +9523,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10453,32 +10453,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129629029</v>
+        <v>129629033</v>
       </c>
       <c r="B97" t="n">
-        <v>83022</v>
+        <v>78083</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6439</v>
+        <v>228579</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10488,10 +10488,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>425332</v>
+        <v>425685</v>
       </c>
       <c r="R97" t="n">
-        <v>7049768</v>
+        <v>7050259</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10528,7 +10528,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>På bark på björkhögstubbe i gammal granskog</t>
+          <t>på gammal levande gran i gammal granskog vid rikkärr vid sjö</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10555,32 +10555,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129628953</v>
+        <v>129629029</v>
       </c>
       <c r="B98" t="n">
-        <v>83039</v>
+        <v>83022</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10590,10 +10590,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>425660</v>
+        <v>425332</v>
       </c>
       <c r="R98" t="n">
-        <v>7050271</v>
+        <v>7049768</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10630,7 +10630,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På bark på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10657,10 +10657,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129627343</v>
+        <v>129628953</v>
       </c>
       <c r="B99" t="n">
-        <v>57730</v>
+        <v>83039</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10668,42 +10668,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>425384</v>
+        <v>425660</v>
       </c>
       <c r="R99" t="n">
-        <v>7049814</v>
+        <v>7050271</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10740,7 +10732,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>ringhack på gran</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10755,22 +10747,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129629033</v>
+        <v>129627343</v>
       </c>
       <c r="B100" t="n">
-        <v>78083</v>
+        <v>57730</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10778,34 +10770,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>425685</v>
+        <v>425384</v>
       </c>
       <c r="R100" t="n">
-        <v>7050259</v>
+        <v>7049814</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>på gammal levande gran i gammal granskog vid rikkärr vid sjö</t>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10857,44 +10857,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129627392</v>
+        <v>129628958</v>
       </c>
       <c r="B101" t="n">
-        <v>75175</v>
+        <v>91581</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1776</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10904,10 +10904,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>425617</v>
+        <v>425674</v>
       </c>
       <c r="R101" t="n">
-        <v>7049900</v>
+        <v>7049982</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10959,44 +10959,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129628958</v>
+        <v>129627392</v>
       </c>
       <c r="B102" t="n">
-        <v>91581</v>
+        <v>75175</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>1776</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11006,10 +11006,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>425674</v>
+        <v>425617</v>
       </c>
       <c r="R102" t="n">
-        <v>7049982</v>
+        <v>7049900</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11046,7 +11046,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11061,12 +11061,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -11175,10 +11175,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129628990</v>
+        <v>129629012</v>
       </c>
       <c r="B104" t="n">
-        <v>78083</v>
+        <v>91577</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11186,21 +11186,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228579</v>
+        <v>1108</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11210,10 +11210,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>425724</v>
+        <v>425698</v>
       </c>
       <c r="R104" t="n">
-        <v>7050035</v>
+        <v>7049997</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>på gran i gammal granskog</t>
+          <t>På död och levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11277,10 +11277,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129629012</v>
+        <v>129628991</v>
       </c>
       <c r="B105" t="n">
-        <v>91577</v>
+        <v>79541</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11288,21 +11288,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1108</v>
+        <v>1797</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11312,10 +11312,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>425698</v>
+        <v>425724</v>
       </c>
       <c r="R105" t="n">
-        <v>7049997</v>
+        <v>7050035</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På död och levande gammal gran i gammal granskog</t>
+          <t>På två gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11379,7 +11379,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129628991</v>
+        <v>129627367</v>
       </c>
       <c r="B106" t="n">
         <v>79541</v>
@@ -11414,10 +11414,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>425724</v>
+        <v>425618</v>
       </c>
       <c r="R106" t="n">
-        <v>7050035</v>
+        <v>7049902</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>På två gamla granar i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11469,22 +11469,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129627367</v>
+        <v>129628990</v>
       </c>
       <c r="B107" t="n">
-        <v>79541</v>
+        <v>78083</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11492,21 +11492,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1797</v>
+        <v>228579</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11516,10 +11516,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>425618</v>
+        <v>425724</v>
       </c>
       <c r="R107" t="n">
-        <v>7049902</v>
+        <v>7050035</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11556,7 +11556,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11571,12 +11571,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -12682,34 +12682,30 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129633456</v>
+        <v>129633476</v>
       </c>
       <c r="B119" t="n">
-        <v>79229</v>
+        <v>91601</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1249</v>
+        <v>5432</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -12717,10 +12713,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>425675</v>
+        <v>425617</v>
       </c>
       <c r="R119" t="n">
-        <v>7050020</v>
+        <v>7050214</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12779,7 +12775,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129633476</v>
+        <v>129633477</v>
       </c>
       <c r="B120" t="n">
         <v>91601</v>
@@ -12810,10 +12806,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>425617</v>
+        <v>425690</v>
       </c>
       <c r="R120" t="n">
-        <v>7050214</v>
+        <v>7050235</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12872,30 +12868,34 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129633477</v>
+        <v>129633456</v>
       </c>
       <c r="B121" t="n">
-        <v>91601</v>
+        <v>79229</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5432</v>
+        <v>1249</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -12903,10 +12903,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>425690</v>
+        <v>425675</v>
       </c>
       <c r="R121" t="n">
-        <v>7050235</v>
+        <v>7050020</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13271,32 +13271,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129633389</v>
+        <v>129633460</v>
       </c>
       <c r="B125" t="n">
-        <v>92299</v>
+        <v>91577</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13306,10 +13306,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>425870</v>
+        <v>425741</v>
       </c>
       <c r="R125" t="n">
-        <v>7050232</v>
+        <v>7050015</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13368,7 +13368,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129633460</v>
+        <v>129633459</v>
       </c>
       <c r="B126" t="n">
         <v>91577</v>
@@ -13403,10 +13403,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>425741</v>
+        <v>425702</v>
       </c>
       <c r="R126" t="n">
-        <v>7050015</v>
+        <v>7050011</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13465,10 +13465,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129633459</v>
+        <v>129633420</v>
       </c>
       <c r="B127" t="n">
-        <v>91577</v>
+        <v>57730</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13476,21 +13476,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>425702</v>
+        <v>425481</v>
       </c>
       <c r="R127" t="n">
-        <v>7050011</v>
+        <v>7049835</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13536,6 +13536,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13562,32 +13567,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129633420</v>
+        <v>129633389</v>
       </c>
       <c r="B128" t="n">
-        <v>57730</v>
+        <v>92299</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13597,10 +13602,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>425481</v>
+        <v>425870</v>
       </c>
       <c r="R128" t="n">
-        <v>7049835</v>
+        <v>7050232</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13633,11 +13638,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -16456,32 +16456,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129633405</v>
+        <v>129633383</v>
       </c>
       <c r="B157" t="n">
-        <v>57730</v>
+        <v>92299</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16491,10 +16491,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>425721</v>
+        <v>425676</v>
       </c>
       <c r="R157" t="n">
-        <v>7050005</v>
+        <v>7050147</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16527,11 +16527,6 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16558,32 +16553,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129633446</v>
+        <v>129633388</v>
       </c>
       <c r="B158" t="n">
-        <v>57730</v>
+        <v>92299</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16593,10 +16588,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>425520</v>
+        <v>425864</v>
       </c>
       <c r="R158" t="n">
-        <v>7050128</v>
+        <v>7050235</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16629,11 +16624,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16660,32 +16650,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129633383</v>
+        <v>129633405</v>
       </c>
       <c r="B159" t="n">
-        <v>92299</v>
+        <v>57730</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16695,10 +16685,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>425676</v>
+        <v>425721</v>
       </c>
       <c r="R159" t="n">
-        <v>7050147</v>
+        <v>7050005</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16731,6 +16721,11 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16757,32 +16752,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129633388</v>
+        <v>129633446</v>
       </c>
       <c r="B160" t="n">
-        <v>92299</v>
+        <v>57730</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16792,10 +16787,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>425864</v>
+        <v>425520</v>
       </c>
       <c r="R160" t="n">
-        <v>7050235</v>
+        <v>7050128</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16828,6 +16823,11 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17645,10 +17645,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129633451</v>
+        <v>129633480</v>
       </c>
       <c r="B169" t="n">
-        <v>57730</v>
+        <v>91601</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17656,23 +17656,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
@@ -17680,10 +17676,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>425266</v>
+        <v>425454</v>
       </c>
       <c r="R169" t="n">
-        <v>7049914</v>
+        <v>7050178</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17716,11 +17712,6 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17747,7 +17738,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129633414</v>
+        <v>129633451</v>
       </c>
       <c r="B170" t="n">
         <v>57730</v>
@@ -17782,10 +17773,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>426002</v>
+        <v>425266</v>
       </c>
       <c r="R170" t="n">
-        <v>7050197</v>
+        <v>7049914</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17822,7 +17813,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17849,10 +17840,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129633453</v>
+        <v>129633414</v>
       </c>
       <c r="B171" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17860,16 +17851,16 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -17884,10 +17875,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>426018</v>
+        <v>426002</v>
       </c>
       <c r="R171" t="n">
-        <v>7050201</v>
+        <v>7050197</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17924,7 +17915,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -17951,10 +17942,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129633480</v>
+        <v>129633453</v>
       </c>
       <c r="B172" t="n">
-        <v>91601</v>
+        <v>57727</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17962,19 +17953,23 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
@@ -17982,10 +17977,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>425454</v>
+        <v>426018</v>
       </c>
       <c r="R172" t="n">
-        <v>7050178</v>
+        <v>7050201</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18018,6 +18013,11 @@
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18141,32 +18141,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129633412</v>
+        <v>129633390</v>
       </c>
       <c r="B174" t="n">
-        <v>57730</v>
+        <v>92299</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18176,10 +18176,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>425867</v>
+        <v>426060</v>
       </c>
       <c r="R174" t="n">
-        <v>7050236</v>
+        <v>7050187</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18212,11 +18212,6 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18243,32 +18238,32 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129633425</v>
+        <v>129633395</v>
       </c>
       <c r="B175" t="n">
-        <v>57730</v>
+        <v>92299</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18278,10 +18273,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>425535</v>
+        <v>425561</v>
       </c>
       <c r="R175" t="n">
-        <v>7049914</v>
+        <v>7050121</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18314,11 +18309,6 @@
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18345,32 +18335,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129633390</v>
+        <v>129633412</v>
       </c>
       <c r="B176" t="n">
-        <v>92299</v>
+        <v>57730</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18380,10 +18370,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>426060</v>
+        <v>425867</v>
       </c>
       <c r="R176" t="n">
-        <v>7050187</v>
+        <v>7050236</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18416,6 +18406,11 @@
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18442,32 +18437,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129633395</v>
+        <v>129633425</v>
       </c>
       <c r="B177" t="n">
-        <v>92299</v>
+        <v>57730</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18477,10 +18472,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>425561</v>
+        <v>425535</v>
       </c>
       <c r="R177" t="n">
-        <v>7050121</v>
+        <v>7049914</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18513,6 +18508,11 @@
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -18641,10 +18641,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129633407</v>
+        <v>129633455</v>
       </c>
       <c r="B179" t="n">
-        <v>57730</v>
+        <v>80176</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18652,21 +18652,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18676,10 +18676,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>425770</v>
+        <v>425628</v>
       </c>
       <c r="R179" t="n">
-        <v>7050089</v>
+        <v>7050057</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18712,11 +18712,6 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -18743,7 +18738,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129633441</v>
+        <v>129633407</v>
       </c>
       <c r="B180" t="n">
         <v>57730</v>
@@ -18778,10 +18773,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>425396</v>
+        <v>425770</v>
       </c>
       <c r="R180" t="n">
-        <v>7050117</v>
+        <v>7050089</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18818,7 +18813,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -18845,7 +18840,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129633417</v>
+        <v>129633441</v>
       </c>
       <c r="B181" t="n">
         <v>57730</v>
@@ -18880,10 +18875,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>425822</v>
+        <v>425396</v>
       </c>
       <c r="R181" t="n">
-        <v>7050023</v>
+        <v>7050117</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18947,7 +18942,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129633438</v>
+        <v>129633417</v>
       </c>
       <c r="B182" t="n">
         <v>57730</v>
@@ -18982,10 +18977,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>425374</v>
+        <v>425822</v>
       </c>
       <c r="R182" t="n">
-        <v>7050144</v>
+        <v>7050023</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19022,7 +19017,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19049,7 +19044,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129633430</v>
+        <v>129633438</v>
       </c>
       <c r="B183" t="n">
         <v>57730</v>
@@ -19084,10 +19079,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>425506</v>
+        <v>425374</v>
       </c>
       <c r="R183" t="n">
-        <v>7050201</v>
+        <v>7050144</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19151,7 +19146,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129633398</v>
+        <v>129633430</v>
       </c>
       <c r="B184" t="n">
         <v>57730</v>
@@ -19186,10 +19181,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>425512</v>
+        <v>425506</v>
       </c>
       <c r="R184" t="n">
-        <v>7049868</v>
+        <v>7050201</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19226,7 +19221,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19253,7 +19248,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129633423</v>
+        <v>129633398</v>
       </c>
       <c r="B185" t="n">
         <v>57730</v>
@@ -19288,10 +19283,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>425400</v>
+        <v>425512</v>
       </c>
       <c r="R185" t="n">
-        <v>7049888</v>
+        <v>7049868</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19328,7 +19323,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19355,7 +19350,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129633410</v>
+        <v>129633423</v>
       </c>
       <c r="B186" t="n">
         <v>57730</v>
@@ -19390,10 +19385,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>425574</v>
+        <v>425400</v>
       </c>
       <c r="R186" t="n">
-        <v>7050154</v>
+        <v>7049888</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19430,7 +19425,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19457,10 +19452,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129633455</v>
+        <v>129633410</v>
       </c>
       <c r="B187" t="n">
-        <v>80176</v>
+        <v>57730</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19468,21 +19463,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19492,10 +19487,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>425628</v>
+        <v>425574</v>
       </c>
       <c r="R187" t="n">
-        <v>7050057</v>
+        <v>7050154</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19528,6 +19523,11 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -22661,32 +22661,32 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129672502</v>
+        <v>129672468</v>
       </c>
       <c r="B219" t="n">
-        <v>79151</v>
+        <v>79326</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>283</v>
+        <v>6459</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -22696,10 +22696,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>425572</v>
+        <v>425444</v>
       </c>
       <c r="R219" t="n">
-        <v>7049859</v>
+        <v>7049814</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22758,10 +22758,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129672487</v>
+        <v>129672502</v>
       </c>
       <c r="B220" t="n">
-        <v>97002</v>
+        <v>79151</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22769,21 +22769,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>53</v>
+        <v>283</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22793,10 +22793,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>425724</v>
+        <v>425572</v>
       </c>
       <c r="R220" t="n">
-        <v>7050188</v>
+        <v>7049859</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22855,32 +22855,32 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129672468</v>
+        <v>129672487</v>
       </c>
       <c r="B221" t="n">
-        <v>79326</v>
+        <v>97002</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6459</v>
+        <v>53</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -22890,10 +22890,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>425444</v>
+        <v>425724</v>
       </c>
       <c r="R221" t="n">
-        <v>7049814</v>
+        <v>7050188</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>

--- a/artfynd/A 47880-2025 artfynd.xlsx
+++ b/artfynd/A 47880-2025 artfynd.xlsx
@@ -3254,32 +3254,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129629010</v>
+        <v>129627342</v>
       </c>
       <c r="B27" t="n">
-        <v>83043</v>
+        <v>92306</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6486</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>425698</v>
+        <v>425473</v>
       </c>
       <c r="R27" t="n">
-        <v>7049997</v>
+        <v>7049830</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande grov gran i gammal fuktig granskog</t>
+          <t>på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3338,74 +3338,64 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129627363</v>
+        <v>129628988</v>
       </c>
       <c r="B28" t="n">
-        <v>79235</v>
+        <v>79076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>425428</v>
+        <v>425724</v>
       </c>
       <c r="R28" t="n">
-        <v>7049830</v>
+        <v>7050035</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3442,7 +3432,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>vid västsluttning och vattenkälla</t>
+          <t>på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3451,29 +3441,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129627342</v>
+        <v>129629025</v>
       </c>
       <c r="B29" t="n">
-        <v>92306</v>
+        <v>83028</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3481,21 +3470,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>6439</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3505,10 +3494,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>425473</v>
+        <v>425717</v>
       </c>
       <c r="R29" t="n">
-        <v>7049830</v>
+        <v>7050119</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3545,7 +3534,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>på gran i gammal granskog</t>
+          <t>På ved i hålighet vid basen av gammal död gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3554,51 +3543,50 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129628988</v>
+        <v>129628999</v>
       </c>
       <c r="B30" t="n">
-        <v>79076</v>
+        <v>97686</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>221063</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3608,10 +3596,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>425724</v>
+        <v>425716</v>
       </c>
       <c r="R30" t="n">
-        <v>7050035</v>
+        <v>7050162</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,7 +3636,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>på gran i gammal granskog</t>
+          <t>På marken i rikare källflöde i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3675,45 +3663,56 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129629025</v>
+        <v>129627363</v>
       </c>
       <c r="B31" t="n">
-        <v>83028</v>
+        <v>79235</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6439</v>
+        <v>1249</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>425717</v>
+        <v>425428</v>
       </c>
       <c r="R31" t="n">
-        <v>7050119</v>
+        <v>7049830</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3750,7 +3749,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På ved i hålighet vid basen av gammal död gran</t>
+          <t>vid västsluttning och vattenkälla</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3759,18 +3758,19 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3879,32 +3879,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129628999</v>
+        <v>129629010</v>
       </c>
       <c r="B33" t="n">
-        <v>97686</v>
+        <v>83043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221063</v>
+        <v>6486</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>425716</v>
+        <v>425698</v>
       </c>
       <c r="R33" t="n">
-        <v>7050162</v>
+        <v>7049997</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På marken i rikare källflöde i gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal levande grov gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4902,32 +4902,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129627338</v>
+        <v>129629035</v>
       </c>
       <c r="B43" t="n">
-        <v>92306</v>
+        <v>75181</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3298</v>
+        <v>1776</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4937,10 +4937,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>425585</v>
+        <v>425578</v>
       </c>
       <c r="R43" t="n">
-        <v>7050170</v>
+        <v>7049878</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>På tunna döda kvistar på ca 200 år gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4992,22 +4992,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129629014</v>
+        <v>129629011</v>
       </c>
       <c r="B44" t="n">
-        <v>91584</v>
+        <v>79547</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5015,21 +5015,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>1797</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>425660</v>
+        <v>425698</v>
       </c>
       <c r="R44" t="n">
-        <v>7049963</v>
+        <v>7049997</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5106,45 +5106,56 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129627374</v>
+        <v>129627354</v>
       </c>
       <c r="B45" t="n">
-        <v>79157</v>
+        <v>79235</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>425431</v>
+        <v>425716</v>
       </c>
       <c r="R45" t="n">
-        <v>7049839</v>
+        <v>7050148</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5179,17 +5190,13 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>på tunna kvistar</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5208,10 +5215,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129629007</v>
+        <v>129627378</v>
       </c>
       <c r="B46" t="n">
-        <v>79157</v>
+        <v>79076</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5219,21 +5226,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5243,10 +5250,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>425720</v>
+        <v>425710</v>
       </c>
       <c r="R46" t="n">
-        <v>7050011</v>
+        <v>7050152</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5283,7 +5290,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal levande senvuxen undertryckt gran i gammal fuktig granskog</t>
+          <t>150 bålar</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5298,44 +5305,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129629035</v>
+        <v>129627338</v>
       </c>
       <c r="B47" t="n">
-        <v>75181</v>
+        <v>92306</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1776</v>
+        <v>3298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5345,10 +5352,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>425578</v>
+        <v>425585</v>
       </c>
       <c r="R47" t="n">
-        <v>7049878</v>
+        <v>7050170</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5385,7 +5392,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På tunna döda kvistar på ca 200 år gammal gran i gammal granskog</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5400,22 +5407,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129629011</v>
+        <v>129629014</v>
       </c>
       <c r="B48" t="n">
-        <v>79547</v>
+        <v>91584</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5423,21 +5430,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1797</v>
+        <v>1108</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5447,10 +5454,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>425698</v>
+        <v>425660</v>
       </c>
       <c r="R48" t="n">
-        <v>7049997</v>
+        <v>7049963</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5487,7 +5494,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5514,56 +5521,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129627354</v>
+        <v>129627374</v>
       </c>
       <c r="B49" t="n">
-        <v>79235</v>
+        <v>79157</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>425716</v>
+        <v>425431</v>
       </c>
       <c r="R49" t="n">
-        <v>7050148</v>
+        <v>7049839</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5598,13 +5594,17 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>på tunna kvistar</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5623,10 +5623,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129627378</v>
+        <v>129629007</v>
       </c>
       <c r="B50" t="n">
-        <v>79076</v>
+        <v>79157</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5634,21 +5634,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5658,10 +5658,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>425710</v>
+        <v>425720</v>
       </c>
       <c r="R50" t="n">
-        <v>7050152</v>
+        <v>7050011</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>150 bålar</t>
+          <t>På tunna kvistar på gammal levande senvuxen undertryckt gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5713,12 +5713,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5830,32 +5830,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129628948</v>
+        <v>129628983</v>
       </c>
       <c r="B52" t="n">
-        <v>97686</v>
+        <v>79235</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221063</v>
+        <v>1249</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>425719</v>
+        <v>425721</v>
       </c>
       <c r="R52" t="n">
-        <v>7050208</v>
+        <v>7050017</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På marken i källflöde i gammal granskog</t>
+          <t>På gren på gammal död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5932,32 +5932,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129628983</v>
+        <v>129628996</v>
       </c>
       <c r="B53" t="n">
-        <v>79235</v>
+        <v>79547</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1249</v>
+        <v>1797</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5967,10 +5967,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>425721</v>
+        <v>425596</v>
       </c>
       <c r="R53" t="n">
-        <v>7050017</v>
+        <v>7049885</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På gren på gammal död gran i gammal granskog</t>
+          <t>På basen av gammal levande gran i gammal fuktig granskog i sluttning</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6034,32 +6034,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129628996</v>
+        <v>129628948</v>
       </c>
       <c r="B54" t="n">
-        <v>79547</v>
+        <v>97686</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1797</v>
+        <v>221063</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>425596</v>
+        <v>425719</v>
       </c>
       <c r="R54" t="n">
-        <v>7049885</v>
+        <v>7050208</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På basen av gammal levande gran i gammal fuktig granskog i sluttning</t>
+          <t>På marken i källflöde i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6136,10 +6136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129629022</v>
+        <v>129628966</v>
       </c>
       <c r="B55" t="n">
-        <v>79076</v>
+        <v>80182</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6147,21 +6147,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>425345</v>
+        <v>425256</v>
       </c>
       <c r="R55" t="n">
-        <v>7049779</v>
+        <v>7049723</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal gles granskog</t>
+          <t>På bark på stam av levande gammal glasbjörk i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6238,45 +6238,56 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129628975</v>
+        <v>129627360</v>
       </c>
       <c r="B56" t="n">
-        <v>79076</v>
+        <v>79235</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>425609</v>
+        <v>425573</v>
       </c>
       <c r="R56" t="n">
-        <v>7050175</v>
+        <v>7049926</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6313,7 +6324,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal granskog</t>
+          <t>långt ner på gammal gran, fuktigt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6322,28 +6333,29 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129629026</v>
+        <v>129628974</v>
       </c>
       <c r="B57" t="n">
-        <v>83037</v>
+        <v>83050</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6351,21 +6363,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>308</v>
+        <v>1467</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6375,10 +6387,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>425717</v>
+        <v>425457</v>
       </c>
       <c r="R57" t="n">
-        <v>7050119</v>
+        <v>7049826</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6415,7 +6427,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På ved i hålighet vid basen av gammal död gran, även gulnål</t>
+          <t>På bark vid basen av gammal levande gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6442,10 +6454,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129629008</v>
+        <v>129629026</v>
       </c>
       <c r="B58" t="n">
-        <v>79157</v>
+        <v>83037</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6453,21 +6465,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6477,10 +6489,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>425267</v>
+        <v>425717</v>
       </c>
       <c r="R58" t="n">
-        <v>7049748</v>
+        <v>7050119</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6517,7 +6529,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På tunna kvistar på levande klen gammal gran i gammal granskog</t>
+          <t>På ved i hålighet vid basen av gammal död gran, även gulnål</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6544,10 +6556,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129628966</v>
+        <v>129629008</v>
       </c>
       <c r="B59" t="n">
-        <v>80182</v>
+        <v>79157</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6555,21 +6567,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6579,10 +6591,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>425256</v>
+        <v>425267</v>
       </c>
       <c r="R59" t="n">
-        <v>7049723</v>
+        <v>7049748</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6619,7 +6631,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal glasbjörk i gammal granskog</t>
+          <t>På tunna kvistar på levande klen gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6646,56 +6658,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129627360</v>
+        <v>129629022</v>
       </c>
       <c r="B60" t="n">
-        <v>79235</v>
+        <v>79076</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>425573</v>
+        <v>425345</v>
       </c>
       <c r="R60" t="n">
-        <v>7049926</v>
+        <v>7049779</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6732,7 +6733,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>långt ner på gammal gran, fuktigt</t>
+          <t>På gammal gran i gammal gles granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6741,29 +6742,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129628974</v>
+        <v>129628975</v>
       </c>
       <c r="B61" t="n">
-        <v>83050</v>
+        <v>79076</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6771,21 +6771,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6795,10 +6795,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>425457</v>
+        <v>425609</v>
       </c>
       <c r="R61" t="n">
-        <v>7049826</v>
+        <v>7050175</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran</t>
+          <t>på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7979,32 +7979,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129628993</v>
+        <v>129627371</v>
       </c>
       <c r="B73" t="n">
-        <v>79547</v>
+        <v>78436</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1797</v>
+        <v>498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>425721</v>
+        <v>425692</v>
       </c>
       <c r="R73" t="n">
-        <v>7050017</v>
+        <v>7050251</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran vid ett rikkärr</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8069,68 +8069,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129627364</v>
+        <v>129628993</v>
       </c>
       <c r="B74" t="n">
-        <v>79235</v>
+        <v>79547</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1249</v>
+        <v>1797</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>425392</v>
+        <v>425721</v>
       </c>
       <c r="R74" t="n">
-        <v>7049820</v>
+        <v>7050017</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8167,7 +8156,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8176,64 +8165,74 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129628959</v>
+        <v>129627364</v>
       </c>
       <c r="B75" t="n">
-        <v>92306</v>
+        <v>79235</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3298</v>
+        <v>1249</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>425626</v>
+        <v>425392</v>
       </c>
       <c r="R75" t="n">
-        <v>7050243</v>
+        <v>7049820</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8270,7 +8269,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8279,50 +8278,51 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129627371</v>
+        <v>129628959</v>
       </c>
       <c r="B76" t="n">
-        <v>78436</v>
+        <v>92306</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>498</v>
+        <v>3298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>425692</v>
+        <v>425626</v>
       </c>
       <c r="R76" t="n">
-        <v>7050251</v>
+        <v>7050243</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På gammal gran vid ett rikkärr</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8387,12 +8387,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -10453,10 +10453,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129627343</v>
+        <v>129629033</v>
       </c>
       <c r="B97" t="n">
-        <v>57736</v>
+        <v>78089</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10464,42 +10464,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>425384</v>
+        <v>425685</v>
       </c>
       <c r="R97" t="n">
-        <v>7049814</v>
+        <v>7050259</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10536,7 +10528,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>ringhack på gran</t>
+          <t>på gammal levande gran i gammal granskog vid rikkärr vid sjö</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10551,22 +10543,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129629033</v>
+        <v>129628953</v>
       </c>
       <c r="B98" t="n">
-        <v>78089</v>
+        <v>83045</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10574,21 +10566,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10598,10 +10590,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>425685</v>
+        <v>425660</v>
       </c>
       <c r="R98" t="n">
-        <v>7050259</v>
+        <v>7050271</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10638,7 +10630,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>på gammal levande gran i gammal granskog vid rikkärr vid sjö</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10665,32 +10657,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129628953</v>
+        <v>129629029</v>
       </c>
       <c r="B99" t="n">
-        <v>83045</v>
+        <v>83028</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10700,10 +10692,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>425660</v>
+        <v>425332</v>
       </c>
       <c r="R99" t="n">
-        <v>7050271</v>
+        <v>7049768</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10740,7 +10732,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På bark på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10767,45 +10759,53 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129629029</v>
+        <v>129627343</v>
       </c>
       <c r="B100" t="n">
-        <v>83028</v>
+        <v>57736</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>425332</v>
+        <v>425384</v>
       </c>
       <c r="R100" t="n">
-        <v>7049768</v>
+        <v>7049814</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>På bark på björkhögstubbe i gammal granskog</t>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10857,44 +10857,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129627392</v>
+        <v>129628958</v>
       </c>
       <c r="B101" t="n">
-        <v>75181</v>
+        <v>91588</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1776</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10904,10 +10904,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>425617</v>
+        <v>425674</v>
       </c>
       <c r="R101" t="n">
-        <v>7049900</v>
+        <v>7049982</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10959,44 +10959,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129628958</v>
+        <v>129627392</v>
       </c>
       <c r="B102" t="n">
-        <v>91588</v>
+        <v>75181</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>1776</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11006,10 +11006,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>425674</v>
+        <v>425617</v>
       </c>
       <c r="R102" t="n">
-        <v>7049982</v>
+        <v>7049900</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11046,7 +11046,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11061,12 +11061,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -11778,10 +11778,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129633458</v>
+        <v>129633408</v>
       </c>
       <c r="B110" t="n">
-        <v>91584</v>
+        <v>57736</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11789,21 +11789,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11813,10 +11813,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>425678</v>
+        <v>425784</v>
       </c>
       <c r="R110" t="n">
-        <v>7050015</v>
+        <v>7050165</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11849,6 +11849,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11875,7 +11880,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129633408</v>
+        <v>129633411</v>
       </c>
       <c r="B111" t="n">
         <v>57736</v>
@@ -11910,10 +11915,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>425784</v>
+        <v>425573</v>
       </c>
       <c r="R111" t="n">
-        <v>7050165</v>
+        <v>7050194</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11977,7 +11982,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129633411</v>
+        <v>129633442</v>
       </c>
       <c r="B112" t="n">
         <v>57736</v>
@@ -12012,10 +12017,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>425573</v>
+        <v>425406</v>
       </c>
       <c r="R112" t="n">
-        <v>7050194</v>
+        <v>7050149</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12079,7 +12084,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129633442</v>
+        <v>129633424</v>
       </c>
       <c r="B113" t="n">
         <v>57736</v>
@@ -12114,10 +12119,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>425406</v>
+        <v>425413</v>
       </c>
       <c r="R113" t="n">
-        <v>7050149</v>
+        <v>7049880</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12181,10 +12186,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129633424</v>
+        <v>129633458</v>
       </c>
       <c r="B114" t="n">
-        <v>57736</v>
+        <v>91584</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12192,21 +12197,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12216,10 +12221,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>425413</v>
+        <v>425678</v>
       </c>
       <c r="R114" t="n">
-        <v>7049880</v>
+        <v>7050015</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12252,11 +12257,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13664,32 +13664,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129633385</v>
+        <v>129633404</v>
       </c>
       <c r="B129" t="n">
-        <v>92306</v>
+        <v>57736</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13699,10 +13699,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>425773</v>
+        <v>425682</v>
       </c>
       <c r="R129" t="n">
-        <v>7050160</v>
+        <v>7050073</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13735,6 +13735,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13761,7 +13766,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129633404</v>
+        <v>129633439</v>
       </c>
       <c r="B130" t="n">
         <v>57736</v>
@@ -13796,10 +13801,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>425682</v>
+        <v>425357</v>
       </c>
       <c r="R130" t="n">
-        <v>7050073</v>
+        <v>7050155</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13863,7 +13868,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129633439</v>
+        <v>129633447</v>
       </c>
       <c r="B131" t="n">
         <v>57736</v>
@@ -13898,10 +13903,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>425357</v>
+        <v>425526</v>
       </c>
       <c r="R131" t="n">
-        <v>7050155</v>
+        <v>7050117</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13965,7 +13970,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129633447</v>
+        <v>129633413</v>
       </c>
       <c r="B132" t="n">
         <v>57736</v>
@@ -14000,10 +14005,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>425526</v>
+        <v>425870</v>
       </c>
       <c r="R132" t="n">
-        <v>7050117</v>
+        <v>7050230</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14067,32 +14072,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129633413</v>
+        <v>129633385</v>
       </c>
       <c r="B133" t="n">
-        <v>57736</v>
+        <v>92306</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14102,10 +14107,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>425870</v>
+        <v>425773</v>
       </c>
       <c r="R133" t="n">
-        <v>7050230</v>
+        <v>7050160</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14138,11 +14143,6 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14664,10 +14664,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129633394</v>
+        <v>129627372</v>
       </c>
       <c r="B139" t="n">
-        <v>92306</v>
+        <v>95426</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14675,34 +14675,38 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3298</v>
+        <v>2412</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Stor-grässjön s, Jmt</t>
+          <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>425325</v>
+        <v>425708</v>
       </c>
       <c r="R139" t="n">
-        <v>7049857</v>
+        <v>7050205</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14737,31 +14741,37 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>på marken i kärr</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129633386</v>
+        <v>129633394</v>
       </c>
       <c r="B140" t="n">
         <v>92306</v>
@@ -14796,10 +14806,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>425587</v>
+        <v>425325</v>
       </c>
       <c r="R140" t="n">
-        <v>7050138</v>
+        <v>7049857</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14858,32 +14868,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129633421</v>
+        <v>129633386</v>
       </c>
       <c r="B141" t="n">
-        <v>57736</v>
+        <v>92306</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14893,10 +14903,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>425262</v>
+        <v>425587</v>
       </c>
       <c r="R141" t="n">
-        <v>7049782</v>
+        <v>7050138</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14929,11 +14939,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14960,7 +14965,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129633415</v>
+        <v>129633421</v>
       </c>
       <c r="B142" t="n">
         <v>57736</v>
@@ -14995,10 +15000,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>426074</v>
+        <v>425262</v>
       </c>
       <c r="R142" t="n">
-        <v>7050193</v>
+        <v>7049782</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15035,7 +15040,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15062,7 +15067,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129633416</v>
+        <v>129633415</v>
       </c>
       <c r="B143" t="n">
         <v>57736</v>
@@ -15097,10 +15102,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>425828</v>
+        <v>426074</v>
       </c>
       <c r="R143" t="n">
-        <v>7050054</v>
+        <v>7050193</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15137,7 +15142,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15164,7 +15169,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129633436</v>
+        <v>129633416</v>
       </c>
       <c r="B144" t="n">
         <v>57736</v>
@@ -15199,10 +15204,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>425329</v>
+        <v>425828</v>
       </c>
       <c r="R144" t="n">
-        <v>7050182</v>
+        <v>7050054</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15239,7 +15244,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15266,49 +15271,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129627372</v>
+        <v>129633436</v>
       </c>
       <c r="B145" t="n">
-        <v>95426</v>
+        <v>57736</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2412</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
+          <t>Stor-grässjön s, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>425708</v>
+        <v>425329</v>
       </c>
       <c r="R145" t="n">
-        <v>7050205</v>
+        <v>7050182</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15345,7 +15346,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>på marken i kärr</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15354,19 +15355,18 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
@@ -17544,10 +17544,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129633473</v>
+        <v>129633453</v>
       </c>
       <c r="B168" t="n">
-        <v>91584</v>
+        <v>57733</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17555,21 +17555,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17579,10 +17579,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>425218</v>
+        <v>426018</v>
       </c>
       <c r="R168" t="n">
-        <v>7049873</v>
+        <v>7050201</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17615,6 +17615,11 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17641,10 +17646,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129633484</v>
+        <v>129633473</v>
       </c>
       <c r="B169" t="n">
-        <v>88987</v>
+        <v>91584</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17652,21 +17657,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17676,10 +17681,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>425629</v>
+        <v>425218</v>
       </c>
       <c r="R169" t="n">
-        <v>7050220</v>
+        <v>7049873</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17738,10 +17743,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129633414</v>
+        <v>129633484</v>
       </c>
       <c r="B170" t="n">
-        <v>57736</v>
+        <v>88987</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17749,21 +17754,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17773,10 +17778,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>426002</v>
+        <v>425629</v>
       </c>
       <c r="R170" t="n">
-        <v>7050197</v>
+        <v>7050220</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17809,11 +17814,6 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17840,7 +17840,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129633451</v>
+        <v>129633414</v>
       </c>
       <c r="B171" t="n">
         <v>57736</v>
@@ -17875,10 +17875,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>425266</v>
+        <v>426002</v>
       </c>
       <c r="R171" t="n">
-        <v>7049914</v>
+        <v>7050197</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17915,7 +17915,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -17942,10 +17942,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129633453</v>
+        <v>129633451</v>
       </c>
       <c r="B172" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17953,16 +17953,16 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -17977,10 +17977,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>426018</v>
+        <v>425266</v>
       </c>
       <c r="R172" t="n">
-        <v>7050201</v>
+        <v>7049914</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19554,32 +19554,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129633474</v>
+        <v>129633391</v>
       </c>
       <c r="B188" t="n">
-        <v>91602</v>
+        <v>92306</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19589,10 +19589,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>425916</v>
+        <v>426028</v>
       </c>
       <c r="R188" t="n">
-        <v>7050154</v>
+        <v>7050169</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19651,10 +19651,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129633433</v>
+        <v>129633485</v>
       </c>
       <c r="B189" t="n">
-        <v>57736</v>
+        <v>88987</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19662,21 +19662,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19686,10 +19686,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>425345</v>
+        <v>425211</v>
       </c>
       <c r="R189" t="n">
-        <v>7050197</v>
+        <v>7049786</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19722,11 +19722,6 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -19753,10 +19748,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129633401</v>
+        <v>129633467</v>
       </c>
       <c r="B190" t="n">
-        <v>57736</v>
+        <v>91584</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19764,21 +19759,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19788,10 +19783,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>425620</v>
+        <v>425215</v>
       </c>
       <c r="R190" t="n">
-        <v>7049978</v>
+        <v>7049827</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19824,11 +19819,6 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -19855,10 +19845,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129633418</v>
+        <v>129633482</v>
       </c>
       <c r="B191" t="n">
-        <v>57736</v>
+        <v>88987</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19866,21 +19856,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19890,10 +19880,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>425785</v>
+        <v>425677</v>
       </c>
       <c r="R191" t="n">
-        <v>7050033</v>
+        <v>7050049</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19926,11 +19916,6 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -19957,10 +19942,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129633432</v>
+        <v>129633474</v>
       </c>
       <c r="B192" t="n">
-        <v>57736</v>
+        <v>91602</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19968,21 +19953,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19992,10 +19977,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>425434</v>
+        <v>425916</v>
       </c>
       <c r="R192" t="n">
-        <v>7050220</v>
+        <v>7050154</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20028,11 +20013,6 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20059,7 +20039,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129633422</v>
+        <v>129633433</v>
       </c>
       <c r="B193" t="n">
         <v>57736</v>
@@ -20094,10 +20074,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>425222</v>
+        <v>425345</v>
       </c>
       <c r="R193" t="n">
-        <v>7049839</v>
+        <v>7050197</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20161,32 +20141,32 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129633391</v>
+        <v>129633401</v>
       </c>
       <c r="B194" t="n">
-        <v>92306</v>
+        <v>57736</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20196,10 +20176,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>426028</v>
+        <v>425620</v>
       </c>
       <c r="R194" t="n">
-        <v>7050169</v>
+        <v>7049978</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20232,6 +20212,11 @@
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20258,10 +20243,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129633485</v>
+        <v>129633418</v>
       </c>
       <c r="B195" t="n">
-        <v>88987</v>
+        <v>57736</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20269,21 +20254,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20293,10 +20278,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>425211</v>
+        <v>425785</v>
       </c>
       <c r="R195" t="n">
-        <v>7049786</v>
+        <v>7050033</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20329,6 +20314,11 @@
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20355,10 +20345,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129633467</v>
+        <v>129633432</v>
       </c>
       <c r="B196" t="n">
-        <v>91584</v>
+        <v>57736</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20366,21 +20356,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20390,10 +20380,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>425215</v>
+        <v>425434</v>
       </c>
       <c r="R196" t="n">
-        <v>7049827</v>
+        <v>7050220</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20426,6 +20416,11 @@
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20452,10 +20447,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129633482</v>
+        <v>129633422</v>
       </c>
       <c r="B197" t="n">
-        <v>88987</v>
+        <v>57736</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20463,21 +20458,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20487,10 +20482,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>425677</v>
+        <v>425222</v>
       </c>
       <c r="R197" t="n">
-        <v>7050049</v>
+        <v>7049839</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20523,6 +20518,11 @@
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20549,32 +20549,32 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129633475</v>
+        <v>129633470</v>
       </c>
       <c r="B198" t="n">
-        <v>91961</v>
+        <v>91584</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>2063</v>
+        <v>1108</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20584,10 +20584,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>425690</v>
+        <v>425383</v>
       </c>
       <c r="R198" t="n">
-        <v>7050235</v>
+        <v>7050135</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20646,7 +20646,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129633470</v>
+        <v>129633462</v>
       </c>
       <c r="B199" t="n">
         <v>91584</v>
@@ -20681,10 +20681,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>425383</v>
+        <v>425779</v>
       </c>
       <c r="R199" t="n">
-        <v>7050135</v>
+        <v>7050242</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20743,10 +20743,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129633462</v>
+        <v>129633400</v>
       </c>
       <c r="B200" t="n">
-        <v>91584</v>
+        <v>57736</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20754,21 +20754,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20778,10 +20778,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>425779</v>
+        <v>425596</v>
       </c>
       <c r="R200" t="n">
-        <v>7050242</v>
+        <v>7049933</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20814,6 +20814,11 @@
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -20840,7 +20845,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129633400</v>
+        <v>129633409</v>
       </c>
       <c r="B201" t="n">
         <v>57736</v>
@@ -20875,10 +20880,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>425596</v>
+        <v>425616</v>
       </c>
       <c r="R201" t="n">
-        <v>7049933</v>
+        <v>7050151</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20915,7 +20920,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -20942,7 +20947,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129633409</v>
+        <v>129633437</v>
       </c>
       <c r="B202" t="n">
         <v>57736</v>
@@ -20977,10 +20982,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>425616</v>
+        <v>425347</v>
       </c>
       <c r="R202" t="n">
-        <v>7050151</v>
+        <v>7050132</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21017,7 +21022,7 @@
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21044,32 +21049,32 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129633437</v>
+        <v>129633475</v>
       </c>
       <c r="B203" t="n">
-        <v>57736</v>
+        <v>91961</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -21079,10 +21084,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>425347</v>
+        <v>425690</v>
       </c>
       <c r="R203" t="n">
-        <v>7050132</v>
+        <v>7050235</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21115,11 +21120,6 @@
       <c r="AA203" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21549,32 +21549,32 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129672492</v>
+        <v>129672509</v>
       </c>
       <c r="B208" t="n">
-        <v>79235</v>
+        <v>80182</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1249</v>
+        <v>2081</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -21584,10 +21584,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>425710</v>
+        <v>425350</v>
       </c>
       <c r="R208" t="n">
-        <v>7050058</v>
+        <v>7049796</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21630,6 +21630,21 @@
       </c>
       <c r="AG208" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO208" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
@@ -21646,32 +21661,32 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129672510</v>
+        <v>129672492</v>
       </c>
       <c r="B209" t="n">
-        <v>80181</v>
+        <v>79235</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -21681,10 +21696,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>425350</v>
+        <v>425710</v>
       </c>
       <c r="R209" t="n">
-        <v>7049796</v>
+        <v>7050058</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21727,21 +21742,6 @@
       </c>
       <c r="AG209" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ209" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK209" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO209" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
@@ -21758,10 +21758,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129672503</v>
+        <v>129672510</v>
       </c>
       <c r="B210" t="n">
-        <v>83045</v>
+        <v>80181</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21769,21 +21769,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21793,10 +21793,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>425559</v>
+        <v>425350</v>
       </c>
       <c r="R210" t="n">
-        <v>7049854</v>
+        <v>7049796</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21839,6 +21839,21 @@
       </c>
       <c r="AG210" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO210" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
@@ -21855,10 +21870,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129672509</v>
+        <v>129672503</v>
       </c>
       <c r="B211" t="n">
-        <v>80182</v>
+        <v>83045</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21866,21 +21881,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21890,10 +21905,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>425350</v>
+        <v>425559</v>
       </c>
       <c r="R211" t="n">
-        <v>7049796</v>
+        <v>7049854</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21936,21 +21951,6 @@
       </c>
       <c r="AG211" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ211" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK211" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO211" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
@@ -21967,32 +21967,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129672514</v>
+        <v>129672472</v>
       </c>
       <c r="B212" t="n">
-        <v>83045</v>
+        <v>75181</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6440</v>
+        <v>1776</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22002,10 +22002,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>425292</v>
+        <v>425341</v>
       </c>
       <c r="R212" t="n">
-        <v>7049741</v>
+        <v>7049761</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22048,6 +22048,21 @@
       </c>
       <c r="AG212" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO212" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
@@ -22064,7 +22079,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129672499</v>
+        <v>129672514</v>
       </c>
       <c r="B213" t="n">
         <v>83045</v>
@@ -22099,10 +22114,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>425535</v>
+        <v>425292</v>
       </c>
       <c r="R213" t="n">
-        <v>7049926</v>
+        <v>7049741</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22161,32 +22176,32 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129672486</v>
+        <v>129672499</v>
       </c>
       <c r="B214" t="n">
-        <v>95995</v>
+        <v>83045</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22196,10 +22211,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>425724</v>
+        <v>425535</v>
       </c>
       <c r="R214" t="n">
-        <v>7050188</v>
+        <v>7049926</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22258,32 +22273,32 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129672472</v>
+        <v>129672486</v>
       </c>
       <c r="B215" t="n">
-        <v>75181</v>
+        <v>95995</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1776</v>
+        <v>2809</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -22293,10 +22308,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>425341</v>
+        <v>425724</v>
       </c>
       <c r="R215" t="n">
-        <v>7049761</v>
+        <v>7050188</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22339,21 +22354,6 @@
       </c>
       <c r="AG215" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ215" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK215" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO215" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
@@ -23161,32 +23161,32 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129672505</v>
+        <v>129672480</v>
       </c>
       <c r="B224" t="n">
-        <v>78089</v>
+        <v>75060</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>228579</v>
+        <v>6428</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -23196,10 +23196,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>425524</v>
+        <v>425403</v>
       </c>
       <c r="R224" t="n">
-        <v>7049845</v>
+        <v>7049803</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23245,7 +23245,7 @@
       </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>barken på gammal gran</t>
+          <t>Grankvist</t>
         </is>
       </c>
       <c r="AT224" t="inlineStr"/>
@@ -23263,10 +23263,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129672483</v>
+        <v>129672467</v>
       </c>
       <c r="B225" t="n">
-        <v>95995</v>
+        <v>79332</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23274,21 +23274,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>2809</v>
+        <v>6459</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23298,10 +23298,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>425601</v>
+        <v>425491</v>
       </c>
       <c r="R225" t="n">
-        <v>7050195</v>
+        <v>7049816</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23360,32 +23360,32 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129672484</v>
+        <v>129672449</v>
       </c>
       <c r="B226" t="n">
-        <v>78100</v>
+        <v>75060</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>314</v>
+        <v>6428</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23395,10 +23395,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>425661</v>
+        <v>425715</v>
       </c>
       <c r="R226" t="n">
-        <v>7050268</v>
+        <v>7050177</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23457,10 +23457,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129672480</v>
+        <v>129672483</v>
       </c>
       <c r="B227" t="n">
-        <v>75060</v>
+        <v>95995</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23468,21 +23468,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6428</v>
+        <v>2809</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23492,10 +23492,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>425403</v>
+        <v>425601</v>
       </c>
       <c r="R227" t="n">
-        <v>7049803</v>
+        <v>7050195</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23538,11 +23538,6 @@
       </c>
       <c r="AG227" t="b">
         <v>0</v>
-      </c>
-      <c r="AO227" t="inlineStr">
-        <is>
-          <t>Grankvist</t>
-        </is>
       </c>
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
@@ -23559,32 +23554,32 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129672467</v>
+        <v>129672505</v>
       </c>
       <c r="B228" t="n">
-        <v>79332</v>
+        <v>78089</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6459</v>
+        <v>228579</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23594,10 +23589,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>425491</v>
+        <v>425524</v>
       </c>
       <c r="R228" t="n">
-        <v>7049816</v>
+        <v>7049845</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23640,6 +23635,11 @@
       </c>
       <c r="AG228" t="b">
         <v>0</v>
+      </c>
+      <c r="AO228" t="inlineStr">
+        <is>
+          <t>barken på gammal gran</t>
+        </is>
       </c>
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
@@ -23656,32 +23656,32 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129672449</v>
+        <v>129672484</v>
       </c>
       <c r="B229" t="n">
-        <v>75060</v>
+        <v>78100</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6428</v>
+        <v>314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23691,10 +23691,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>425715</v>
+        <v>425661</v>
       </c>
       <c r="R229" t="n">
-        <v>7050177</v>
+        <v>7050268</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24621,32 +24621,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129672495</v>
+        <v>129672460</v>
       </c>
       <c r="B239" t="n">
-        <v>79547</v>
+        <v>95995</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>1797</v>
+        <v>2809</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24656,10 +24656,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>425655</v>
+        <v>425706</v>
       </c>
       <c r="R239" t="n">
-        <v>7049983</v>
+        <v>7050014</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24718,32 +24718,32 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129672460</v>
+        <v>129672495</v>
       </c>
       <c r="B240" t="n">
-        <v>95995</v>
+        <v>79547</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>2809</v>
+        <v>1797</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -24753,10 +24753,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>425706</v>
+        <v>425655</v>
       </c>
       <c r="R240" t="n">
-        <v>7050014</v>
+        <v>7049983</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25203,32 +25203,32 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>129672489</v>
+        <v>129672444</v>
       </c>
       <c r="B245" t="n">
-        <v>79076</v>
+        <v>75181</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6425</v>
+        <v>1776</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25238,10 +25238,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>425717</v>
+        <v>425652</v>
       </c>
       <c r="R245" t="n">
-        <v>7050159</v>
+        <v>7050265</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25300,32 +25300,32 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>129672444</v>
+        <v>129672469</v>
       </c>
       <c r="B246" t="n">
-        <v>75181</v>
+        <v>79547</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1776</v>
+        <v>1797</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -25335,10 +25335,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>425652</v>
+        <v>425359</v>
       </c>
       <c r="R246" t="n">
-        <v>7050265</v>
+        <v>7049806</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25397,10 +25397,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>129672469</v>
+        <v>129672489</v>
       </c>
       <c r="B247" t="n">
-        <v>79547</v>
+        <v>79076</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25408,21 +25408,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>1797</v>
+        <v>6425</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -25432,10 +25432,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>425359</v>
+        <v>425717</v>
       </c>
       <c r="R247" t="n">
-        <v>7049806</v>
+        <v>7050159</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25883,32 +25883,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>129672451</v>
+        <v>129672507</v>
       </c>
       <c r="B252" t="n">
-        <v>92543</v>
+        <v>79157</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>4769</v>
+        <v>283</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25918,10 +25918,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>425710</v>
+        <v>425450</v>
       </c>
       <c r="R252" t="n">
-        <v>7050150</v>
+        <v>7049825</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25980,7 +25980,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>129672507</v>
+        <v>129672506</v>
       </c>
       <c r="B253" t="n">
         <v>79157</v>
@@ -26015,10 +26015,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>425450</v>
+        <v>425480</v>
       </c>
       <c r="R253" t="n">
-        <v>7049825</v>
+        <v>7049813</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26077,32 +26077,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>129672506</v>
+        <v>129672451</v>
       </c>
       <c r="B254" t="n">
-        <v>79157</v>
+        <v>92543</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>283</v>
+        <v>4769</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26112,10 +26112,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>425480</v>
+        <v>425710</v>
       </c>
       <c r="R254" t="n">
-        <v>7049813</v>
+        <v>7050150</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>

--- a/artfynd/A 47880-2025 artfynd.xlsx
+++ b/artfynd/A 47880-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129629020</v>
+        <v>129627353</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,45 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>425596</v>
+        <v>425377</v>
       </c>
       <c r="R2" t="n">
-        <v>7049885</v>
+        <v>7049766</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>250 bålar på gammal levande gran i gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,29 +759,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129628949</v>
+        <v>129628994</v>
       </c>
       <c r="B3" t="n">
-        <v>78105</v>
+        <v>79552</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>314</v>
+        <v>1797</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>425719</v>
+        <v>425704</v>
       </c>
       <c r="R3" t="n">
-        <v>7050208</v>
+        <v>7050007</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran vid källflöde i gammal granskog, även trådfräken</t>
+          <t>På bark vid basen av gammal död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129627353</v>
+        <v>129628981</v>
       </c>
       <c r="B4" t="n">
-        <v>80187</v>
+        <v>79240</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -926,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>425377</v>
+        <v>425716</v>
       </c>
       <c r="R4" t="n">
-        <v>7049766</v>
+        <v>7050121</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>2 stora bålar på gammal levande gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129628994</v>
+        <v>129629020</v>
       </c>
       <c r="B5" t="n">
-        <v>79552</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,34 +992,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1797</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>425704</v>
+        <v>425596</v>
       </c>
       <c r="R5" t="n">
-        <v>7050007</v>
+        <v>7049885</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,7 +1067,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal död gran i gammal granskog</t>
+          <t>250 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1077,6 +1076,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1095,32 +1095,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129628981</v>
+        <v>129628949</v>
       </c>
       <c r="B6" t="n">
-        <v>79240</v>
+        <v>78105</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1249</v>
+        <v>314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>425716</v>
+        <v>425719</v>
       </c>
       <c r="R6" t="n">
-        <v>7050121</v>
+        <v>7050208</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2 stora bålar på gammal levande gran</t>
+          <t>På bark på undersidan av död gren på gammal levande gran vid källflöde i gammal granskog, även trådfräken</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1299,56 +1299,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129627355</v>
+        <v>129628961</v>
       </c>
       <c r="B8" t="n">
-        <v>79240</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1249</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>425715</v>
+        <v>425479</v>
       </c>
       <c r="R8" t="n">
-        <v>7050107</v>
+        <v>7049837</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,57 +1372,61 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gammal levande gran i gammal granskog, även på rötter</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129627341</v>
+        <v>129627370</v>
       </c>
       <c r="B9" t="n">
-        <v>92317</v>
+        <v>78094</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1436,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>425495</v>
+        <v>425453</v>
       </c>
       <c r="R9" t="n">
-        <v>7049796</v>
+        <v>7049864</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,6 +1472,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,41 +1503,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129627377</v>
+        <v>129627355</v>
       </c>
       <c r="B10" t="n">
-        <v>91619</v>
+        <v>79240</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1249</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>425701</v>
+        <v>425715</v>
       </c>
       <c r="R10" t="n">
-        <v>7050250</v>
+        <v>7050107</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,17 +1587,13 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På granhögstubbe</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1603,32 +1612,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129628961</v>
+        <v>129627341</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>92317</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1647,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>425479</v>
+        <v>425495</v>
       </c>
       <c r="R11" t="n">
-        <v>7049837</v>
+        <v>7049796</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1676,11 +1685,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gammal levande gran i gammal granskog, även på rötter</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1693,22 +1697,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129627370</v>
+        <v>129627377</v>
       </c>
       <c r="B12" t="n">
-        <v>78094</v>
+        <v>91619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,23 +1720,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>425453</v>
+        <v>425701</v>
       </c>
       <c r="R12" t="n">
-        <v>7049864</v>
+        <v>7050250</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>På granhögstubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,32 +1807,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129629034</v>
+        <v>129627351</v>
       </c>
       <c r="B13" t="n">
-        <v>75186</v>
+        <v>80187</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1776</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>425685</v>
+        <v>425338</v>
       </c>
       <c r="R13" t="n">
-        <v>7050259</v>
+        <v>7049778</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran i gammal granskog vid rikkärr vid sjö, även liten svartspik</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1897,68 +1897,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129627356</v>
+        <v>129628995</v>
       </c>
       <c r="B14" t="n">
-        <v>79240</v>
+        <v>79552</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1249</v>
+        <v>1797</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>425723</v>
+        <v>425662</v>
       </c>
       <c r="R14" t="n">
-        <v>7050083</v>
+        <v>7049950</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1993,57 +1982,61 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt på bark på stam av levande gammal gran vid källflöde i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129628957</v>
+        <v>129628977</v>
       </c>
       <c r="B15" t="n">
-        <v>91599</v>
+        <v>75065</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6428</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2053,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>425661</v>
+        <v>425488</v>
       </c>
       <c r="R15" t="n">
-        <v>7049950</v>
+        <v>7049835</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2093,7 +2086,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På bark vid basen av gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2120,32 +2113,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129628977</v>
+        <v>129629034</v>
       </c>
       <c r="B16" t="n">
-        <v>75065</v>
+        <v>75186</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6428</v>
+        <v>1776</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2155,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>425488</v>
+        <v>425685</v>
       </c>
       <c r="R16" t="n">
-        <v>7049835</v>
+        <v>7050259</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2195,7 +2188,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran i gammal granskog</t>
+          <t>På döda grenar på gammal levande gran i gammal granskog vid rikkärr vid sjö, även liten svartspik</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2222,45 +2215,56 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129627351</v>
+        <v>129627356</v>
       </c>
       <c r="B17" t="n">
-        <v>80187</v>
+        <v>79240</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>425338</v>
+        <v>425723</v>
       </c>
       <c r="R17" t="n">
-        <v>7049778</v>
+        <v>7050083</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2295,17 +2299,13 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129628995</v>
+        <v>129628957</v>
       </c>
       <c r="B18" t="n">
-        <v>79552</v>
+        <v>91599</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1797</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>425662</v>
+        <v>425661</v>
       </c>
       <c r="R18" t="n">
         <v>7049950</v>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran vid källflöde i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2426,32 +2426,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129628984</v>
+        <v>129628992</v>
       </c>
       <c r="B19" t="n">
-        <v>80214</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>425327</v>
+        <v>425721</v>
       </c>
       <c r="R19" t="n">
-        <v>7049709</v>
+        <v>7050017</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>20 bålar på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2528,10 +2528,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129627375</v>
+        <v>129628954</v>
       </c>
       <c r="B20" t="n">
-        <v>91595</v>
+        <v>83052</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2539,21 +2539,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>425697</v>
+        <v>425469</v>
       </c>
       <c r="R20" t="n">
-        <v>7050004</v>
+        <v>7049817</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2618,22 +2618,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129628997</v>
+        <v>129627375</v>
       </c>
       <c r="B21" t="n">
-        <v>79552</v>
+        <v>91595</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1797</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>425393</v>
+        <v>425697</v>
       </c>
       <c r="R21" t="n">
-        <v>7049812</v>
+        <v>7050004</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2720,68 +2720,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129627361</v>
+        <v>129628997</v>
       </c>
       <c r="B22" t="n">
-        <v>79240</v>
+        <v>79552</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1249</v>
+        <v>1797</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>425570</v>
+        <v>425393</v>
       </c>
       <c r="R22" t="n">
-        <v>7049933</v>
+        <v>7049812</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2818,7 +2807,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2827,64 +2816,74 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129627369</v>
+        <v>129627361</v>
       </c>
       <c r="B23" t="n">
-        <v>79552</v>
+        <v>79240</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1797</v>
+        <v>1249</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>425420</v>
+        <v>425570</v>
       </c>
       <c r="R23" t="n">
-        <v>7049825</v>
+        <v>7049933</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2930,6 +2929,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2948,10 +2948,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129629009</v>
+        <v>129627369</v>
       </c>
       <c r="B24" t="n">
-        <v>91595</v>
+        <v>79552</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>1797</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>425707</v>
+        <v>425420</v>
       </c>
       <c r="R24" t="n">
-        <v>7050031</v>
+        <v>7049825</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3038,22 +3038,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129628992</v>
+        <v>129629009</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3061,21 +3061,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>425721</v>
+        <v>425707</v>
       </c>
       <c r="R25" t="n">
-        <v>7050017</v>
+        <v>7050031</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>20 bålar på gammal gran i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3152,32 +3152,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129628954</v>
+        <v>129628984</v>
       </c>
       <c r="B26" t="n">
-        <v>83052</v>
+        <v>80214</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>425469</v>
+        <v>425327</v>
       </c>
       <c r="R26" t="n">
-        <v>7049817</v>
+        <v>7049709</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3254,27 +3254,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129629028</v>
+        <v>129629010</v>
       </c>
       <c r="B27" t="n">
-        <v>83047</v>
+        <v>83050</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>310</v>
+        <v>6486</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>425332</v>
+        <v>425698</v>
       </c>
       <c r="R27" t="n">
-        <v>7049768</v>
+        <v>7049997</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark på björkhögstubbe i gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal levande grov gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3356,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129629010</v>
+        <v>129627363</v>
       </c>
       <c r="B28" t="n">
-        <v>83050</v>
+        <v>79240</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,34 +3367,45 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6486</v>
+        <v>1249</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Nádv.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>425698</v>
+        <v>425428</v>
       </c>
       <c r="R28" t="n">
-        <v>7049997</v>
+        <v>7049830</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3431,7 +3442,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande grov gran i gammal fuktig granskog</t>
+          <t>vid västsluttning och vattenkälla</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3440,71 +3451,61 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129627363</v>
+        <v>129627342</v>
       </c>
       <c r="B29" t="n">
-        <v>79240</v>
+        <v>92317</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1249</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>425428</v>
+        <v>425473</v>
       </c>
       <c r="R29" t="n">
         <v>7049830</v>
@@ -3544,7 +3545,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>vid västsluttning och vattenkälla</t>
+          <t>på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3572,32 +3573,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129627342</v>
+        <v>129628988</v>
       </c>
       <c r="B30" t="n">
-        <v>92317</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3607,10 +3608,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>425473</v>
+        <v>425724</v>
       </c>
       <c r="R30" t="n">
-        <v>7049830</v>
+        <v>7050035</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3656,51 +3657,50 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129628988</v>
+        <v>129629025</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>83035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>425724</v>
+        <v>425717</v>
       </c>
       <c r="R31" t="n">
-        <v>7050035</v>
+        <v>7050119</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>på gran i gammal granskog</t>
+          <t>På ved i hålighet vid basen av gammal död gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3777,32 +3777,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129629025</v>
+        <v>129629028</v>
       </c>
       <c r="B32" t="n">
-        <v>83035</v>
+        <v>83047</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6439</v>
+        <v>310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3812,10 +3812,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>425717</v>
+        <v>425332</v>
       </c>
       <c r="R32" t="n">
-        <v>7050119</v>
+        <v>7049768</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På ved i hålighet vid basen av gammal död gran</t>
+          <t>På bark på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5004,10 +5004,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129627378</v>
+        <v>129627374</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>79162</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5015,21 +5015,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>425710</v>
+        <v>425431</v>
       </c>
       <c r="R44" t="n">
-        <v>7050152</v>
+        <v>7049839</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>150 bålar</t>
+          <t>på tunna kvistar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5106,7 +5106,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129627374</v>
+        <v>129629007</v>
       </c>
       <c r="B45" t="n">
         <v>79162</v>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>425431</v>
+        <v>425720</v>
       </c>
       <c r="R45" t="n">
-        <v>7049839</v>
+        <v>7050011</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>på tunna kvistar</t>
+          <t>På tunna kvistar på gammal levande senvuxen undertryckt gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5196,22 +5196,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129629007</v>
+        <v>129627345</v>
       </c>
       <c r="B46" t="n">
-        <v>79162</v>
+        <v>57896</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5219,34 +5219,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>283</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>425720</v>
+        <v>425507</v>
       </c>
       <c r="R46" t="n">
-        <v>7050011</v>
+        <v>7049861</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5281,11 +5289,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På tunna kvistar på gammal levande senvuxen undertryckt gran i gammal fuktig granskog</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5298,22 +5301,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129627345</v>
+        <v>129629014</v>
       </c>
       <c r="B47" t="n">
-        <v>57896</v>
+        <v>91595</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5321,42 +5324,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>425507</v>
+        <v>425660</v>
       </c>
       <c r="R47" t="n">
-        <v>7049861</v>
+        <v>7049963</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5391,6 +5386,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På gammal levande gran i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5403,22 +5403,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129629014</v>
+        <v>129629011</v>
       </c>
       <c r="B48" t="n">
-        <v>91595</v>
+        <v>79552</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5426,21 +5426,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>1797</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5450,10 +5450,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>425660</v>
+        <v>425698</v>
       </c>
       <c r="R48" t="n">
-        <v>7049963</v>
+        <v>7049997</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5517,45 +5517,56 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129629011</v>
+        <v>129627354</v>
       </c>
       <c r="B49" t="n">
-        <v>79552</v>
+        <v>79240</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1797</v>
+        <v>1249</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>425698</v>
+        <v>425716</v>
       </c>
       <c r="R49" t="n">
-        <v>7049997</v>
+        <v>7050148</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5590,85 +5601,70 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>på bark på stam av levande gammal gran i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129627354</v>
+        <v>129627338</v>
       </c>
       <c r="B50" t="n">
-        <v>79240</v>
+        <v>92317</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1249</v>
+        <v>3298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>425716</v>
+        <v>425585</v>
       </c>
       <c r="R50" t="n">
-        <v>7050148</v>
+        <v>7050170</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5703,13 +5699,17 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På granstubbe</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5728,32 +5728,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129627338</v>
+        <v>129627378</v>
       </c>
       <c r="B51" t="n">
-        <v>92317</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5763,10 +5763,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>425585</v>
+        <v>425710</v>
       </c>
       <c r="R51" t="n">
-        <v>7050170</v>
+        <v>7050152</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>150 bålar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6136,10 +6136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129628966</v>
+        <v>129629026</v>
       </c>
       <c r="B55" t="n">
-        <v>80187</v>
+        <v>83044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6147,21 +6147,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>425256</v>
+        <v>425717</v>
       </c>
       <c r="R55" t="n">
-        <v>7049723</v>
+        <v>7050119</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal glasbjörk i gammal granskog</t>
+          <t>På ved i hålighet vid basen av gammal död gran, även gulnål</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6238,56 +6238,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129627360</v>
+        <v>129629008</v>
       </c>
       <c r="B56" t="n">
-        <v>79240</v>
+        <v>79162</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>425573</v>
+        <v>425267</v>
       </c>
       <c r="R56" t="n">
-        <v>7049926</v>
+        <v>7049748</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6324,7 +6313,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>långt ner på gammal gran, fuktigt</t>
+          <t>På tunna kvistar på levande klen gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6333,29 +6322,28 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129628974</v>
+        <v>129628966</v>
       </c>
       <c r="B57" t="n">
-        <v>83057</v>
+        <v>80187</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6363,21 +6351,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6387,10 +6375,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>425457</v>
+        <v>425256</v>
       </c>
       <c r="R57" t="n">
-        <v>7049826</v>
+        <v>7049723</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6427,7 +6415,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran</t>
+          <t>På bark på stam av levande gammal glasbjörk i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6454,45 +6442,56 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129629022</v>
+        <v>129627360</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>79240</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>425345</v>
+        <v>425573</v>
       </c>
       <c r="R58" t="n">
-        <v>7049779</v>
+        <v>7049926</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6529,7 +6528,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal gles granskog</t>
+          <t>långt ner på gammal gran, fuktigt</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6538,28 +6537,29 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129628975</v>
+        <v>129628974</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>83057</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6567,21 +6567,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6591,10 +6591,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>425609</v>
+        <v>425457</v>
       </c>
       <c r="R59" t="n">
-        <v>7050175</v>
+        <v>7049826</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal granskog</t>
+          <t>På bark vid basen av gammal levande gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6658,10 +6658,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129629026</v>
+        <v>129629022</v>
       </c>
       <c r="B60" t="n">
-        <v>83044</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6669,21 +6669,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>425717</v>
+        <v>425345</v>
       </c>
       <c r="R60" t="n">
-        <v>7050119</v>
+        <v>7049779</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På ved i hålighet vid basen av gammal död gran, även gulnål</t>
+          <t>På gammal gran i gammal gles granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6760,10 +6760,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129629008</v>
+        <v>129628975</v>
       </c>
       <c r="B61" t="n">
-        <v>79162</v>
+        <v>79081</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6771,21 +6771,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6795,10 +6795,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>425267</v>
+        <v>425609</v>
       </c>
       <c r="R61" t="n">
-        <v>7049748</v>
+        <v>7050175</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På tunna kvistar på levande klen gammal gran i gammal granskog</t>
+          <t>på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6862,10 +6862,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129628987</v>
+        <v>129628955</v>
       </c>
       <c r="B62" t="n">
-        <v>83047</v>
+        <v>78094</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6873,21 +6873,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>310</v>
+        <v>228579</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6897,10 +6897,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>425242</v>
+        <v>425268</v>
       </c>
       <c r="R62" t="n">
-        <v>7049734</v>
+        <v>7049748</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6964,10 +6964,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129629027</v>
+        <v>129628987</v>
       </c>
       <c r="B63" t="n">
-        <v>83044</v>
+        <v>83047</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6975,21 +6975,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6999,10 +6999,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>425717</v>
+        <v>425242</v>
       </c>
       <c r="R63" t="n">
-        <v>7050114</v>
+        <v>7049734</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På ved på grov gammal naturlig granstubbe i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7066,10 +7066,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129628955</v>
+        <v>129629027</v>
       </c>
       <c r="B64" t="n">
-        <v>78094</v>
+        <v>83044</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7077,21 +7077,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228579</v>
+        <v>308</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7101,10 +7101,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>425268</v>
+        <v>425717</v>
       </c>
       <c r="R64" t="n">
-        <v>7049748</v>
+        <v>7050114</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På ved på grov gammal naturlig granstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8501,45 +8501,56 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129627376</v>
+        <v>129627358</v>
       </c>
       <c r="B78" t="n">
-        <v>91595</v>
+        <v>79240</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1108</v>
+        <v>1249</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>425618</v>
+        <v>425715</v>
       </c>
       <c r="R78" t="n">
-        <v>7049908</v>
+        <v>7050016</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8576,7 +8587,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>på gran</t>
+          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8585,6 +8596,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8603,7 +8615,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129629015</v>
+        <v>129627376</v>
       </c>
       <c r="B79" t="n">
         <v>91595</v>
@@ -8638,10 +8650,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>425619</v>
+        <v>425618</v>
       </c>
       <c r="R79" t="n">
-        <v>7050217</v>
+        <v>7049908</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8678,7 +8690,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På död gammal gran i gammal granskog</t>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8693,68 +8705,57 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129627358</v>
+        <v>129629015</v>
       </c>
       <c r="B80" t="n">
-        <v>79240</v>
+        <v>91595</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1249</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>425715</v>
+        <v>425619</v>
       </c>
       <c r="R80" t="n">
-        <v>7050016</v>
+        <v>7050217</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8791,7 +8792,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>På död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8800,19 +8801,18 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -8921,45 +8921,56 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129627339</v>
+        <v>129627357</v>
       </c>
       <c r="B82" t="n">
-        <v>92317</v>
+        <v>79240</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3298</v>
+        <v>1249</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>425702</v>
+        <v>425721</v>
       </c>
       <c r="R82" t="n">
-        <v>7050007</v>
+        <v>7050057</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8994,12 +9005,18 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>på gammal gran</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9018,56 +9035,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129627357</v>
+        <v>129627339</v>
       </c>
       <c r="B83" t="n">
-        <v>79240</v>
+        <v>92317</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1249</v>
+        <v>3298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>425721</v>
+        <v>425702</v>
       </c>
       <c r="R83" t="n">
-        <v>7050057</v>
+        <v>7050007</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9102,18 +9108,12 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>på gammal gran</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9637,10 +9637,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129629005</v>
+        <v>129628978</v>
       </c>
       <c r="B89" t="n">
-        <v>79162</v>
+        <v>79081</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9648,21 +9648,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>425718</v>
+        <v>425716</v>
       </c>
       <c r="R89" t="n">
-        <v>7050118</v>
+        <v>7050121</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På senvuxen undertryckt klen gran i gammal granskog</t>
+          <t>på gammal levande gran</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9739,10 +9739,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129628986</v>
+        <v>129627381</v>
       </c>
       <c r="B90" t="n">
-        <v>83047</v>
+        <v>82918</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9750,21 +9750,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>310</v>
+        <v>1312</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9774,10 +9774,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>425529</v>
+        <v>425617</v>
       </c>
       <c r="R90" t="n">
-        <v>7049841</v>
+        <v>7049903</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal sälg i gammal granskog</t>
+          <t>Tillsammans med gammelgranslav</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9829,22 +9829,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129629024</v>
+        <v>129629005</v>
       </c>
       <c r="B91" t="n">
-        <v>83044</v>
+        <v>79162</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9852,21 +9852,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9876,10 +9876,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>425699</v>
+        <v>425718</v>
       </c>
       <c r="R91" t="n">
-        <v>7050143</v>
+        <v>7050118</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På senvuxen undertryckt klen gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9943,10 +9943,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129627373</v>
+        <v>129628986</v>
       </c>
       <c r="B92" t="n">
-        <v>79162</v>
+        <v>83047</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9954,21 +9954,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>283</v>
+        <v>310</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9978,10 +9978,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>425608</v>
+        <v>425529</v>
       </c>
       <c r="R92" t="n">
-        <v>7049894</v>
+        <v>7049841</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>på tunna kvistar</t>
+          <t>På bark på stam av död gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10033,22 +10033,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129627381</v>
+        <v>129629024</v>
       </c>
       <c r="B93" t="n">
-        <v>82918</v>
+        <v>83044</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10056,21 +10056,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10080,10 +10080,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>425617</v>
+        <v>425699</v>
       </c>
       <c r="R93" t="n">
-        <v>7049903</v>
+        <v>7050143</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Tillsammans med gammelgranslav</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10135,22 +10135,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129628978</v>
+        <v>129627373</v>
       </c>
       <c r="B94" t="n">
-        <v>79081</v>
+        <v>79162</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10158,21 +10158,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10182,10 +10182,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>425716</v>
+        <v>425608</v>
       </c>
       <c r="R94" t="n">
-        <v>7050121</v>
+        <v>7049894</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10222,7 +10222,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>på gammal levande gran</t>
+          <t>på tunna kvistar</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10237,12 +10237,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -14664,10 +14664,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129633394</v>
+        <v>129627372</v>
       </c>
       <c r="B139" t="n">
-        <v>92317</v>
+        <v>95437</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14675,34 +14675,38 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3298</v>
+        <v>2412</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Stor-grässjön s, Jmt</t>
+          <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>425325</v>
+        <v>425708</v>
       </c>
       <c r="R139" t="n">
-        <v>7049857</v>
+        <v>7050205</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14737,31 +14741,37 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>på marken i kärr</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129633386</v>
+        <v>129633394</v>
       </c>
       <c r="B140" t="n">
         <v>92317</v>
@@ -14796,10 +14806,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>425587</v>
+        <v>425325</v>
       </c>
       <c r="R140" t="n">
-        <v>7050138</v>
+        <v>7049857</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14858,32 +14868,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129633421</v>
+        <v>129633386</v>
       </c>
       <c r="B141" t="n">
-        <v>57736</v>
+        <v>92317</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14893,10 +14903,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>425262</v>
+        <v>425587</v>
       </c>
       <c r="R141" t="n">
-        <v>7049782</v>
+        <v>7050138</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14929,11 +14939,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14960,7 +14965,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129633415</v>
+        <v>129633421</v>
       </c>
       <c r="B142" t="n">
         <v>57736</v>
@@ -14995,10 +15000,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>426074</v>
+        <v>425262</v>
       </c>
       <c r="R142" t="n">
-        <v>7050193</v>
+        <v>7049782</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15035,7 +15040,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15062,7 +15067,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129633416</v>
+        <v>129633415</v>
       </c>
       <c r="B143" t="n">
         <v>57736</v>
@@ -15097,10 +15102,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>425828</v>
+        <v>426074</v>
       </c>
       <c r="R143" t="n">
-        <v>7050054</v>
+        <v>7050193</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15137,7 +15142,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15164,7 +15169,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129633436</v>
+        <v>129633416</v>
       </c>
       <c r="B144" t="n">
         <v>57736</v>
@@ -15199,10 +15204,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>425329</v>
+        <v>425828</v>
       </c>
       <c r="R144" t="n">
-        <v>7050182</v>
+        <v>7050054</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15239,7 +15244,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15266,49 +15271,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129627372</v>
+        <v>129633436</v>
       </c>
       <c r="B145" t="n">
-        <v>95437</v>
+        <v>57736</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2412</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
+          <t>Stor-grässjön s, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>425708</v>
+        <v>425329</v>
       </c>
       <c r="R145" t="n">
-        <v>7050205</v>
+        <v>7050182</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15345,7 +15346,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>på marken i kärr</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15354,51 +15355,50 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129633429</v>
+        <v>129633457</v>
       </c>
       <c r="B146" t="n">
-        <v>57736</v>
+        <v>79240</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100109</v>
+        <v>1249</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15408,10 +15408,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>425508</v>
+        <v>425579</v>
       </c>
       <c r="R146" t="n">
-        <v>7050208</v>
+        <v>7049866</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15444,11 +15444,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15475,32 +15470,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129633449</v>
+        <v>129633396</v>
       </c>
       <c r="B147" t="n">
-        <v>57736</v>
+        <v>92317</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15510,10 +15505,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>425515</v>
+        <v>425537</v>
       </c>
       <c r="R147" t="n">
-        <v>7050097</v>
+        <v>7050007</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15546,11 +15541,6 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15577,32 +15567,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129633457</v>
+        <v>129633483</v>
       </c>
       <c r="B148" t="n">
-        <v>79240</v>
+        <v>88998</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1249</v>
+        <v>510</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15612,10 +15602,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>425579</v>
+        <v>425789</v>
       </c>
       <c r="R148" t="n">
-        <v>7049866</v>
+        <v>7050109</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15674,32 +15664,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129633396</v>
+        <v>129633429</v>
       </c>
       <c r="B149" t="n">
-        <v>92317</v>
+        <v>57736</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15709,10 +15699,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>425537</v>
+        <v>425508</v>
       </c>
       <c r="R149" t="n">
-        <v>7050007</v>
+        <v>7050208</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15745,6 +15735,11 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15771,10 +15766,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129633483</v>
+        <v>129633449</v>
       </c>
       <c r="B150" t="n">
-        <v>88998</v>
+        <v>57736</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15782,21 +15777,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15806,10 +15801,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>425789</v>
+        <v>425515</v>
       </c>
       <c r="R150" t="n">
-        <v>7050109</v>
+        <v>7050097</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15842,6 +15837,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15868,30 +15868,34 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129633481</v>
+        <v>129633393</v>
       </c>
       <c r="B151" t="n">
-        <v>91619</v>
+        <v>92317</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
@@ -15899,10 +15903,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>425411</v>
+        <v>425772</v>
       </c>
       <c r="R151" t="n">
-        <v>7050144</v>
+        <v>7050008</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15961,34 +15965,30 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129633393</v>
+        <v>129633481</v>
       </c>
       <c r="B152" t="n">
-        <v>92317</v>
+        <v>91619</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
@@ -15996,10 +15996,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>425772</v>
+        <v>425411</v>
       </c>
       <c r="R152" t="n">
-        <v>7050008</v>
+        <v>7050144</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -21146,10 +21146,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129633469</v>
+        <v>129633434</v>
       </c>
       <c r="B204" t="n">
-        <v>91595</v>
+        <v>57736</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21157,21 +21157,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -21181,10 +21181,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>425533</v>
+        <v>425344</v>
       </c>
       <c r="R204" t="n">
-        <v>7050194</v>
+        <v>7050202</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21217,6 +21217,11 @@
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21243,7 +21248,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129633434</v>
+        <v>129633431</v>
       </c>
       <c r="B205" t="n">
         <v>57736</v>
@@ -21278,10 +21283,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>425344</v>
+        <v>425451</v>
       </c>
       <c r="R205" t="n">
-        <v>7050202</v>
+        <v>7050183</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21345,7 +21350,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129633431</v>
+        <v>129633452</v>
       </c>
       <c r="B206" t="n">
         <v>57736</v>
@@ -21380,10 +21385,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>425451</v>
+        <v>425230</v>
       </c>
       <c r="R206" t="n">
-        <v>7050183</v>
+        <v>7049882</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21420,7 +21425,7 @@
       </c>
       <c r="AC206" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -21447,10 +21452,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129633452</v>
+        <v>129633469</v>
       </c>
       <c r="B207" t="n">
-        <v>57736</v>
+        <v>91595</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21458,21 +21463,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -21482,10 +21487,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>425230</v>
+        <v>425533</v>
       </c>
       <c r="R207" t="n">
-        <v>7049882</v>
+        <v>7050194</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21518,11 +21523,6 @@
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23258,10 +23258,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129672480</v>
+        <v>129672483</v>
       </c>
       <c r="B225" t="n">
-        <v>75065</v>
+        <v>96006</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23269,21 +23269,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6428</v>
+        <v>2809</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23293,10 +23293,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>425403</v>
+        <v>425601</v>
       </c>
       <c r="R225" t="n">
-        <v>7049803</v>
+        <v>7050195</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23339,11 +23339,6 @@
       </c>
       <c r="AG225" t="b">
         <v>0</v>
-      </c>
-      <c r="AO225" t="inlineStr">
-        <is>
-          <t>Grankvist</t>
-        </is>
       </c>
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
@@ -23360,10 +23355,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129672467</v>
+        <v>129672480</v>
       </c>
       <c r="B226" t="n">
-        <v>79337</v>
+        <v>75065</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23371,21 +23366,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6459</v>
+        <v>6428</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23395,10 +23390,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>425491</v>
+        <v>425403</v>
       </c>
       <c r="R226" t="n">
-        <v>7049816</v>
+        <v>7049803</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23441,6 +23436,11 @@
       </c>
       <c r="AG226" t="b">
         <v>0</v>
+      </c>
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t>Grankvist</t>
+        </is>
       </c>
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
@@ -23457,10 +23457,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129672449</v>
+        <v>129672467</v>
       </c>
       <c r="B227" t="n">
-        <v>75065</v>
+        <v>79337</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23468,21 +23468,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6428</v>
+        <v>6459</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23492,10 +23492,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>425715</v>
+        <v>425491</v>
       </c>
       <c r="R227" t="n">
-        <v>7050177</v>
+        <v>7049816</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23554,32 +23554,32 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129672505</v>
+        <v>129672449</v>
       </c>
       <c r="B228" t="n">
-        <v>78094</v>
+        <v>75065</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>228579</v>
+        <v>6428</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23589,10 +23589,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>425524</v>
+        <v>425715</v>
       </c>
       <c r="R228" t="n">
-        <v>7049845</v>
+        <v>7050177</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23635,11 +23635,6 @@
       </c>
       <c r="AG228" t="b">
         <v>0</v>
-      </c>
-      <c r="AO228" t="inlineStr">
-        <is>
-          <t>barken på gammal gran</t>
-        </is>
       </c>
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
@@ -23656,32 +23651,32 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129672483</v>
+        <v>129672505</v>
       </c>
       <c r="B229" t="n">
-        <v>96006</v>
+        <v>78094</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>2809</v>
+        <v>228579</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23691,10 +23686,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>425601</v>
+        <v>425524</v>
       </c>
       <c r="R229" t="n">
-        <v>7050195</v>
+        <v>7049845</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23737,6 +23732,11 @@
       </c>
       <c r="AG229" t="b">
         <v>0</v>
+      </c>
+      <c r="AO229" t="inlineStr">
+        <is>
+          <t>barken på gammal gran</t>
+        </is>
       </c>
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
@@ -26271,32 +26271,32 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>129672491</v>
+        <v>129672466</v>
       </c>
       <c r="B256" t="n">
-        <v>79337</v>
+        <v>79240</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6459</v>
+        <v>1249</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26306,10 +26306,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>425740</v>
+        <v>425505</v>
       </c>
       <c r="R256" t="n">
-        <v>7050084</v>
+        <v>7049842</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26368,32 +26368,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>129672466</v>
+        <v>129672491</v>
       </c>
       <c r="B257" t="n">
-        <v>79240</v>
+        <v>79337</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>1249</v>
+        <v>6459</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -26403,10 +26403,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>425505</v>
+        <v>425740</v>
       </c>
       <c r="R257" t="n">
-        <v>7049842</v>
+        <v>7050084</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>

--- a/artfynd/A 47880-2025 artfynd.xlsx
+++ b/artfynd/A 47880-2025 artfynd.xlsx
@@ -1299,45 +1299,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129628961</v>
+        <v>129627355</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>79240</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>425479</v>
+        <v>425715</v>
       </c>
       <c r="R8" t="n">
-        <v>7049837</v>
+        <v>7050107</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,61 +1383,57 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gammal levande gran i gammal granskog, även på rötter</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129627370</v>
+        <v>129627341</v>
       </c>
       <c r="B9" t="n">
-        <v>78094</v>
+        <v>92317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1436,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>425453</v>
+        <v>425495</v>
       </c>
       <c r="R9" t="n">
-        <v>7049864</v>
+        <v>7049796</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,11 +1479,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1503,56 +1505,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129627355</v>
+        <v>129627377</v>
       </c>
       <c r="B10" t="n">
-        <v>79240</v>
+        <v>91619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1249</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>425715</v>
+        <v>425701</v>
       </c>
       <c r="R10" t="n">
-        <v>7050107</v>
+        <v>7050250</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,13 +1574,17 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På granhögstubbe</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1612,32 +1603,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129627341</v>
+        <v>129628961</v>
       </c>
       <c r="B11" t="n">
-        <v>92317</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1647,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>425495</v>
+        <v>425479</v>
       </c>
       <c r="R11" t="n">
-        <v>7049796</v>
+        <v>7049837</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1685,6 +1676,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gammal levande gran i gammal granskog, även på rötter</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1697,22 +1693,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129627377</v>
+        <v>129627370</v>
       </c>
       <c r="B12" t="n">
-        <v>91619</v>
+        <v>78094</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1720,19 +1716,23 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>425701</v>
+        <v>425453</v>
       </c>
       <c r="R12" t="n">
-        <v>7050250</v>
+        <v>7049864</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På granhögstubbe</t>
+          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2426,32 +2426,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129628992</v>
+        <v>129628984</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>80214</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>425721</v>
+        <v>425327</v>
       </c>
       <c r="R19" t="n">
-        <v>7050017</v>
+        <v>7049709</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>20 bålar på gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2528,10 +2528,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129628954</v>
+        <v>129627375</v>
       </c>
       <c r="B20" t="n">
-        <v>83052</v>
+        <v>91595</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2539,21 +2539,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>425469</v>
+        <v>425697</v>
       </c>
       <c r="R20" t="n">
-        <v>7049817</v>
+        <v>7050004</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2618,22 +2618,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129627375</v>
+        <v>129628997</v>
       </c>
       <c r="B21" t="n">
-        <v>91595</v>
+        <v>79552</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>1797</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>425697</v>
+        <v>425393</v>
       </c>
       <c r="R21" t="n">
-        <v>7050004</v>
+        <v>7049812</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2720,57 +2720,68 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129628997</v>
+        <v>129627361</v>
       </c>
       <c r="B22" t="n">
-        <v>79552</v>
+        <v>79240</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1797</v>
+        <v>1249</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>425393</v>
+        <v>425570</v>
       </c>
       <c r="R22" t="n">
-        <v>7049812</v>
+        <v>7049933</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2807,7 +2818,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2816,74 +2827,64 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129627361</v>
+        <v>129627369</v>
       </c>
       <c r="B23" t="n">
-        <v>79240</v>
+        <v>79552</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1249</v>
+        <v>1797</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>425570</v>
+        <v>425420</v>
       </c>
       <c r="R23" t="n">
-        <v>7049933</v>
+        <v>7049825</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,7 +2930,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2948,10 +2948,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129627369</v>
+        <v>129629009</v>
       </c>
       <c r="B24" t="n">
-        <v>79552</v>
+        <v>91595</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1797</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>425420</v>
+        <v>425707</v>
       </c>
       <c r="R24" t="n">
-        <v>7049825</v>
+        <v>7050031</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3038,22 +3038,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129629009</v>
+        <v>129628992</v>
       </c>
       <c r="B25" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3061,21 +3061,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>425707</v>
+        <v>425721</v>
       </c>
       <c r="R25" t="n">
-        <v>7050031</v>
+        <v>7050017</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>20 bålar på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3152,32 +3152,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129628984</v>
+        <v>129628954</v>
       </c>
       <c r="B26" t="n">
-        <v>80214</v>
+        <v>83052</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>425327</v>
+        <v>425469</v>
       </c>
       <c r="R26" t="n">
-        <v>7049709</v>
+        <v>7049817</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3254,27 +3254,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129629010</v>
+        <v>129629028</v>
       </c>
       <c r="B27" t="n">
-        <v>83050</v>
+        <v>83047</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6486</v>
+        <v>310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>425698</v>
+        <v>425332</v>
       </c>
       <c r="R27" t="n">
-        <v>7049997</v>
+        <v>7049768</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande grov gran i gammal fuktig granskog</t>
+          <t>På bark på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3356,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129627363</v>
+        <v>129629010</v>
       </c>
       <c r="B28" t="n">
-        <v>79240</v>
+        <v>83050</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,45 +3367,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1249</v>
+        <v>6486</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>425428</v>
+        <v>425698</v>
       </c>
       <c r="R28" t="n">
-        <v>7049830</v>
+        <v>7049997</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3442,7 +3431,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>vid västsluttning och vattenkälla</t>
+          <t>På bark i hålighet vid basen av gammal levande grov gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3451,61 +3440,71 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129627342</v>
+        <v>129627363</v>
       </c>
       <c r="B29" t="n">
-        <v>92317</v>
+        <v>79240</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>1249</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>425473</v>
+        <v>425428</v>
       </c>
       <c r="R29" t="n">
         <v>7049830</v>
@@ -3545,7 +3544,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>på gran i gammal granskog</t>
+          <t>vid västsluttning och vattenkälla</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3573,32 +3572,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129628988</v>
+        <v>129627342</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>92317</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3608,10 +3607,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>425724</v>
+        <v>425473</v>
       </c>
       <c r="R30" t="n">
-        <v>7050035</v>
+        <v>7049830</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3657,50 +3656,51 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129629025</v>
+        <v>129628988</v>
       </c>
       <c r="B31" t="n">
-        <v>83035</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>425717</v>
+        <v>425724</v>
       </c>
       <c r="R31" t="n">
-        <v>7050119</v>
+        <v>7050035</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På ved i hålighet vid basen av gammal död gran</t>
+          <t>på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3777,32 +3777,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129629028</v>
+        <v>129629025</v>
       </c>
       <c r="B32" t="n">
-        <v>83047</v>
+        <v>83035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>310</v>
+        <v>6439</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3812,10 +3812,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>425332</v>
+        <v>425717</v>
       </c>
       <c r="R32" t="n">
-        <v>7049768</v>
+        <v>7050119</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På bark på björkhögstubbe i gammal granskog</t>
+          <t>På ved i hålighet vid basen av gammal död gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5004,10 +5004,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129627374</v>
+        <v>129627378</v>
       </c>
       <c r="B44" t="n">
-        <v>79162</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5015,21 +5015,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>425431</v>
+        <v>425710</v>
       </c>
       <c r="R44" t="n">
-        <v>7049839</v>
+        <v>7050152</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>på tunna kvistar</t>
+          <t>150 bålar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5106,7 +5106,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129629007</v>
+        <v>129627374</v>
       </c>
       <c r="B45" t="n">
         <v>79162</v>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>425720</v>
+        <v>425431</v>
       </c>
       <c r="R45" t="n">
-        <v>7050011</v>
+        <v>7049839</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal levande senvuxen undertryckt gran i gammal fuktig granskog</t>
+          <t>på tunna kvistar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5196,22 +5196,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129627345</v>
+        <v>129629007</v>
       </c>
       <c r="B46" t="n">
-        <v>57896</v>
+        <v>79162</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5219,42 +5219,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>425507</v>
+        <v>425720</v>
       </c>
       <c r="R46" t="n">
-        <v>7049861</v>
+        <v>7050011</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5289,6 +5281,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På tunna kvistar på gammal levande senvuxen undertryckt gran i gammal fuktig granskog</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5301,22 +5298,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129629014</v>
+        <v>129627345</v>
       </c>
       <c r="B47" t="n">
-        <v>91595</v>
+        <v>57896</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5324,34 +5321,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>425660</v>
+        <v>425507</v>
       </c>
       <c r="R47" t="n">
-        <v>7049963</v>
+        <v>7049861</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5386,11 +5391,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På gammal levande gran i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5403,22 +5403,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129629011</v>
+        <v>129629014</v>
       </c>
       <c r="B48" t="n">
-        <v>79552</v>
+        <v>91595</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5426,21 +5426,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1797</v>
+        <v>1108</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5450,10 +5450,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>425698</v>
+        <v>425660</v>
       </c>
       <c r="R48" t="n">
-        <v>7049997</v>
+        <v>7049963</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5517,56 +5517,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129627354</v>
+        <v>129629011</v>
       </c>
       <c r="B49" t="n">
-        <v>79240</v>
+        <v>79552</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1249</v>
+        <v>1797</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>425716</v>
+        <v>425698</v>
       </c>
       <c r="R49" t="n">
-        <v>7050148</v>
+        <v>7049997</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5601,70 +5590,85 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>på bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129627338</v>
+        <v>129627354</v>
       </c>
       <c r="B50" t="n">
-        <v>92317</v>
+        <v>79240</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3298</v>
+        <v>1249</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>425585</v>
+        <v>425716</v>
       </c>
       <c r="R50" t="n">
-        <v>7050170</v>
+        <v>7050148</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5699,17 +5703,13 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På granstubbe</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5728,32 +5728,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129627378</v>
+        <v>129627338</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>92317</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5763,10 +5763,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>425710</v>
+        <v>425585</v>
       </c>
       <c r="R51" t="n">
-        <v>7050152</v>
+        <v>7050170</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>150 bålar</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -8501,56 +8501,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129627358</v>
+        <v>129627376</v>
       </c>
       <c r="B78" t="n">
-        <v>79240</v>
+        <v>91595</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1249</v>
+        <v>1108</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>425715</v>
+        <v>425618</v>
       </c>
       <c r="R78" t="n">
-        <v>7050016</v>
+        <v>7049908</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8587,7 +8576,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8596,7 +8585,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8615,7 +8603,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129627376</v>
+        <v>129629015</v>
       </c>
       <c r="B79" t="n">
         <v>91595</v>
@@ -8650,10 +8638,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>425618</v>
+        <v>425619</v>
       </c>
       <c r="R79" t="n">
-        <v>7049908</v>
+        <v>7050217</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8690,7 +8678,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>på gran</t>
+          <t>På död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8705,57 +8693,68 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129629015</v>
+        <v>129627358</v>
       </c>
       <c r="B80" t="n">
-        <v>91595</v>
+        <v>79240</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1108</v>
+        <v>1249</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>425619</v>
+        <v>425715</v>
       </c>
       <c r="R80" t="n">
-        <v>7050217</v>
+        <v>7050016</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8792,7 +8791,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På död gammal gran i gammal granskog</t>
+          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8801,18 +8800,19 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -8921,56 +8921,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129627357</v>
+        <v>129627339</v>
       </c>
       <c r="B82" t="n">
-        <v>79240</v>
+        <v>92317</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1249</v>
+        <v>3298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>425721</v>
+        <v>425702</v>
       </c>
       <c r="R82" t="n">
-        <v>7050057</v>
+        <v>7050007</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9005,18 +8994,12 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>på gammal gran</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9035,45 +9018,56 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129627339</v>
+        <v>129627357</v>
       </c>
       <c r="B83" t="n">
-        <v>92317</v>
+        <v>79240</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3298</v>
+        <v>1249</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>425702</v>
+        <v>425721</v>
       </c>
       <c r="R83" t="n">
-        <v>7050007</v>
+        <v>7050057</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9108,12 +9102,18 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>på gammal gran</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10453,10 +10453,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129627343</v>
+        <v>129628953</v>
       </c>
       <c r="B97" t="n">
-        <v>57736</v>
+        <v>83052</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10464,42 +10464,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>425384</v>
+        <v>425660</v>
       </c>
       <c r="R97" t="n">
-        <v>7049814</v>
+        <v>7050271</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10536,7 +10528,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>ringhack på gran</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10551,44 +10543,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129629033</v>
+        <v>129629029</v>
       </c>
       <c r="B98" t="n">
-        <v>78094</v>
+        <v>83035</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228579</v>
+        <v>6439</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10598,10 +10590,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>425685</v>
+        <v>425332</v>
       </c>
       <c r="R98" t="n">
-        <v>7050259</v>
+        <v>7049768</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10638,7 +10630,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>på gammal levande gran i gammal granskog vid rikkärr vid sjö</t>
+          <t>På bark på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10665,10 +10657,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129628953</v>
+        <v>129627343</v>
       </c>
       <c r="B99" t="n">
-        <v>83052</v>
+        <v>57736</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10676,34 +10668,42 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>425660</v>
+        <v>425384</v>
       </c>
       <c r="R99" t="n">
-        <v>7050271</v>
+        <v>7049814</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10755,44 +10755,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129629029</v>
+        <v>129629033</v>
       </c>
       <c r="B100" t="n">
-        <v>83035</v>
+        <v>78094</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6439</v>
+        <v>228579</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10802,10 +10802,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>425332</v>
+        <v>425685</v>
       </c>
       <c r="R100" t="n">
-        <v>7049768</v>
+        <v>7050259</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>På bark på björkhögstubbe i gammal granskog</t>
+          <t>på gammal levande gran i gammal granskog vid rikkärr vid sjö</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12965,7 +12965,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129633445</v>
+        <v>129633444</v>
       </c>
       <c r="B122" t="n">
         <v>57736</v>
@@ -13000,10 +13000,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>425490</v>
+        <v>425419</v>
       </c>
       <c r="R122" t="n">
-        <v>7050129</v>
+        <v>7050137</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13067,7 +13067,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129633444</v>
+        <v>129633435</v>
       </c>
       <c r="B123" t="n">
         <v>57736</v>
@@ -13102,10 +13102,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>425419</v>
+        <v>425324</v>
       </c>
       <c r="R123" t="n">
-        <v>7050137</v>
+        <v>7050192</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13169,7 +13169,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129633435</v>
+        <v>129633445</v>
       </c>
       <c r="B124" t="n">
         <v>57736</v>
@@ -13204,10 +13204,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>425324</v>
+        <v>425490</v>
       </c>
       <c r="R124" t="n">
-        <v>7050192</v>
+        <v>7050129</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13271,32 +13271,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129633460</v>
+        <v>129633389</v>
       </c>
       <c r="B125" t="n">
-        <v>91595</v>
+        <v>92317</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13306,10 +13306,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>425741</v>
+        <v>425870</v>
       </c>
       <c r="R125" t="n">
-        <v>7050015</v>
+        <v>7050232</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13368,10 +13368,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129633459</v>
+        <v>129633420</v>
       </c>
       <c r="B126" t="n">
-        <v>91595</v>
+        <v>57736</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13379,21 +13379,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13403,10 +13403,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>425702</v>
+        <v>425481</v>
       </c>
       <c r="R126" t="n">
-        <v>7050011</v>
+        <v>7049835</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13439,6 +13439,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13465,32 +13470,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129633389</v>
+        <v>129633460</v>
       </c>
       <c r="B127" t="n">
-        <v>92317</v>
+        <v>91595</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13500,10 +13505,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>425870</v>
+        <v>425741</v>
       </c>
       <c r="R127" t="n">
-        <v>7050232</v>
+        <v>7050015</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13562,10 +13567,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129633420</v>
+        <v>129633459</v>
       </c>
       <c r="B128" t="n">
-        <v>57736</v>
+        <v>91595</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13573,21 +13578,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13597,10 +13602,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>425481</v>
+        <v>425702</v>
       </c>
       <c r="R128" t="n">
-        <v>7049835</v>
+        <v>7050011</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13633,11 +13638,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15470,32 +15470,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129633396</v>
+        <v>129633483</v>
       </c>
       <c r="B147" t="n">
-        <v>92317</v>
+        <v>88998</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3298</v>
+        <v>510</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15505,10 +15505,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>425537</v>
+        <v>425789</v>
       </c>
       <c r="R147" t="n">
-        <v>7050007</v>
+        <v>7050109</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15567,10 +15567,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129633483</v>
+        <v>129633429</v>
       </c>
       <c r="B148" t="n">
-        <v>88998</v>
+        <v>57736</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15578,21 +15578,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15602,10 +15602,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>425789</v>
+        <v>425508</v>
       </c>
       <c r="R148" t="n">
-        <v>7050109</v>
+        <v>7050208</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15638,6 +15638,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15664,7 +15669,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129633429</v>
+        <v>129633449</v>
       </c>
       <c r="B149" t="n">
         <v>57736</v>
@@ -15699,10 +15704,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>425508</v>
+        <v>425515</v>
       </c>
       <c r="R149" t="n">
-        <v>7050208</v>
+        <v>7050097</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15766,32 +15771,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129633449</v>
+        <v>129633396</v>
       </c>
       <c r="B150" t="n">
-        <v>57736</v>
+        <v>92317</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15801,10 +15806,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>425515</v>
+        <v>425537</v>
       </c>
       <c r="R150" t="n">
-        <v>7050097</v>
+        <v>7050007</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15837,11 +15842,6 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -19554,10 +19554,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129633474</v>
+        <v>129633485</v>
       </c>
       <c r="B188" t="n">
-        <v>91613</v>
+        <v>88998</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19565,21 +19565,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19589,10 +19589,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>425916</v>
+        <v>425211</v>
       </c>
       <c r="R188" t="n">
-        <v>7050154</v>
+        <v>7049786</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19651,10 +19651,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129633467</v>
+        <v>129633482</v>
       </c>
       <c r="B189" t="n">
-        <v>91595</v>
+        <v>88998</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19662,21 +19662,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19686,10 +19686,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>425215</v>
+        <v>425677</v>
       </c>
       <c r="R189" t="n">
-        <v>7049827</v>
+        <v>7050049</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19748,32 +19748,32 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129633391</v>
+        <v>129633474</v>
       </c>
       <c r="B190" t="n">
-        <v>92317</v>
+        <v>91613</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19783,10 +19783,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>426028</v>
+        <v>425916</v>
       </c>
       <c r="R190" t="n">
-        <v>7050169</v>
+        <v>7050154</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19845,10 +19845,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129633433</v>
+        <v>129633467</v>
       </c>
       <c r="B191" t="n">
-        <v>57736</v>
+        <v>91595</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19856,21 +19856,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19880,10 +19880,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>425345</v>
+        <v>425215</v>
       </c>
       <c r="R191" t="n">
-        <v>7050197</v>
+        <v>7049827</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19916,11 +19916,6 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -19947,32 +19942,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129633401</v>
+        <v>129633391</v>
       </c>
       <c r="B192" t="n">
-        <v>57736</v>
+        <v>92317</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19982,10 +19977,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>425620</v>
+        <v>426028</v>
       </c>
       <c r="R192" t="n">
-        <v>7049978</v>
+        <v>7050169</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20018,11 +20013,6 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20049,7 +20039,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129633418</v>
+        <v>129633433</v>
       </c>
       <c r="B193" t="n">
         <v>57736</v>
@@ -20084,10 +20074,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>425785</v>
+        <v>425345</v>
       </c>
       <c r="R193" t="n">
-        <v>7050033</v>
+        <v>7050197</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20124,7 +20114,7 @@
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20151,7 +20141,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129633432</v>
+        <v>129633401</v>
       </c>
       <c r="B194" t="n">
         <v>57736</v>
@@ -20186,10 +20176,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>425434</v>
+        <v>425620</v>
       </c>
       <c r="R194" t="n">
-        <v>7050220</v>
+        <v>7049978</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20226,7 +20216,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20253,7 +20243,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129633422</v>
+        <v>129633418</v>
       </c>
       <c r="B195" t="n">
         <v>57736</v>
@@ -20288,10 +20278,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>425222</v>
+        <v>425785</v>
       </c>
       <c r="R195" t="n">
-        <v>7049839</v>
+        <v>7050033</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20328,7 +20318,7 @@
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20355,10 +20345,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129633485</v>
+        <v>129633432</v>
       </c>
       <c r="B196" t="n">
-        <v>88998</v>
+        <v>57736</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20366,21 +20356,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20390,10 +20380,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>425211</v>
+        <v>425434</v>
       </c>
       <c r="R196" t="n">
-        <v>7049786</v>
+        <v>7050220</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20426,6 +20416,11 @@
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20452,10 +20447,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129633482</v>
+        <v>129633422</v>
       </c>
       <c r="B197" t="n">
-        <v>88998</v>
+        <v>57736</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20463,21 +20458,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20487,10 +20482,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>425677</v>
+        <v>425222</v>
       </c>
       <c r="R197" t="n">
-        <v>7050049</v>
+        <v>7049839</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20523,6 +20518,11 @@
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -23258,10 +23258,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129672483</v>
+        <v>129672480</v>
       </c>
       <c r="B225" t="n">
-        <v>96006</v>
+        <v>75065</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23269,21 +23269,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>2809</v>
+        <v>6428</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23293,10 +23293,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>425601</v>
+        <v>425403</v>
       </c>
       <c r="R225" t="n">
-        <v>7050195</v>
+        <v>7049803</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23339,6 +23339,11 @@
       </c>
       <c r="AG225" t="b">
         <v>0</v>
+      </c>
+      <c r="AO225" t="inlineStr">
+        <is>
+          <t>Grankvist</t>
+        </is>
       </c>
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
@@ -23355,10 +23360,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129672480</v>
+        <v>129672467</v>
       </c>
       <c r="B226" t="n">
-        <v>75065</v>
+        <v>79337</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23366,21 +23371,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6428</v>
+        <v>6459</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23390,10 +23395,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>425403</v>
+        <v>425491</v>
       </c>
       <c r="R226" t="n">
-        <v>7049803</v>
+        <v>7049816</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23436,11 +23441,6 @@
       </c>
       <c r="AG226" t="b">
         <v>0</v>
-      </c>
-      <c r="AO226" t="inlineStr">
-        <is>
-          <t>Grankvist</t>
-        </is>
       </c>
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
@@ -23457,10 +23457,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129672467</v>
+        <v>129672449</v>
       </c>
       <c r="B227" t="n">
-        <v>79337</v>
+        <v>75065</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23468,21 +23468,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6459</v>
+        <v>6428</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23492,10 +23492,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>425491</v>
+        <v>425715</v>
       </c>
       <c r="R227" t="n">
-        <v>7049816</v>
+        <v>7050177</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23554,32 +23554,32 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129672449</v>
+        <v>129672505</v>
       </c>
       <c r="B228" t="n">
-        <v>75065</v>
+        <v>78094</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6428</v>
+        <v>228579</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23589,10 +23589,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>425715</v>
+        <v>425524</v>
       </c>
       <c r="R228" t="n">
-        <v>7050177</v>
+        <v>7049845</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23635,6 +23635,11 @@
       </c>
       <c r="AG228" t="b">
         <v>0</v>
+      </c>
+      <c r="AO228" t="inlineStr">
+        <is>
+          <t>barken på gammal gran</t>
+        </is>
       </c>
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
@@ -23651,32 +23656,32 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129672505</v>
+        <v>129672483</v>
       </c>
       <c r="B229" t="n">
-        <v>78094</v>
+        <v>96006</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>228579</v>
+        <v>2809</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23686,10 +23691,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>425524</v>
+        <v>425601</v>
       </c>
       <c r="R229" t="n">
-        <v>7049845</v>
+        <v>7050195</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23732,11 +23737,6 @@
       </c>
       <c r="AG229" t="b">
         <v>0</v>
-      </c>
-      <c r="AO229" t="inlineStr">
-        <is>
-          <t>barken på gammal gran</t>
-        </is>
       </c>
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
@@ -26271,32 +26271,32 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>129672466</v>
+        <v>129672491</v>
       </c>
       <c r="B256" t="n">
-        <v>79240</v>
+        <v>79337</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>1249</v>
+        <v>6459</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26306,10 +26306,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>425505</v>
+        <v>425740</v>
       </c>
       <c r="R256" t="n">
-        <v>7049842</v>
+        <v>7050084</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26368,32 +26368,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>129672491</v>
+        <v>129672466</v>
       </c>
       <c r="B257" t="n">
-        <v>79337</v>
+        <v>79240</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6459</v>
+        <v>1249</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -26403,10 +26403,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>425740</v>
+        <v>425505</v>
       </c>
       <c r="R257" t="n">
-        <v>7050084</v>
+        <v>7049842</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>

--- a/artfynd/A 47880-2025 artfynd.xlsx
+++ b/artfynd/A 47880-2025 artfynd.xlsx
@@ -2426,32 +2426,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129628984</v>
+        <v>129628992</v>
       </c>
       <c r="B19" t="n">
-        <v>80214</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>425327</v>
+        <v>425721</v>
       </c>
       <c r="R19" t="n">
-        <v>7049709</v>
+        <v>7050017</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>20 bålar på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2528,10 +2528,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129627375</v>
+        <v>129628954</v>
       </c>
       <c r="B20" t="n">
-        <v>91595</v>
+        <v>83052</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2539,21 +2539,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>425697</v>
+        <v>425469</v>
       </c>
       <c r="R20" t="n">
-        <v>7050004</v>
+        <v>7049817</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2618,22 +2618,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129628997</v>
+        <v>129627375</v>
       </c>
       <c r="B21" t="n">
-        <v>79552</v>
+        <v>91595</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1797</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>425393</v>
+        <v>425697</v>
       </c>
       <c r="R21" t="n">
-        <v>7049812</v>
+        <v>7050004</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2720,68 +2720,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129627361</v>
+        <v>129628997</v>
       </c>
       <c r="B22" t="n">
-        <v>79240</v>
+        <v>79552</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1249</v>
+        <v>1797</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>425570</v>
+        <v>425393</v>
       </c>
       <c r="R22" t="n">
-        <v>7049933</v>
+        <v>7049812</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2818,7 +2807,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2827,64 +2816,74 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129627369</v>
+        <v>129627361</v>
       </c>
       <c r="B23" t="n">
-        <v>79552</v>
+        <v>79240</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1797</v>
+        <v>1249</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>425420</v>
+        <v>425570</v>
       </c>
       <c r="R23" t="n">
-        <v>7049825</v>
+        <v>7049933</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2930,6 +2929,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2948,10 +2948,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129629009</v>
+        <v>129627369</v>
       </c>
       <c r="B24" t="n">
-        <v>91595</v>
+        <v>79552</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>1797</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>425707</v>
+        <v>425420</v>
       </c>
       <c r="R24" t="n">
-        <v>7050031</v>
+        <v>7049825</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3038,22 +3038,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129628992</v>
+        <v>129629009</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3061,21 +3061,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>425721</v>
+        <v>425707</v>
       </c>
       <c r="R25" t="n">
-        <v>7050017</v>
+        <v>7050031</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>20 bålar på gammal gran i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3152,32 +3152,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129628954</v>
+        <v>129628984</v>
       </c>
       <c r="B26" t="n">
-        <v>83052</v>
+        <v>80214</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>425469</v>
+        <v>425327</v>
       </c>
       <c r="R26" t="n">
-        <v>7049817</v>
+        <v>7049709</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -8501,45 +8501,56 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129627376</v>
+        <v>129627358</v>
       </c>
       <c r="B78" t="n">
-        <v>91595</v>
+        <v>79240</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1108</v>
+        <v>1249</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>425618</v>
+        <v>425715</v>
       </c>
       <c r="R78" t="n">
-        <v>7049908</v>
+        <v>7050016</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8576,7 +8587,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>på gran</t>
+          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8585,6 +8596,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8603,7 +8615,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129629015</v>
+        <v>129627376</v>
       </c>
       <c r="B79" t="n">
         <v>91595</v>
@@ -8638,10 +8650,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>425619</v>
+        <v>425618</v>
       </c>
       <c r="R79" t="n">
-        <v>7050217</v>
+        <v>7049908</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8678,7 +8690,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På död gammal gran i gammal granskog</t>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8693,68 +8705,57 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129627358</v>
+        <v>129629015</v>
       </c>
       <c r="B80" t="n">
-        <v>79240</v>
+        <v>91595</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1249</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>425715</v>
+        <v>425619</v>
       </c>
       <c r="R80" t="n">
-        <v>7050016</v>
+        <v>7050217</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8791,7 +8792,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>På död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8800,19 +8801,18 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -8921,45 +8921,56 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129627339</v>
+        <v>129627357</v>
       </c>
       <c r="B82" t="n">
-        <v>92317</v>
+        <v>79240</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3298</v>
+        <v>1249</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>425702</v>
+        <v>425721</v>
       </c>
       <c r="R82" t="n">
-        <v>7050007</v>
+        <v>7050057</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8994,12 +9005,18 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>på gammal gran</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9018,56 +9035,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129627357</v>
+        <v>129627339</v>
       </c>
       <c r="B83" t="n">
-        <v>79240</v>
+        <v>92317</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1249</v>
+        <v>3298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>425721</v>
+        <v>425702</v>
       </c>
       <c r="R83" t="n">
-        <v>7050057</v>
+        <v>7050007</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9102,18 +9108,12 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>på gammal gran</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -15470,32 +15470,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129633483</v>
+        <v>129633396</v>
       </c>
       <c r="B147" t="n">
-        <v>88998</v>
+        <v>92317</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>510</v>
+        <v>3298</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15505,10 +15505,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>425789</v>
+        <v>425537</v>
       </c>
       <c r="R147" t="n">
-        <v>7050109</v>
+        <v>7050007</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15567,10 +15567,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129633429</v>
+        <v>129633483</v>
       </c>
       <c r="B148" t="n">
-        <v>57736</v>
+        <v>88998</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15578,21 +15578,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15602,10 +15602,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>425508</v>
+        <v>425789</v>
       </c>
       <c r="R148" t="n">
-        <v>7050208</v>
+        <v>7050109</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15638,11 +15638,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15669,7 +15664,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129633449</v>
+        <v>129633429</v>
       </c>
       <c r="B149" t="n">
         <v>57736</v>
@@ -15704,10 +15699,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>425515</v>
+        <v>425508</v>
       </c>
       <c r="R149" t="n">
-        <v>7050097</v>
+        <v>7050208</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15771,32 +15766,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129633396</v>
+        <v>129633449</v>
       </c>
       <c r="B150" t="n">
-        <v>92317</v>
+        <v>57736</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15806,10 +15801,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>425537</v>
+        <v>425515</v>
       </c>
       <c r="R150" t="n">
-        <v>7050007</v>
+        <v>7050097</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15842,6 +15837,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18044,32 +18044,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129633472</v>
+        <v>129633390</v>
       </c>
       <c r="B173" t="n">
-        <v>91595</v>
+        <v>92317</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18079,10 +18079,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>425559</v>
+        <v>426060</v>
       </c>
       <c r="R173" t="n">
-        <v>7050001</v>
+        <v>7050187</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18141,7 +18141,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129633390</v>
+        <v>129633395</v>
       </c>
       <c r="B174" t="n">
         <v>92317</v>
@@ -18176,10 +18176,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>426060</v>
+        <v>425561</v>
       </c>
       <c r="R174" t="n">
-        <v>7050187</v>
+        <v>7050121</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18238,32 +18238,32 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129633395</v>
+        <v>129633425</v>
       </c>
       <c r="B175" t="n">
-        <v>92317</v>
+        <v>57736</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18273,10 +18273,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>425561</v>
+        <v>425535</v>
       </c>
       <c r="R175" t="n">
-        <v>7050121</v>
+        <v>7049914</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18309,6 +18309,11 @@
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18335,7 +18340,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129633425</v>
+        <v>129633412</v>
       </c>
       <c r="B176" t="n">
         <v>57736</v>
@@ -18370,10 +18375,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>425535</v>
+        <v>425867</v>
       </c>
       <c r="R176" t="n">
-        <v>7049914</v>
+        <v>7050236</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18437,10 +18442,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129633412</v>
+        <v>129633472</v>
       </c>
       <c r="B177" t="n">
-        <v>57736</v>
+        <v>91595</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18448,21 +18453,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18472,10 +18477,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>425867</v>
+        <v>425559</v>
       </c>
       <c r="R177" t="n">
-        <v>7050236</v>
+        <v>7050001</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18508,11 +18513,6 @@
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD177" t="b">

--- a/artfynd/A 47880-2025 artfynd.xlsx
+++ b/artfynd/A 47880-2025 artfynd.xlsx
@@ -3357,27 +3357,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129629028</v>
+        <v>129629010</v>
       </c>
       <c r="B28" t="n">
-        <v>83047</v>
+        <v>83050</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>310</v>
+        <v>6486</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>425332</v>
+        <v>425698</v>
       </c>
       <c r="R28" t="n">
-        <v>7049768</v>
+        <v>7049997</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På bark på björkhögstubbe i gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal levande grov gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3561,27 +3561,27 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129629010</v>
+        <v>129629028</v>
       </c>
       <c r="B30" t="n">
-        <v>83050</v>
+        <v>83047</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6486</v>
+        <v>310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3596,10 +3596,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>425698</v>
+        <v>425332</v>
       </c>
       <c r="R30" t="n">
-        <v>7049997</v>
+        <v>7049768</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande grov gran i gammal fuktig granskog</t>
+          <t>På bark på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -5208,32 +5208,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129627338</v>
+        <v>129627378</v>
       </c>
       <c r="B46" t="n">
-        <v>92317</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>425585</v>
+        <v>425710</v>
       </c>
       <c r="R46" t="n">
-        <v>7050170</v>
+        <v>7050152</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>150 bålar</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5310,32 +5310,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129627378</v>
+        <v>129627338</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>92317</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>425710</v>
+        <v>425585</v>
       </c>
       <c r="R47" t="n">
-        <v>7050152</v>
+        <v>7050170</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>150 bålar</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5412,45 +5412,53 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129629035</v>
+        <v>129627345</v>
       </c>
       <c r="B48" t="n">
-        <v>75186</v>
+        <v>57896</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1776</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>425578</v>
+        <v>425507</v>
       </c>
       <c r="R48" t="n">
-        <v>7049878</v>
+        <v>7049861</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5485,11 +5493,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På tunna döda kvistar på ca 200 år gammal gran i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5502,44 +5505,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129629011</v>
+        <v>129629035</v>
       </c>
       <c r="B49" t="n">
-        <v>79552</v>
+        <v>75186</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1797</v>
+        <v>1776</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5549,10 +5552,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>425698</v>
+        <v>425578</v>
       </c>
       <c r="R49" t="n">
-        <v>7049997</v>
+        <v>7049878</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5589,7 +5592,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På tunna döda kvistar på ca 200 år gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5616,56 +5619,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129627354</v>
+        <v>129629011</v>
       </c>
       <c r="B50" t="n">
-        <v>79240</v>
+        <v>79552</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1249</v>
+        <v>1797</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>425716</v>
+        <v>425698</v>
       </c>
       <c r="R50" t="n">
-        <v>7050148</v>
+        <v>7049997</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5700,67 +5692,74 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>på bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129627345</v>
+        <v>129627354</v>
       </c>
       <c r="B51" t="n">
-        <v>57896</v>
+        <v>79240</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>1249</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5768,10 +5767,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>425507</v>
+        <v>425716</v>
       </c>
       <c r="R51" t="n">
-        <v>7049861</v>
+        <v>7050148</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5812,6 +5811,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6136,10 +6136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129629026</v>
+        <v>129628966</v>
       </c>
       <c r="B55" t="n">
-        <v>83044</v>
+        <v>80187</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6147,21 +6147,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>425717</v>
+        <v>425256</v>
       </c>
       <c r="R55" t="n">
-        <v>7050119</v>
+        <v>7049723</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På ved i hålighet vid basen av gammal död gran, även gulnål</t>
+          <t>På bark på stam av levande gammal glasbjörk i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6238,45 +6238,56 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129629008</v>
+        <v>129627360</v>
       </c>
       <c r="B56" t="n">
-        <v>79162</v>
+        <v>79240</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>425267</v>
+        <v>425573</v>
       </c>
       <c r="R56" t="n">
-        <v>7049748</v>
+        <v>7049926</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6313,7 +6324,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På tunna kvistar på levande klen gammal gran i gammal granskog</t>
+          <t>långt ner på gammal gran, fuktigt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6322,28 +6333,29 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129628966</v>
+        <v>129628974</v>
       </c>
       <c r="B57" t="n">
-        <v>80187</v>
+        <v>83057</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6351,21 +6363,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6375,10 +6387,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>425256</v>
+        <v>425457</v>
       </c>
       <c r="R57" t="n">
-        <v>7049723</v>
+        <v>7049826</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6415,7 +6427,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal glasbjörk i gammal granskog</t>
+          <t>På bark vid basen av gammal levande gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6442,56 +6454,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129627360</v>
+        <v>129629026</v>
       </c>
       <c r="B58" t="n">
-        <v>79240</v>
+        <v>83044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1249</v>
+        <v>308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>425573</v>
+        <v>425717</v>
       </c>
       <c r="R58" t="n">
-        <v>7049926</v>
+        <v>7050119</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6528,7 +6529,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>långt ner på gammal gran, fuktigt</t>
+          <t>På ved i hålighet vid basen av gammal död gran, även gulnål</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6537,29 +6538,28 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129628974</v>
+        <v>129629008</v>
       </c>
       <c r="B59" t="n">
-        <v>83057</v>
+        <v>79162</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6567,21 +6567,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1467</v>
+        <v>283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6591,10 +6591,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>425457</v>
+        <v>425267</v>
       </c>
       <c r="R59" t="n">
-        <v>7049826</v>
+        <v>7049748</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran</t>
+          <t>På tunna kvistar på levande klen gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7168,32 +7168,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129627365</v>
+        <v>129629030</v>
       </c>
       <c r="B65" t="n">
-        <v>80214</v>
+        <v>83044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6461</v>
+        <v>308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7203,10 +7203,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>425720</v>
+        <v>425332</v>
       </c>
       <c r="R65" t="n">
-        <v>7050056</v>
+        <v>7049768</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7241,6 +7241,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På ved på björkhögstubbe i gammal granskog, även gulnål och nordlig nållav på barken</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7253,12 +7258,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7571,32 +7576,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129629030</v>
+        <v>129627365</v>
       </c>
       <c r="B69" t="n">
-        <v>83044</v>
+        <v>80214</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>308</v>
+        <v>6461</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7606,10 +7611,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>425332</v>
+        <v>425720</v>
       </c>
       <c r="R69" t="n">
-        <v>7049768</v>
+        <v>7050056</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7644,11 +7649,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På ved på björkhögstubbe i gammal granskog, även gulnål och nordlig nållav på barken</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7661,12 +7661,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8501,10 +8501,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129629021</v>
+        <v>129627376</v>
       </c>
       <c r="B78" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8512,21 +8512,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8536,10 +8536,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>425518</v>
+        <v>425618</v>
       </c>
       <c r="R78" t="n">
-        <v>7049851</v>
+        <v>7049908</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8591,44 +8591,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129628976</v>
+        <v>129629015</v>
       </c>
       <c r="B79" t="n">
-        <v>75065</v>
+        <v>91595</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6428</v>
+        <v>1108</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8638,10 +8638,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>425609</v>
+        <v>425619</v>
       </c>
       <c r="R79" t="n">
-        <v>7050175</v>
+        <v>7050217</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På grankvist I gammal granskog</t>
+          <t>På död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8705,56 +8705,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129627358</v>
+        <v>129627339</v>
       </c>
       <c r="B80" t="n">
-        <v>79240</v>
+        <v>92317</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1249</v>
+        <v>3298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>425715</v>
+        <v>425702</v>
       </c>
       <c r="R80" t="n">
-        <v>7050016</v>
+        <v>7050007</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8789,18 +8778,12 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>på gammal gran</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8819,32 +8802,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129627380</v>
+        <v>129627349</v>
       </c>
       <c r="B81" t="n">
-        <v>82918</v>
+        <v>80215</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8854,10 +8837,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>425713</v>
+        <v>425382</v>
       </c>
       <c r="R81" t="n">
-        <v>7050121</v>
+        <v>7049760</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8894,7 +8877,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8921,56 +8904,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129627357</v>
+        <v>129627366</v>
       </c>
       <c r="B82" t="n">
-        <v>79240</v>
+        <v>80214</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1249</v>
+        <v>6461</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>425721</v>
+        <v>425552</v>
       </c>
       <c r="R82" t="n">
-        <v>7050057</v>
+        <v>7049855</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9005,18 +8977,12 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>på gammal gran</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9028,17 +8994,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129627376</v>
+        <v>129629021</v>
       </c>
       <c r="B83" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9046,21 +9012,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9070,10 +9036,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>425618</v>
+        <v>425518</v>
       </c>
       <c r="R83" t="n">
-        <v>7049908</v>
+        <v>7049851</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9110,7 +9076,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>på gran</t>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9125,44 +9091,44 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129629015</v>
+        <v>129628976</v>
       </c>
       <c r="B84" t="n">
-        <v>91595</v>
+        <v>75065</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1108</v>
+        <v>6428</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9172,10 +9138,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>425619</v>
+        <v>425609</v>
       </c>
       <c r="R84" t="n">
-        <v>7050217</v>
+        <v>7050175</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9212,7 +9178,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>På död gammal gran i gammal granskog</t>
+          <t>På grankvist I gammal granskog</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9239,45 +9205,56 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129627339</v>
+        <v>129627358</v>
       </c>
       <c r="B85" t="n">
-        <v>92317</v>
+        <v>79240</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3298</v>
+        <v>1249</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>425702</v>
+        <v>425715</v>
       </c>
       <c r="R85" t="n">
-        <v>7050007</v>
+        <v>7050016</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9312,12 +9289,18 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>på gammal gran</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9336,32 +9319,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129627349</v>
+        <v>129627380</v>
       </c>
       <c r="B86" t="n">
-        <v>80215</v>
+        <v>82918</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9371,10 +9354,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>425382</v>
+        <v>425713</v>
       </c>
       <c r="R86" t="n">
-        <v>7049760</v>
+        <v>7050121</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9411,7 +9394,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9438,45 +9421,56 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129627366</v>
+        <v>129627357</v>
       </c>
       <c r="B87" t="n">
-        <v>80214</v>
+        <v>79240</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6461</v>
+        <v>1249</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>425552</v>
+        <v>425721</v>
       </c>
       <c r="R87" t="n">
-        <v>7049855</v>
+        <v>7050057</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9511,12 +9505,18 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>på gammal gran</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10249,32 +10249,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129628963</v>
+        <v>129628952</v>
       </c>
       <c r="B95" t="n">
-        <v>92554</v>
+        <v>78094</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4769</v>
+        <v>228579</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10284,10 +10284,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>425275</v>
+        <v>425660</v>
       </c>
       <c r="R95" t="n">
-        <v>7049745</v>
+        <v>7050271</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10351,32 +10351,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129628952</v>
+        <v>129628963</v>
       </c>
       <c r="B96" t="n">
-        <v>78094</v>
+        <v>92554</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228579</v>
+        <v>4769</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10386,10 +10386,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>425660</v>
+        <v>425275</v>
       </c>
       <c r="R96" t="n">
-        <v>7050271</v>
+        <v>7049745</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10453,32 +10453,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129629029</v>
+        <v>129629033</v>
       </c>
       <c r="B97" t="n">
-        <v>83035</v>
+        <v>78094</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6439</v>
+        <v>228579</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10488,10 +10488,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>425332</v>
+        <v>425685</v>
       </c>
       <c r="R97" t="n">
-        <v>7049768</v>
+        <v>7050259</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10528,7 +10528,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>På bark på björkhögstubbe i gammal granskog</t>
+          <t>på gammal levande gran i gammal granskog vid rikkärr vid sjö</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10555,32 +10555,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129628953</v>
+        <v>129629029</v>
       </c>
       <c r="B98" t="n">
-        <v>83052</v>
+        <v>83035</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10590,10 +10590,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>425660</v>
+        <v>425332</v>
       </c>
       <c r="R98" t="n">
-        <v>7050271</v>
+        <v>7049768</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10630,7 +10630,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På bark på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10657,10 +10657,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129627343</v>
+        <v>129628953</v>
       </c>
       <c r="B99" t="n">
-        <v>57736</v>
+        <v>83052</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10668,42 +10668,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>425384</v>
+        <v>425660</v>
       </c>
       <c r="R99" t="n">
-        <v>7049814</v>
+        <v>7050271</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10740,7 +10732,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>ringhack på gran</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10755,22 +10747,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129629033</v>
+        <v>129627343</v>
       </c>
       <c r="B100" t="n">
-        <v>78094</v>
+        <v>57736</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10778,34 +10770,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>425685</v>
+        <v>425384</v>
       </c>
       <c r="R100" t="n">
-        <v>7050259</v>
+        <v>7049814</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>på gammal levande gran i gammal granskog vid rikkärr vid sjö</t>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10857,12 +10857,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11175,10 +11175,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129628990</v>
+        <v>129628991</v>
       </c>
       <c r="B104" t="n">
-        <v>78094</v>
+        <v>79552</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11186,21 +11186,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228579</v>
+        <v>1797</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>på gran i gammal granskog</t>
+          <t>På två gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11277,10 +11277,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129629012</v>
+        <v>129627367</v>
       </c>
       <c r="B105" t="n">
-        <v>91595</v>
+        <v>79552</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11288,21 +11288,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1108</v>
+        <v>1797</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11312,10 +11312,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>425698</v>
+        <v>425618</v>
       </c>
       <c r="R105" t="n">
-        <v>7049997</v>
+        <v>7049902</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På död och levande gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11367,22 +11367,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129628991</v>
+        <v>129629012</v>
       </c>
       <c r="B106" t="n">
-        <v>79552</v>
+        <v>91595</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11390,21 +11390,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1797</v>
+        <v>1108</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11414,10 +11414,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>425724</v>
+        <v>425698</v>
       </c>
       <c r="R106" t="n">
-        <v>7050035</v>
+        <v>7049997</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>På två gamla granar i gammal granskog</t>
+          <t>På död och levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11481,10 +11481,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129627367</v>
+        <v>129628990</v>
       </c>
       <c r="B107" t="n">
-        <v>79552</v>
+        <v>78094</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11492,21 +11492,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1797</v>
+        <v>228579</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11516,10 +11516,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>425618</v>
+        <v>425724</v>
       </c>
       <c r="R107" t="n">
-        <v>7049902</v>
+        <v>7050035</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11556,7 +11556,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11571,12 +11571,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -12682,32 +12682,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129633456</v>
+        <v>129633444</v>
       </c>
       <c r="B119" t="n">
-        <v>79240</v>
+        <v>57736</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1249</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12717,10 +12717,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>425675</v>
+        <v>425419</v>
       </c>
       <c r="R119" t="n">
-        <v>7050020</v>
+        <v>7050137</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12753,6 +12753,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12779,7 +12784,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129633444</v>
+        <v>129633435</v>
       </c>
       <c r="B120" t="n">
         <v>57736</v>
@@ -12814,10 +12819,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>425419</v>
+        <v>425324</v>
       </c>
       <c r="R120" t="n">
-        <v>7050137</v>
+        <v>7050192</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12854,7 +12859,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12881,7 +12886,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129633435</v>
+        <v>129633445</v>
       </c>
       <c r="B121" t="n">
         <v>57736</v>
@@ -12916,10 +12921,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>425324</v>
+        <v>425490</v>
       </c>
       <c r="R121" t="n">
-        <v>7050192</v>
+        <v>7050129</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12983,32 +12988,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129633445</v>
+        <v>129633456</v>
       </c>
       <c r="B122" t="n">
-        <v>57736</v>
+        <v>79240</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>1249</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13018,10 +13023,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>425490</v>
+        <v>425675</v>
       </c>
       <c r="R122" t="n">
-        <v>7050129</v>
+        <v>7050020</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13054,11 +13059,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14664,32 +14664,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129633394</v>
+        <v>129633421</v>
       </c>
       <c r="B139" t="n">
-        <v>92317</v>
+        <v>57736</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14699,10 +14699,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>425325</v>
+        <v>425262</v>
       </c>
       <c r="R139" t="n">
-        <v>7049857</v>
+        <v>7049782</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14735,6 +14735,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14761,32 +14766,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129633386</v>
+        <v>129633416</v>
       </c>
       <c r="B140" t="n">
-        <v>92317</v>
+        <v>57736</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14796,10 +14801,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>425587</v>
+        <v>425828</v>
       </c>
       <c r="R140" t="n">
-        <v>7050138</v>
+        <v>7050054</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14832,6 +14837,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14858,49 +14868,45 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129627372</v>
+        <v>129633436</v>
       </c>
       <c r="B141" t="n">
-        <v>95447</v>
+        <v>57736</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2412</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
+          <t>Stor-grässjön s, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>425708</v>
+        <v>425329</v>
       </c>
       <c r="R141" t="n">
-        <v>7050205</v>
+        <v>7050182</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14937,7 +14943,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>på marken i kärr</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14946,51 +14952,50 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129633415</v>
+        <v>129633394</v>
       </c>
       <c r="B142" t="n">
-        <v>57736</v>
+        <v>92317</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15000,10 +15005,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>426074</v>
+        <v>425325</v>
       </c>
       <c r="R142" t="n">
-        <v>7050193</v>
+        <v>7049857</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15036,11 +15041,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15067,32 +15067,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129633421</v>
+        <v>129633386</v>
       </c>
       <c r="B143" t="n">
-        <v>57736</v>
+        <v>92317</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15102,10 +15102,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>425262</v>
+        <v>425587</v>
       </c>
       <c r="R143" t="n">
-        <v>7049782</v>
+        <v>7050138</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15138,11 +15138,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15169,45 +15164,49 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129633416</v>
+        <v>129627372</v>
       </c>
       <c r="B144" t="n">
-        <v>57736</v>
+        <v>95447</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100109</v>
+        <v>2412</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Stor-grässjön s, Jmt</t>
+          <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>425828</v>
+        <v>425708</v>
       </c>
       <c r="R144" t="n">
-        <v>7050054</v>
+        <v>7050205</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15244,7 +15243,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>på marken i kärr</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15253,25 +15252,26 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129633436</v>
+        <v>129633415</v>
       </c>
       <c r="B145" t="n">
         <v>57736</v>
@@ -15306,10 +15306,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>425329</v>
+        <v>426074</v>
       </c>
       <c r="R145" t="n">
-        <v>7050182</v>
+        <v>7050193</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -18335,7 +18335,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129633425</v>
+        <v>129633412</v>
       </c>
       <c r="B176" t="n">
         <v>57736</v>
@@ -18370,10 +18370,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>425535</v>
+        <v>425867</v>
       </c>
       <c r="R176" t="n">
-        <v>7049914</v>
+        <v>7050236</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18437,7 +18437,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129633412</v>
+        <v>129633425</v>
       </c>
       <c r="B177" t="n">
         <v>57736</v>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>425867</v>
+        <v>425535</v>
       </c>
       <c r="R177" t="n">
-        <v>7050236</v>
+        <v>7049914</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -21146,10 +21146,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129633469</v>
+        <v>129633431</v>
       </c>
       <c r="B204" t="n">
-        <v>91595</v>
+        <v>57736</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21157,21 +21157,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -21181,10 +21181,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>425533</v>
+        <v>425451</v>
       </c>
       <c r="R204" t="n">
-        <v>7050194</v>
+        <v>7050183</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21217,6 +21217,11 @@
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21243,7 +21248,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129633434</v>
+        <v>129633452</v>
       </c>
       <c r="B205" t="n">
         <v>57736</v>
@@ -21278,10 +21283,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>425344</v>
+        <v>425230</v>
       </c>
       <c r="R205" t="n">
-        <v>7050202</v>
+        <v>7049882</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21318,7 +21323,7 @@
       </c>
       <c r="AC205" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -21345,7 +21350,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129633431</v>
+        <v>129633434</v>
       </c>
       <c r="B206" t="n">
         <v>57736</v>
@@ -21380,10 +21385,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>425451</v>
+        <v>425344</v>
       </c>
       <c r="R206" t="n">
-        <v>7050183</v>
+        <v>7050202</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21447,10 +21452,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129633452</v>
+        <v>129633469</v>
       </c>
       <c r="B207" t="n">
-        <v>57736</v>
+        <v>91595</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21458,21 +21463,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -21482,10 +21487,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>425230</v>
+        <v>425533</v>
       </c>
       <c r="R207" t="n">
-        <v>7049882</v>
+        <v>7050194</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21518,11 +21523,6 @@
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -21967,32 +21967,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129672499</v>
+        <v>129672472</v>
       </c>
       <c r="B212" t="n">
-        <v>83052</v>
+        <v>75186</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6440</v>
+        <v>1776</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22002,10 +22002,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>425535</v>
+        <v>425341</v>
       </c>
       <c r="R212" t="n">
-        <v>7049926</v>
+        <v>7049761</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22048,6 +22048,21 @@
       </c>
       <c r="AG212" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO212" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
@@ -22064,32 +22079,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129672514</v>
+        <v>129672486</v>
       </c>
       <c r="B213" t="n">
-        <v>83052</v>
+        <v>96016</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6440</v>
+        <v>2809</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22099,10 +22114,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>425292</v>
+        <v>425724</v>
       </c>
       <c r="R213" t="n">
-        <v>7049741</v>
+        <v>7050188</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22161,32 +22176,32 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129672472</v>
+        <v>129672499</v>
       </c>
       <c r="B214" t="n">
-        <v>75186</v>
+        <v>83052</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1776</v>
+        <v>6440</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22196,10 +22211,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>425341</v>
+        <v>425535</v>
       </c>
       <c r="R214" t="n">
-        <v>7049761</v>
+        <v>7049926</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22242,21 +22257,6 @@
       </c>
       <c r="AG214" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ214" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK214" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO214" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
@@ -22273,32 +22273,32 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129672486</v>
+        <v>129672514</v>
       </c>
       <c r="B215" t="n">
-        <v>96016</v>
+        <v>83052</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -22308,10 +22308,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>425724</v>
+        <v>425292</v>
       </c>
       <c r="R215" t="n">
-        <v>7050188</v>
+        <v>7049741</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22467,32 +22467,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129672511</v>
+        <v>129672494</v>
       </c>
       <c r="B217" t="n">
-        <v>57840</v>
+        <v>79240</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>103031</v>
+        <v>1249</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22502,10 +22502,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>425324</v>
+        <v>425655</v>
       </c>
       <c r="R217" t="n">
-        <v>7049763</v>
+        <v>7049983</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22564,32 +22564,32 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129672494</v>
+        <v>129672511</v>
       </c>
       <c r="B218" t="n">
-        <v>79240</v>
+        <v>57840</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>1249</v>
+        <v>103031</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -22599,10 +22599,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>425655</v>
+        <v>425324</v>
       </c>
       <c r="R218" t="n">
-        <v>7049983</v>
+        <v>7049763</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23258,10 +23258,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129672483</v>
+        <v>129672467</v>
       </c>
       <c r="B225" t="n">
-        <v>96016</v>
+        <v>79337</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23269,21 +23269,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>2809</v>
+        <v>6459</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23293,10 +23293,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>425601</v>
+        <v>425491</v>
       </c>
       <c r="R225" t="n">
-        <v>7050195</v>
+        <v>7049816</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23355,10 +23355,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129672480</v>
+        <v>129672483</v>
       </c>
       <c r="B226" t="n">
-        <v>75065</v>
+        <v>96016</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23366,21 +23366,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6428</v>
+        <v>2809</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23390,10 +23390,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>425403</v>
+        <v>425601</v>
       </c>
       <c r="R226" t="n">
-        <v>7049803</v>
+        <v>7050195</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23436,11 +23436,6 @@
       </c>
       <c r="AG226" t="b">
         <v>0</v>
-      </c>
-      <c r="AO226" t="inlineStr">
-        <is>
-          <t>Grankvist</t>
-        </is>
       </c>
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
@@ -23457,7 +23452,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129672449</v>
+        <v>129672480</v>
       </c>
       <c r="B227" t="n">
         <v>75065</v>
@@ -23492,10 +23487,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>425715</v>
+        <v>425403</v>
       </c>
       <c r="R227" t="n">
-        <v>7050177</v>
+        <v>7049803</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23538,6 +23533,11 @@
       </c>
       <c r="AG227" t="b">
         <v>0</v>
+      </c>
+      <c r="AO227" t="inlineStr">
+        <is>
+          <t>Grankvist</t>
+        </is>
       </c>
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
@@ -23554,32 +23554,32 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129672505</v>
+        <v>129672449</v>
       </c>
       <c r="B228" t="n">
-        <v>78094</v>
+        <v>75065</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>228579</v>
+        <v>6428</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23589,10 +23589,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>425524</v>
+        <v>425715</v>
       </c>
       <c r="R228" t="n">
-        <v>7049845</v>
+        <v>7050177</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23635,11 +23635,6 @@
       </c>
       <c r="AG228" t="b">
         <v>0</v>
-      </c>
-      <c r="AO228" t="inlineStr">
-        <is>
-          <t>barken på gammal gran</t>
-        </is>
       </c>
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
@@ -23656,32 +23651,32 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129672467</v>
+        <v>129672505</v>
       </c>
       <c r="B229" t="n">
-        <v>79337</v>
+        <v>78094</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6459</v>
+        <v>228579</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23691,10 +23686,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>425491</v>
+        <v>425524</v>
       </c>
       <c r="R229" t="n">
-        <v>7049816</v>
+        <v>7049845</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23737,6 +23732,11 @@
       </c>
       <c r="AG229" t="b">
         <v>0</v>
+      </c>
+      <c r="AO229" t="inlineStr">
+        <is>
+          <t>barken på gammal gran</t>
+        </is>
       </c>
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
@@ -24621,32 +24621,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129672460</v>
+        <v>129672495</v>
       </c>
       <c r="B239" t="n">
-        <v>96016</v>
+        <v>79552</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>2809</v>
+        <v>1797</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24656,10 +24656,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>425706</v>
+        <v>425655</v>
       </c>
       <c r="R239" t="n">
-        <v>7050014</v>
+        <v>7049983</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24718,32 +24718,32 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129672495</v>
+        <v>129672488</v>
       </c>
       <c r="B240" t="n">
-        <v>79552</v>
+        <v>91563</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>1797</v>
+        <v>5447</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -24753,10 +24753,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>425655</v>
+        <v>425717</v>
       </c>
       <c r="R240" t="n">
-        <v>7049983</v>
+        <v>7050159</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24815,10 +24815,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129672488</v>
+        <v>129672460</v>
       </c>
       <c r="B241" t="n">
-        <v>91563</v>
+        <v>96016</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24826,21 +24826,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -24850,10 +24850,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>425717</v>
+        <v>425706</v>
       </c>
       <c r="R241" t="n">
-        <v>7050159</v>
+        <v>7050014</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25688,32 +25688,32 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>129672447</v>
+        <v>129672481</v>
       </c>
       <c r="B250" t="n">
-        <v>75186</v>
+        <v>97036</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>1776</v>
+        <v>53</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -25723,10 +25723,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>425702</v>
+        <v>425594</v>
       </c>
       <c r="R250" t="n">
-        <v>7050232</v>
+        <v>7050152</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25767,7 +25767,6 @@
       <c r="AE250" t="b">
         <v>0</v>
       </c>
-      <c r="AF250" t="inlineStr"/>
       <c r="AG250" t="b">
         <v>0</v>
       </c>
@@ -25786,32 +25785,32 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>129672481</v>
+        <v>129672447</v>
       </c>
       <c r="B251" t="n">
-        <v>97036</v>
+        <v>75186</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>53</v>
+        <v>1776</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -25821,10 +25820,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>425594</v>
+        <v>425702</v>
       </c>
       <c r="R251" t="n">
-        <v>7050152</v>
+        <v>7050232</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25865,6 +25864,7 @@
       <c r="AE251" t="b">
         <v>0</v>
       </c>
+      <c r="AF251" t="inlineStr"/>
       <c r="AG251" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47880-2025 artfynd.xlsx
+++ b/artfynd/A 47880-2025 artfynd.xlsx
@@ -6136,10 +6136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129628966</v>
+        <v>129629026</v>
       </c>
       <c r="B55" t="n">
-        <v>80187</v>
+        <v>83044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6147,21 +6147,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>425256</v>
+        <v>425717</v>
       </c>
       <c r="R55" t="n">
-        <v>7049723</v>
+        <v>7050119</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal glasbjörk i gammal granskog</t>
+          <t>På ved i hålighet vid basen av gammal död gran, även gulnål</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6238,56 +6238,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129627360</v>
+        <v>129629008</v>
       </c>
       <c r="B56" t="n">
-        <v>79240</v>
+        <v>79162</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>425573</v>
+        <v>425267</v>
       </c>
       <c r="R56" t="n">
-        <v>7049926</v>
+        <v>7049748</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6324,7 +6313,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>långt ner på gammal gran, fuktigt</t>
+          <t>På tunna kvistar på levande klen gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6333,29 +6322,28 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129628974</v>
+        <v>129628966</v>
       </c>
       <c r="B57" t="n">
-        <v>83057</v>
+        <v>80187</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6363,21 +6351,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6387,10 +6375,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>425457</v>
+        <v>425256</v>
       </c>
       <c r="R57" t="n">
-        <v>7049826</v>
+        <v>7049723</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6427,7 +6415,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran</t>
+          <t>På bark på stam av levande gammal glasbjörk i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6454,45 +6442,56 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129629026</v>
+        <v>129627360</v>
       </c>
       <c r="B58" t="n">
-        <v>83044</v>
+        <v>79240</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>308</v>
+        <v>1249</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>425717</v>
+        <v>425573</v>
       </c>
       <c r="R58" t="n">
-        <v>7050119</v>
+        <v>7049926</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6529,7 +6528,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På ved i hålighet vid basen av gammal död gran, även gulnål</t>
+          <t>långt ner på gammal gran, fuktigt</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6538,28 +6537,29 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129629008</v>
+        <v>129628974</v>
       </c>
       <c r="B59" t="n">
-        <v>79162</v>
+        <v>83057</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6567,21 +6567,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>283</v>
+        <v>1467</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6591,10 +6591,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>425267</v>
+        <v>425457</v>
       </c>
       <c r="R59" t="n">
-        <v>7049748</v>
+        <v>7049826</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På tunna kvistar på levande klen gammal gran i gammal granskog</t>
+          <t>På bark vid basen av gammal levande gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6862,10 +6862,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129628987</v>
+        <v>129628955</v>
       </c>
       <c r="B62" t="n">
-        <v>83047</v>
+        <v>78094</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6873,21 +6873,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>310</v>
+        <v>228579</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6897,10 +6897,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>425242</v>
+        <v>425268</v>
       </c>
       <c r="R62" t="n">
-        <v>7049734</v>
+        <v>7049748</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6964,10 +6964,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129629027</v>
+        <v>129628987</v>
       </c>
       <c r="B63" t="n">
-        <v>83044</v>
+        <v>83047</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6975,21 +6975,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6999,10 +6999,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>425717</v>
+        <v>425242</v>
       </c>
       <c r="R63" t="n">
-        <v>7050114</v>
+        <v>7049734</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På ved på grov gammal naturlig granstubbe i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7066,10 +7066,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129628955</v>
+        <v>129629027</v>
       </c>
       <c r="B64" t="n">
-        <v>78094</v>
+        <v>83044</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7077,21 +7077,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228579</v>
+        <v>308</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7101,10 +7101,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>425268</v>
+        <v>425717</v>
       </c>
       <c r="R64" t="n">
-        <v>7049748</v>
+        <v>7050114</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På ved på grov gammal naturlig granstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8802,32 +8802,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129627349</v>
+        <v>129629021</v>
       </c>
       <c r="B81" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8837,10 +8837,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>425382</v>
+        <v>425518</v>
       </c>
       <c r="R81" t="n">
-        <v>7049760</v>
+        <v>7049851</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8877,7 +8877,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8892,22 +8892,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129627366</v>
+        <v>129628976</v>
       </c>
       <c r="B82" t="n">
-        <v>80214</v>
+        <v>75065</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8915,21 +8915,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6461</v>
+        <v>6428</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8939,10 +8939,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>425552</v>
+        <v>425609</v>
       </c>
       <c r="R82" t="n">
-        <v>7049855</v>
+        <v>7050175</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8977,6 +8977,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På grankvist I gammal granskog</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -8989,44 +8994,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129629021</v>
+        <v>129627349</v>
       </c>
       <c r="B83" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9036,10 +9041,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>425518</v>
+        <v>425382</v>
       </c>
       <c r="R83" t="n">
-        <v>7049851</v>
+        <v>7049760</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9076,7 +9081,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9091,22 +9096,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129628976</v>
+        <v>129627366</v>
       </c>
       <c r="B84" t="n">
-        <v>75065</v>
+        <v>80214</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9114,21 +9119,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6428</v>
+        <v>6461</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9138,10 +9143,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>425609</v>
+        <v>425552</v>
       </c>
       <c r="R84" t="n">
-        <v>7050175</v>
+        <v>7049855</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9176,11 +9181,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På grankvist I gammal granskog</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9193,12 +9193,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -13271,10 +13271,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129633420</v>
+        <v>129633460</v>
       </c>
       <c r="B125" t="n">
-        <v>57736</v>
+        <v>91595</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13282,21 +13282,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13306,10 +13306,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>425481</v>
+        <v>425741</v>
       </c>
       <c r="R125" t="n">
-        <v>7049835</v>
+        <v>7050015</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13342,11 +13342,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13373,7 +13368,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129633460</v>
+        <v>129633459</v>
       </c>
       <c r="B126" t="n">
         <v>91595</v>
@@ -13408,10 +13403,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>425741</v>
+        <v>425702</v>
       </c>
       <c r="R126" t="n">
-        <v>7050015</v>
+        <v>7050011</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13470,32 +13465,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129633459</v>
+        <v>129633389</v>
       </c>
       <c r="B127" t="n">
-        <v>91595</v>
+        <v>92317</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13505,10 +13500,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>425702</v>
+        <v>425870</v>
       </c>
       <c r="R127" t="n">
-        <v>7050011</v>
+        <v>7050232</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13567,32 +13562,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129633389</v>
+        <v>129633420</v>
       </c>
       <c r="B128" t="n">
-        <v>92317</v>
+        <v>57736</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13602,10 +13597,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>425870</v>
+        <v>425481</v>
       </c>
       <c r="R128" t="n">
-        <v>7050232</v>
+        <v>7049835</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13638,6 +13633,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15965,10 +15965,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129633426</v>
+        <v>129633481</v>
       </c>
       <c r="B152" t="n">
-        <v>57736</v>
+        <v>91619</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15976,23 +15976,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
@@ -16000,10 +15996,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>425567</v>
+        <v>425411</v>
       </c>
       <c r="R152" t="n">
-        <v>7049949</v>
+        <v>7050144</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16036,11 +16032,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16067,10 +16058,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129633481</v>
+        <v>129633448</v>
       </c>
       <c r="B153" t="n">
-        <v>91619</v>
+        <v>57736</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16078,19 +16069,23 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
@@ -16098,10 +16093,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>425411</v>
+        <v>425518</v>
       </c>
       <c r="R153" t="n">
-        <v>7050144</v>
+        <v>7050117</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16134,6 +16129,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16160,7 +16160,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129633448</v>
+        <v>129633426</v>
       </c>
       <c r="B154" t="n">
         <v>57736</v>
@@ -16195,10 +16195,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>425518</v>
+        <v>425567</v>
       </c>
       <c r="R154" t="n">
-        <v>7050117</v>
+        <v>7049949</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16235,7 +16235,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18335,7 +18335,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129633412</v>
+        <v>129633425</v>
       </c>
       <c r="B176" t="n">
         <v>57736</v>
@@ -18370,10 +18370,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>425867</v>
+        <v>425535</v>
       </c>
       <c r="R176" t="n">
-        <v>7050236</v>
+        <v>7049914</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18437,7 +18437,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129633425</v>
+        <v>129633412</v>
       </c>
       <c r="B177" t="n">
         <v>57736</v>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>425535</v>
+        <v>425867</v>
       </c>
       <c r="R177" t="n">
-        <v>7049914</v>
+        <v>7050236</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18641,10 +18641,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129633438</v>
+        <v>129633455</v>
       </c>
       <c r="B179" t="n">
-        <v>57736</v>
+        <v>80187</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18652,21 +18652,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18676,10 +18676,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>425374</v>
+        <v>425628</v>
       </c>
       <c r="R179" t="n">
-        <v>7050144</v>
+        <v>7050057</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18712,11 +18712,6 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -18743,7 +18738,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129633398</v>
+        <v>129633438</v>
       </c>
       <c r="B180" t="n">
         <v>57736</v>
@@ -18778,10 +18773,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>425512</v>
+        <v>425374</v>
       </c>
       <c r="R180" t="n">
-        <v>7049868</v>
+        <v>7050144</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18818,7 +18813,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -18845,7 +18840,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129633423</v>
+        <v>129633398</v>
       </c>
       <c r="B181" t="n">
         <v>57736</v>
@@ -18880,10 +18875,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>425400</v>
+        <v>425512</v>
       </c>
       <c r="R181" t="n">
-        <v>7049888</v>
+        <v>7049868</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18920,7 +18915,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -18947,7 +18942,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129633417</v>
+        <v>129633423</v>
       </c>
       <c r="B182" t="n">
         <v>57736</v>
@@ -18982,10 +18977,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>425822</v>
+        <v>425400</v>
       </c>
       <c r="R182" t="n">
-        <v>7050023</v>
+        <v>7049888</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19049,10 +19044,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129633455</v>
+        <v>129633417</v>
       </c>
       <c r="B183" t="n">
-        <v>80187</v>
+        <v>57736</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19060,21 +19055,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19084,10 +19079,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>425628</v>
+        <v>425822</v>
       </c>
       <c r="R183" t="n">
-        <v>7050057</v>
+        <v>7050023</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19120,6 +19115,11 @@
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -22952,32 +22952,32 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129672473</v>
+        <v>129672452</v>
       </c>
       <c r="B222" t="n">
-        <v>83057</v>
+        <v>96028</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1467</v>
+        <v>2813</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -22987,10 +22987,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>425341</v>
+        <v>425710</v>
       </c>
       <c r="R222" t="n">
-        <v>7049761</v>
+        <v>7050150</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23033,21 +23033,6 @@
       </c>
       <c r="AG222" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ222" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK222" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO222" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
@@ -23064,32 +23049,32 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129672452</v>
+        <v>129672473</v>
       </c>
       <c r="B223" t="n">
-        <v>96028</v>
+        <v>83057</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>2813</v>
+        <v>1467</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -23099,10 +23084,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>425710</v>
+        <v>425341</v>
       </c>
       <c r="R223" t="n">
-        <v>7050150</v>
+        <v>7049761</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23145,6 +23130,21 @@
       </c>
       <c r="AG223" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ223" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK223" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO223" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
@@ -23258,10 +23258,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129672467</v>
+        <v>129672483</v>
       </c>
       <c r="B225" t="n">
-        <v>79337</v>
+        <v>96016</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23269,21 +23269,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6459</v>
+        <v>2809</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23293,10 +23293,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>425491</v>
+        <v>425601</v>
       </c>
       <c r="R225" t="n">
-        <v>7049816</v>
+        <v>7050195</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23355,10 +23355,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129672483</v>
+        <v>129672480</v>
       </c>
       <c r="B226" t="n">
-        <v>96016</v>
+        <v>75065</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23366,21 +23366,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>2809</v>
+        <v>6428</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23390,10 +23390,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>425601</v>
+        <v>425403</v>
       </c>
       <c r="R226" t="n">
-        <v>7050195</v>
+        <v>7049803</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23436,6 +23436,11 @@
       </c>
       <c r="AG226" t="b">
         <v>0</v>
+      </c>
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t>Grankvist</t>
+        </is>
       </c>
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
@@ -23452,7 +23457,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129672480</v>
+        <v>129672449</v>
       </c>
       <c r="B227" t="n">
         <v>75065</v>
@@ -23487,10 +23492,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>425403</v>
+        <v>425715</v>
       </c>
       <c r="R227" t="n">
-        <v>7049803</v>
+        <v>7050177</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23533,11 +23538,6 @@
       </c>
       <c r="AG227" t="b">
         <v>0</v>
-      </c>
-      <c r="AO227" t="inlineStr">
-        <is>
-          <t>Grankvist</t>
-        </is>
       </c>
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
@@ -23554,32 +23554,32 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129672449</v>
+        <v>129672505</v>
       </c>
       <c r="B228" t="n">
-        <v>75065</v>
+        <v>78094</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6428</v>
+        <v>228579</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23589,10 +23589,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>425715</v>
+        <v>425524</v>
       </c>
       <c r="R228" t="n">
-        <v>7050177</v>
+        <v>7049845</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23635,6 +23635,11 @@
       </c>
       <c r="AG228" t="b">
         <v>0</v>
+      </c>
+      <c r="AO228" t="inlineStr">
+        <is>
+          <t>barken på gammal gran</t>
+        </is>
       </c>
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
@@ -23651,32 +23656,32 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129672505</v>
+        <v>129672467</v>
       </c>
       <c r="B229" t="n">
-        <v>78094</v>
+        <v>79337</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>228579</v>
+        <v>6459</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23686,10 +23691,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>425524</v>
+        <v>425491</v>
       </c>
       <c r="R229" t="n">
-        <v>7049845</v>
+        <v>7049816</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23732,11 +23737,6 @@
       </c>
       <c r="AG229" t="b">
         <v>0</v>
-      </c>
-      <c r="AO229" t="inlineStr">
-        <is>
-          <t>barken på gammal gran</t>
-        </is>
       </c>
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
@@ -24621,32 +24621,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129672495</v>
+        <v>129672460</v>
       </c>
       <c r="B239" t="n">
-        <v>79552</v>
+        <v>96016</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>1797</v>
+        <v>2809</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24656,10 +24656,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>425655</v>
+        <v>425706</v>
       </c>
       <c r="R239" t="n">
-        <v>7049983</v>
+        <v>7050014</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24718,32 +24718,32 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129672488</v>
+        <v>129672495</v>
       </c>
       <c r="B240" t="n">
-        <v>91563</v>
+        <v>79552</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>5447</v>
+        <v>1797</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -24753,10 +24753,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>425717</v>
+        <v>425655</v>
       </c>
       <c r="R240" t="n">
-        <v>7050159</v>
+        <v>7049983</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24815,10 +24815,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129672460</v>
+        <v>129672488</v>
       </c>
       <c r="B241" t="n">
-        <v>96016</v>
+        <v>91563</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24826,21 +24826,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -24850,10 +24850,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>425706</v>
+        <v>425717</v>
       </c>
       <c r="R241" t="n">
-        <v>7050014</v>
+        <v>7050159</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25688,32 +25688,32 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>129672481</v>
+        <v>129672447</v>
       </c>
       <c r="B250" t="n">
-        <v>97036</v>
+        <v>75186</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>53</v>
+        <v>1776</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -25723,10 +25723,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>425594</v>
+        <v>425702</v>
       </c>
       <c r="R250" t="n">
-        <v>7050152</v>
+        <v>7050232</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25767,6 +25767,7 @@
       <c r="AE250" t="b">
         <v>0</v>
       </c>
+      <c r="AF250" t="inlineStr"/>
       <c r="AG250" t="b">
         <v>0</v>
       </c>
@@ -25785,32 +25786,32 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>129672447</v>
+        <v>129672481</v>
       </c>
       <c r="B251" t="n">
-        <v>75186</v>
+        <v>97036</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1776</v>
+        <v>53</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -25820,10 +25821,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>425702</v>
+        <v>425594</v>
       </c>
       <c r="R251" t="n">
-        <v>7050232</v>
+        <v>7050152</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25864,7 +25865,6 @@
       <c r="AE251" t="b">
         <v>0</v>
       </c>
-      <c r="AF251" t="inlineStr"/>
       <c r="AG251" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47880-2025 artfynd.xlsx
+++ b/artfynd/A 47880-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129628949</v>
+        <v>129629020</v>
       </c>
       <c r="B2" t="n">
-        <v>78108</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>425719</v>
+        <v>425596</v>
       </c>
       <c r="R2" t="n">
-        <v>7050208</v>
+        <v>7049885</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +761,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran vid källflöde i gammal granskog, även trådfräken</t>
+          <t>250 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129629020</v>
+        <v>129628949</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>78108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,45 +800,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>425596</v>
+        <v>425719</v>
       </c>
       <c r="R3" t="n">
-        <v>7049885</v>
+        <v>7050208</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,7 +864,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>250 bålar på gammal levande gran i gammal granskog</t>
+          <t>På bark på undersidan av död gren på gammal levande gran vid källflöde i gammal granskog, även trådfräken</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,7 +873,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1807,32 +1807,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129629034</v>
+        <v>129628977</v>
       </c>
       <c r="B13" t="n">
-        <v>75189</v>
+        <v>75068</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1776</v>
+        <v>6428</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>425685</v>
+        <v>425488</v>
       </c>
       <c r="R13" t="n">
-        <v>7050259</v>
+        <v>7049835</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran i gammal granskog vid rikkärr vid sjö, även liten svartspik</t>
+          <t>På bark vid basen av gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129627356</v>
+        <v>129629034</v>
       </c>
       <c r="B14" t="n">
-        <v>79243</v>
+        <v>75189</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1920,45 +1920,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1249</v>
+        <v>1776</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>Egea &amp; Torrente</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>425723</v>
+        <v>425685</v>
       </c>
       <c r="R14" t="n">
-        <v>7050083</v>
+        <v>7050259</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1993,70 +1982,85 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På döda grenar på gammal levande gran i gammal granskog vid rikkärr vid sjö, även liten svartspik</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129628957</v>
+        <v>129627356</v>
       </c>
       <c r="B15" t="n">
-        <v>91602</v>
+        <v>79243</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1249</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>425661</v>
+        <v>425723</v>
       </c>
       <c r="R15" t="n">
-        <v>7049950</v>
+        <v>7050083</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,39 +2095,35 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129627351</v>
+        <v>129628957</v>
       </c>
       <c r="B16" t="n">
-        <v>80190</v>
+        <v>91602</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>425338</v>
+        <v>425661</v>
       </c>
       <c r="R16" t="n">
-        <v>7049778</v>
+        <v>7049950</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2210,22 +2210,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129628995</v>
+        <v>129627351</v>
       </c>
       <c r="B17" t="n">
-        <v>79555</v>
+        <v>80190</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2233,21 +2233,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1797</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>425662</v>
+        <v>425338</v>
       </c>
       <c r="R17" t="n">
-        <v>7049950</v>
+        <v>7049778</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran vid källflöde i gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2312,44 +2312,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129628977</v>
+        <v>129628995</v>
       </c>
       <c r="B18" t="n">
-        <v>75068</v>
+        <v>79555</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6428</v>
+        <v>1797</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>425488</v>
+        <v>425662</v>
       </c>
       <c r="R18" t="n">
-        <v>7049835</v>
+        <v>7049950</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran i gammal granskog</t>
+          <t>Rikligt på bark på stam av levande gammal gran vid källflöde i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3254,10 +3254,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129629028</v>
+        <v>129628988</v>
       </c>
       <c r="B27" t="n">
-        <v>83050</v>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3265,21 +3265,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>425332</v>
+        <v>425724</v>
       </c>
       <c r="R27" t="n">
-        <v>7049768</v>
+        <v>7050035</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark på björkhögstubbe i gammal granskog</t>
+          <t>på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3356,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129627342</v>
+        <v>129629025</v>
       </c>
       <c r="B28" t="n">
-        <v>92320</v>
+        <v>83038</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,21 +3367,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>6439</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>425473</v>
+        <v>425717</v>
       </c>
       <c r="R28" t="n">
-        <v>7049830</v>
+        <v>7050119</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>på gran i gammal granskog</t>
+          <t>På ved i hålighet vid basen av gammal död gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3440,64 +3440,74 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129628988</v>
+        <v>129627363</v>
       </c>
       <c r="B29" t="n">
-        <v>79084</v>
+        <v>79243</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>425724</v>
+        <v>425428</v>
       </c>
       <c r="R29" t="n">
-        <v>7050035</v>
+        <v>7049830</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3534,7 +3544,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>på gran i gammal granskog</t>
+          <t>vid västsluttning och vattenkälla</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3543,50 +3553,51 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129629025</v>
+        <v>129629028</v>
       </c>
       <c r="B30" t="n">
-        <v>83038</v>
+        <v>83050</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6439</v>
+        <v>310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3596,10 +3607,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>425717</v>
+        <v>425332</v>
       </c>
       <c r="R30" t="n">
-        <v>7050119</v>
+        <v>7049768</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3636,7 +3647,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På ved i hålighet vid basen av gammal död gran</t>
+          <t>På bark på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3663,32 +3674,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129629010</v>
+        <v>129628999</v>
       </c>
       <c r="B31" t="n">
-        <v>83053</v>
+        <v>97711</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6486</v>
+        <v>221063</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3709,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>425698</v>
+        <v>425716</v>
       </c>
       <c r="R31" t="n">
-        <v>7049997</v>
+        <v>7050162</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3738,7 +3749,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande grov gran i gammal fuktig granskog</t>
+          <t>På marken i rikare källflöde i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3765,53 +3776,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129627363</v>
+        <v>129627342</v>
       </c>
       <c r="B32" t="n">
-        <v>79243</v>
+        <v>92320</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1249</v>
+        <v>3298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>425428</v>
+        <v>425473</v>
       </c>
       <c r="R32" t="n">
         <v>7049830</v>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>vid västsluttning och vattenkälla</t>
+          <t>på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3879,32 +3879,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129628999</v>
+        <v>129629010</v>
       </c>
       <c r="B33" t="n">
-        <v>97711</v>
+        <v>83053</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221063</v>
+        <v>6486</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>425716</v>
+        <v>425698</v>
       </c>
       <c r="R33" t="n">
-        <v>7050162</v>
+        <v>7049997</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På marken i rikare källflöde i gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal levande grov gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4902,32 +4902,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129627374</v>
+        <v>129627338</v>
       </c>
       <c r="B43" t="n">
-        <v>79165</v>
+        <v>92320</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>283</v>
+        <v>3298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4937,10 +4937,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>425431</v>
+        <v>425585</v>
       </c>
       <c r="R43" t="n">
-        <v>7049839</v>
+        <v>7050170</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>på tunna kvistar</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5004,10 +5004,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129629007</v>
+        <v>129627378</v>
       </c>
       <c r="B44" t="n">
-        <v>79165</v>
+        <v>79084</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5015,21 +5015,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>425720</v>
+        <v>425710</v>
       </c>
       <c r="R44" t="n">
-        <v>7050011</v>
+        <v>7050152</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal levande senvuxen undertryckt gran i gammal fuktig granskog</t>
+          <t>150 bålar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5094,44 +5094,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129627338</v>
+        <v>129629007</v>
       </c>
       <c r="B45" t="n">
-        <v>92320</v>
+        <v>79165</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3298</v>
+        <v>283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>425585</v>
+        <v>425720</v>
       </c>
       <c r="R45" t="n">
-        <v>7050170</v>
+        <v>7050011</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>På tunna kvistar på gammal levande senvuxen undertryckt gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5196,44 +5196,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129627378</v>
+        <v>129629035</v>
       </c>
       <c r="B46" t="n">
-        <v>79084</v>
+        <v>75189</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1776</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>425710</v>
+        <v>425578</v>
       </c>
       <c r="R46" t="n">
-        <v>7050152</v>
+        <v>7049878</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>150 bålar</t>
+          <t>På tunna döda kvistar på ca 200 år gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5298,22 +5298,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129627345</v>
+        <v>129629014</v>
       </c>
       <c r="B47" t="n">
-        <v>57895</v>
+        <v>91598</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5321,42 +5321,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>425507</v>
+        <v>425660</v>
       </c>
       <c r="R47" t="n">
-        <v>7049861</v>
+        <v>7049963</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5391,6 +5383,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På gammal levande gran i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5403,22 +5400,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129629014</v>
+        <v>129629011</v>
       </c>
       <c r="B48" t="n">
-        <v>91598</v>
+        <v>79555</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5426,21 +5423,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>1797</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5450,10 +5447,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>425660</v>
+        <v>425698</v>
       </c>
       <c r="R48" t="n">
-        <v>7049963</v>
+        <v>7049997</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5490,7 +5487,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5626,32 +5623,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129629035</v>
+        <v>129627374</v>
       </c>
       <c r="B50" t="n">
-        <v>75189</v>
+        <v>79165</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1776</v>
+        <v>283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5661,10 +5658,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>425578</v>
+        <v>425431</v>
       </c>
       <c r="R50" t="n">
-        <v>7049878</v>
+        <v>7049839</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5701,7 +5698,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På tunna döda kvistar på ca 200 år gammal gran i gammal granskog</t>
+          <t>på tunna kvistar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5716,22 +5713,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129629011</v>
+        <v>129627345</v>
       </c>
       <c r="B51" t="n">
-        <v>79555</v>
+        <v>57895</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5739,34 +5736,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1797</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>425698</v>
+        <v>425507</v>
       </c>
       <c r="R51" t="n">
-        <v>7049997</v>
+        <v>7049861</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5801,11 +5806,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>på bark på stam av levande gammal gran i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5818,12 +5818,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -7168,10 +7168,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129629030</v>
+        <v>129627379</v>
       </c>
       <c r="B65" t="n">
-        <v>83047</v>
+        <v>79084</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7179,21 +7179,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7203,10 +7203,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>425332</v>
+        <v>425501</v>
       </c>
       <c r="R65" t="n">
-        <v>7049768</v>
+        <v>7049848</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På ved på björkhögstubbe i gammal granskog, även gulnål och nordlig nållav på barken</t>
+          <t>100 bålar</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7258,44 +7258,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129629004</v>
+        <v>129628985</v>
       </c>
       <c r="B66" t="n">
-        <v>96225</v>
+        <v>83055</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2682</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kärrkammossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Helodium blandowii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7305,10 +7305,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>425685</v>
+        <v>425529</v>
       </c>
       <c r="R66" t="n">
-        <v>7050259</v>
+        <v>7049841</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På marken i rikkärr</t>
+          <t>På bark på stam av död gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7372,10 +7372,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129628989</v>
+        <v>129629030</v>
       </c>
       <c r="B67" t="n">
-        <v>83055</v>
+        <v>83047</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7383,21 +7383,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7407,10 +7407,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>425724</v>
+        <v>425332</v>
       </c>
       <c r="R67" t="n">
-        <v>7050035</v>
+        <v>7049768</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>på gran i gammal granskog</t>
+          <t>På ved på björkhögstubbe i gammal granskog, även gulnål och nordlig nållav på barken</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7474,32 +7474,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129627379</v>
+        <v>129627365</v>
       </c>
       <c r="B68" t="n">
-        <v>79084</v>
+        <v>80217</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>425501</v>
+        <v>425720</v>
       </c>
       <c r="R68" t="n">
-        <v>7049848</v>
+        <v>7050056</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7547,11 +7547,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>100 bålar</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7569,39 +7564,39 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129628985</v>
+        <v>129629004</v>
       </c>
       <c r="B69" t="n">
-        <v>83055</v>
+        <v>96225</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>2682</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kärrkammossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Helodium blandowii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7611,10 +7606,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>425529</v>
+        <v>425685</v>
       </c>
       <c r="R69" t="n">
-        <v>7049841</v>
+        <v>7050259</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7651,7 +7646,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal sälg i gammal granskog</t>
+          <t>På marken i rikkärr</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7678,32 +7673,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129627365</v>
+        <v>129628989</v>
       </c>
       <c r="B70" t="n">
-        <v>80217</v>
+        <v>83055</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6461</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7713,10 +7708,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>425720</v>
+        <v>425724</v>
       </c>
       <c r="R70" t="n">
-        <v>7050056</v>
+        <v>7050035</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7751,6 +7746,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>på gran i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7763,12 +7763,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8081,10 +8081,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129629003</v>
+        <v>129628993</v>
       </c>
       <c r="B74" t="n">
-        <v>78097</v>
+        <v>79555</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8092,21 +8092,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228579</v>
+        <v>1797</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>425395</v>
+        <v>425721</v>
       </c>
       <c r="R74" t="n">
-        <v>7049812</v>
+        <v>7050017</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8183,32 +8183,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129628993</v>
+        <v>129627371</v>
       </c>
       <c r="B75" t="n">
-        <v>79555</v>
+        <v>78443</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1797</v>
+        <v>498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>425721</v>
+        <v>425692</v>
       </c>
       <c r="R75" t="n">
-        <v>7050017</v>
+        <v>7050251</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8258,7 +8258,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran vid ett rikkärr</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8273,22 +8273,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129627371</v>
+        <v>129627364</v>
       </c>
       <c r="B76" t="n">
-        <v>78443</v>
+        <v>79243</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8296,34 +8296,45 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>498</v>
+        <v>1249</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>425692</v>
+        <v>425392</v>
       </c>
       <c r="R76" t="n">
-        <v>7050251</v>
+        <v>7049820</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8360,7 +8371,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På gammal gran vid ett rikkärr</t>
+          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8369,6 +8380,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8387,56 +8399,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129627364</v>
+        <v>129629003</v>
       </c>
       <c r="B77" t="n">
-        <v>79243</v>
+        <v>78097</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1249</v>
+        <v>228579</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>425392</v>
+        <v>425395</v>
       </c>
       <c r="R77" t="n">
-        <v>7049820</v>
+        <v>7049812</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8473,7 +8474,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8482,51 +8483,50 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129629021</v>
+        <v>129627339</v>
       </c>
       <c r="B78" t="n">
-        <v>79084</v>
+        <v>92320</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8536,10 +8536,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>425518</v>
+        <v>425702</v>
       </c>
       <c r="R78" t="n">
-        <v>7049851</v>
+        <v>7050007</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8574,11 +8574,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -8591,22 +8586,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129628976</v>
+        <v>129627366</v>
       </c>
       <c r="B79" t="n">
-        <v>75068</v>
+        <v>80217</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8614,21 +8609,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6428</v>
+        <v>6461</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8638,10 +8633,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>425609</v>
+        <v>425552</v>
       </c>
       <c r="R79" t="n">
-        <v>7050175</v>
+        <v>7049855</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8676,11 +8671,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På grankvist I gammal granskog</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -8693,57 +8683,68 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129627349</v>
+        <v>129627358</v>
       </c>
       <c r="B80" t="n">
-        <v>80218</v>
+        <v>79243</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>1249</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>425382</v>
+        <v>425715</v>
       </c>
       <c r="R80" t="n">
-        <v>7049760</v>
+        <v>7050016</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8780,7 +8781,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8789,6 +8790,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8807,32 +8809,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129627339</v>
+        <v>129627376</v>
       </c>
       <c r="B81" t="n">
-        <v>92320</v>
+        <v>91598</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8842,10 +8844,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>425702</v>
+        <v>425618</v>
       </c>
       <c r="R81" t="n">
-        <v>7050007</v>
+        <v>7049908</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8878,6 +8880,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8904,32 +8911,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129627366</v>
+        <v>129629015</v>
       </c>
       <c r="B82" t="n">
-        <v>80217</v>
+        <v>91598</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6461</v>
+        <v>1108</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8939,10 +8946,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>425552</v>
+        <v>425619</v>
       </c>
       <c r="R82" t="n">
-        <v>7049855</v>
+        <v>7050217</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8977,6 +8984,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På död gammal gran i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -8989,68 +9001,57 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129627358</v>
+        <v>129627380</v>
       </c>
       <c r="B83" t="n">
-        <v>79243</v>
+        <v>82921</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1249</v>
+        <v>1312</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>425715</v>
+        <v>425713</v>
       </c>
       <c r="R83" t="n">
-        <v>7050016</v>
+        <v>7050121</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9087,7 +9088,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9096,7 +9097,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9115,45 +9115,56 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129627376</v>
+        <v>129627357</v>
       </c>
       <c r="B84" t="n">
-        <v>91598</v>
+        <v>79243</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1108</v>
+        <v>1249</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>425618</v>
+        <v>425721</v>
       </c>
       <c r="R84" t="n">
-        <v>7049908</v>
+        <v>7050057</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9190,7 +9201,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>på gran</t>
+          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9199,6 +9210,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9217,10 +9229,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129629015</v>
+        <v>129629021</v>
       </c>
       <c r="B85" t="n">
-        <v>91598</v>
+        <v>79084</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9228,21 +9240,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9252,10 +9264,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>425619</v>
+        <v>425518</v>
       </c>
       <c r="R85" t="n">
-        <v>7050217</v>
+        <v>7049851</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9292,7 +9304,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På död gammal gran i gammal granskog</t>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9319,32 +9331,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129627380</v>
+        <v>129628976</v>
       </c>
       <c r="B86" t="n">
-        <v>82921</v>
+        <v>75068</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1312</v>
+        <v>6428</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9354,10 +9366,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>425713</v>
+        <v>425609</v>
       </c>
       <c r="R86" t="n">
-        <v>7050121</v>
+        <v>7050175</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9394,7 +9406,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På grankvist I gammal granskog</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9409,68 +9421,57 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129627357</v>
+        <v>129627349</v>
       </c>
       <c r="B87" t="n">
-        <v>79243</v>
+        <v>80218</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1249</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>425721</v>
+        <v>425382</v>
       </c>
       <c r="R87" t="n">
-        <v>7050057</v>
+        <v>7049760</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9507,7 +9508,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9516,7 +9517,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9943,32 +9943,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129628978</v>
+        <v>129628970</v>
       </c>
       <c r="B92" t="n">
-        <v>79084</v>
+        <v>96032</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>2813</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9978,10 +9978,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>425716</v>
+        <v>425698</v>
       </c>
       <c r="R92" t="n">
-        <v>7050121</v>
+        <v>7050160</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>på gammal levande gran</t>
+          <t>På marken i fuktstråk i gammal granskog</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10045,10 +10045,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129627381</v>
+        <v>129628978</v>
       </c>
       <c r="B93" t="n">
-        <v>82921</v>
+        <v>79084</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10056,21 +10056,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10080,10 +10080,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>425617</v>
+        <v>425716</v>
       </c>
       <c r="R93" t="n">
-        <v>7049903</v>
+        <v>7050121</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Tillsammans med gammelgranslav</t>
+          <t>på gammal levande gran</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10135,44 +10135,44 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129628970</v>
+        <v>129627381</v>
       </c>
       <c r="B94" t="n">
-        <v>96032</v>
+        <v>82921</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2813</v>
+        <v>1312</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10182,10 +10182,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>425698</v>
+        <v>425617</v>
       </c>
       <c r="R94" t="n">
-        <v>7050160</v>
+        <v>7049903</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10222,7 +10222,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På marken i fuktstråk i gammal granskog</t>
+          <t>Tillsammans med gammelgranslav</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10237,44 +10237,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129628963</v>
+        <v>129628952</v>
       </c>
       <c r="B95" t="n">
-        <v>92557</v>
+        <v>78097</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4769</v>
+        <v>228579</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10284,10 +10284,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>425275</v>
+        <v>425660</v>
       </c>
       <c r="R95" t="n">
-        <v>7049745</v>
+        <v>7050271</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10351,32 +10351,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129628952</v>
+        <v>129628963</v>
       </c>
       <c r="B96" t="n">
-        <v>78097</v>
+        <v>92557</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228579</v>
+        <v>4769</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10386,10 +10386,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>425660</v>
+        <v>425275</v>
       </c>
       <c r="R96" t="n">
-        <v>7050271</v>
+        <v>7049745</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11175,10 +11175,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129629012</v>
+        <v>129628990</v>
       </c>
       <c r="B104" t="n">
-        <v>91598</v>
+        <v>78097</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11186,21 +11186,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1108</v>
+        <v>228579</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11210,10 +11210,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>425698</v>
+        <v>425724</v>
       </c>
       <c r="R104" t="n">
-        <v>7049997</v>
+        <v>7050035</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>På död och levande gammal gran i gammal granskog</t>
+          <t>på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11277,10 +11277,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129628991</v>
+        <v>129629012</v>
       </c>
       <c r="B105" t="n">
-        <v>79555</v>
+        <v>91598</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11288,21 +11288,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1797</v>
+        <v>1108</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11312,10 +11312,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>425724</v>
+        <v>425698</v>
       </c>
       <c r="R105" t="n">
-        <v>7050035</v>
+        <v>7049997</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På två gamla granar i gammal granskog</t>
+          <t>På död och levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11379,7 +11379,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129627367</v>
+        <v>129628991</v>
       </c>
       <c r="B106" t="n">
         <v>79555</v>
@@ -11414,10 +11414,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>425618</v>
+        <v>425724</v>
       </c>
       <c r="R106" t="n">
-        <v>7049902</v>
+        <v>7050035</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På två gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11469,22 +11469,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129628990</v>
+        <v>129627367</v>
       </c>
       <c r="B107" t="n">
-        <v>78097</v>
+        <v>79555</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11492,21 +11492,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228579</v>
+        <v>1797</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11516,10 +11516,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>425724</v>
+        <v>425618</v>
       </c>
       <c r="R107" t="n">
-        <v>7050035</v>
+        <v>7049902</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11556,7 +11556,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>på gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11571,12 +11571,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -12779,10 +12779,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129633476</v>
+        <v>129633444</v>
       </c>
       <c r="B120" t="n">
-        <v>91622</v>
+        <v>57737</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12790,19 +12790,23 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -12810,10 +12814,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>425617</v>
+        <v>425419</v>
       </c>
       <c r="R120" t="n">
-        <v>7050214</v>
+        <v>7050137</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12846,6 +12850,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12872,10 +12881,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129633477</v>
+        <v>129633435</v>
       </c>
       <c r="B121" t="n">
-        <v>91622</v>
+        <v>57737</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12883,19 +12892,23 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -12903,10 +12916,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>425690</v>
+        <v>425324</v>
       </c>
       <c r="R121" t="n">
-        <v>7050235</v>
+        <v>7050192</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12939,6 +12952,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12965,7 +12983,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129633444</v>
+        <v>129633445</v>
       </c>
       <c r="B122" t="n">
         <v>57737</v>
@@ -13000,10 +13018,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>425419</v>
+        <v>425490</v>
       </c>
       <c r="R122" t="n">
-        <v>7050137</v>
+        <v>7050129</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13040,7 +13058,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13067,10 +13085,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129633435</v>
+        <v>129633476</v>
       </c>
       <c r="B123" t="n">
-        <v>57737</v>
+        <v>91622</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13078,23 +13096,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13102,10 +13116,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>425324</v>
+        <v>425617</v>
       </c>
       <c r="R123" t="n">
-        <v>7050192</v>
+        <v>7050214</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13138,11 +13152,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13169,10 +13178,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129633445</v>
+        <v>129633477</v>
       </c>
       <c r="B124" t="n">
-        <v>57737</v>
+        <v>91622</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13180,23 +13189,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13204,10 +13209,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>425490</v>
+        <v>425690</v>
       </c>
       <c r="R124" t="n">
-        <v>7050129</v>
+        <v>7050235</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13240,11 +13245,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13368,10 +13368,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129633460</v>
+        <v>129633420</v>
       </c>
       <c r="B126" t="n">
-        <v>91598</v>
+        <v>57737</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13379,21 +13379,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13403,10 +13403,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>425741</v>
+        <v>425481</v>
       </c>
       <c r="R126" t="n">
-        <v>7050015</v>
+        <v>7049835</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13439,6 +13439,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13465,7 +13470,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129633459</v>
+        <v>129633460</v>
       </c>
       <c r="B127" t="n">
         <v>91598</v>
@@ -13500,10 +13505,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>425702</v>
+        <v>425741</v>
       </c>
       <c r="R127" t="n">
-        <v>7050011</v>
+        <v>7050015</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13562,10 +13567,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129633420</v>
+        <v>129633459</v>
       </c>
       <c r="B128" t="n">
-        <v>57737</v>
+        <v>91598</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13573,21 +13578,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13597,10 +13602,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>425481</v>
+        <v>425702</v>
       </c>
       <c r="R128" t="n">
-        <v>7049835</v>
+        <v>7050011</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13633,11 +13638,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14363,10 +14363,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129633468</v>
+        <v>129633419</v>
       </c>
       <c r="B136" t="n">
-        <v>91598</v>
+        <v>57737</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14374,21 +14374,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14398,10 +14398,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>425549</v>
+        <v>425609</v>
       </c>
       <c r="R136" t="n">
-        <v>7050165</v>
+        <v>7049867</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14434,6 +14434,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14460,7 +14465,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129633419</v>
+        <v>129633403</v>
       </c>
       <c r="B137" t="n">
         <v>57737</v>
@@ -14495,10 +14500,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>425609</v>
+        <v>425668</v>
       </c>
       <c r="R137" t="n">
-        <v>7049867</v>
+        <v>7050116</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14535,7 +14540,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14562,10 +14567,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129633403</v>
+        <v>129633468</v>
       </c>
       <c r="B138" t="n">
-        <v>57737</v>
+        <v>91598</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14573,21 +14578,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14597,10 +14602,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>425668</v>
+        <v>425549</v>
       </c>
       <c r="R138" t="n">
-        <v>7050116</v>
+        <v>7050165</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14633,11 +14638,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15067,7 +15067,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129633436</v>
+        <v>129633415</v>
       </c>
       <c r="B143" t="n">
         <v>57737</v>
@@ -15102,10 +15102,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>425329</v>
+        <v>426074</v>
       </c>
       <c r="R143" t="n">
-        <v>7050182</v>
+        <v>7050193</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15169,7 +15169,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129633415</v>
+        <v>129633416</v>
       </c>
       <c r="B144" t="n">
         <v>57737</v>
@@ -15204,10 +15204,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>426074</v>
+        <v>425828</v>
       </c>
       <c r="R144" t="n">
-        <v>7050193</v>
+        <v>7050054</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15244,7 +15244,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15271,7 +15271,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129633416</v>
+        <v>129633436</v>
       </c>
       <c r="B145" t="n">
         <v>57737</v>
@@ -15306,10 +15306,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>425828</v>
+        <v>425329</v>
       </c>
       <c r="R145" t="n">
-        <v>7050054</v>
+        <v>7050182</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15346,7 +15346,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15373,32 +15373,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129633457</v>
+        <v>129633396</v>
       </c>
       <c r="B146" t="n">
-        <v>79243</v>
+        <v>92320</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1249</v>
+        <v>3298</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15408,10 +15408,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>425579</v>
+        <v>425537</v>
       </c>
       <c r="R146" t="n">
-        <v>7049866</v>
+        <v>7050007</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15470,32 +15470,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129633483</v>
+        <v>129633457</v>
       </c>
       <c r="B147" t="n">
-        <v>89001</v>
+        <v>79243</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>510</v>
+        <v>1249</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15505,10 +15505,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>425789</v>
+        <v>425579</v>
       </c>
       <c r="R147" t="n">
-        <v>7050109</v>
+        <v>7049866</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15567,10 +15567,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129633429</v>
+        <v>129633483</v>
       </c>
       <c r="B148" t="n">
-        <v>57737</v>
+        <v>89001</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15578,21 +15578,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15602,10 +15602,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>425508</v>
+        <v>425789</v>
       </c>
       <c r="R148" t="n">
-        <v>7050208</v>
+        <v>7050109</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15638,11 +15638,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15669,7 +15664,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129633449</v>
+        <v>129633429</v>
       </c>
       <c r="B149" t="n">
         <v>57737</v>
@@ -15704,10 +15699,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>425515</v>
+        <v>425508</v>
       </c>
       <c r="R149" t="n">
-        <v>7050097</v>
+        <v>7050208</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15771,32 +15766,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129633396</v>
+        <v>129633449</v>
       </c>
       <c r="B150" t="n">
-        <v>92320</v>
+        <v>57737</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15806,10 +15801,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>425537</v>
+        <v>425515</v>
       </c>
       <c r="R150" t="n">
-        <v>7050007</v>
+        <v>7050097</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15842,6 +15837,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -19554,32 +19554,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129633474</v>
+        <v>129633391</v>
       </c>
       <c r="B188" t="n">
-        <v>91616</v>
+        <v>92320</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19589,10 +19589,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>425916</v>
+        <v>426028</v>
       </c>
       <c r="R188" t="n">
-        <v>7050154</v>
+        <v>7050169</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19942,10 +19942,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129633433</v>
+        <v>129633474</v>
       </c>
       <c r="B192" t="n">
-        <v>57737</v>
+        <v>91616</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19953,21 +19953,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19977,10 +19977,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>425345</v>
+        <v>425916</v>
       </c>
       <c r="R192" t="n">
-        <v>7050197</v>
+        <v>7050154</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20013,11 +20013,6 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20044,7 +20039,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129633401</v>
+        <v>129633433</v>
       </c>
       <c r="B193" t="n">
         <v>57737</v>
@@ -20079,10 +20074,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>425620</v>
+        <v>425345</v>
       </c>
       <c r="R193" t="n">
-        <v>7049978</v>
+        <v>7050197</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20119,7 +20114,7 @@
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20146,7 +20141,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129633418</v>
+        <v>129633401</v>
       </c>
       <c r="B194" t="n">
         <v>57737</v>
@@ -20181,10 +20176,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>425785</v>
+        <v>425620</v>
       </c>
       <c r="R194" t="n">
-        <v>7050033</v>
+        <v>7049978</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20221,7 +20216,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20248,7 +20243,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129633432</v>
+        <v>129633418</v>
       </c>
       <c r="B195" t="n">
         <v>57737</v>
@@ -20283,10 +20278,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>425434</v>
+        <v>425785</v>
       </c>
       <c r="R195" t="n">
-        <v>7050220</v>
+        <v>7050033</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20350,7 +20345,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129633422</v>
+        <v>129633432</v>
       </c>
       <c r="B196" t="n">
         <v>57737</v>
@@ -20385,10 +20380,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>425222</v>
+        <v>425434</v>
       </c>
       <c r="R196" t="n">
-        <v>7049839</v>
+        <v>7050220</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20425,7 +20420,7 @@
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20452,32 +20447,32 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129633391</v>
+        <v>129633422</v>
       </c>
       <c r="B197" t="n">
-        <v>92320</v>
+        <v>57737</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20487,10 +20482,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>426028</v>
+        <v>425222</v>
       </c>
       <c r="R197" t="n">
-        <v>7050169</v>
+        <v>7049839</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20523,6 +20518,11 @@
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20549,7 +20549,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129633462</v>
+        <v>129633470</v>
       </c>
       <c r="B198" t="n">
         <v>91598</v>
@@ -20584,10 +20584,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>425779</v>
+        <v>425383</v>
       </c>
       <c r="R198" t="n">
-        <v>7050242</v>
+        <v>7050135</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20646,32 +20646,32 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129633400</v>
+        <v>129633475</v>
       </c>
       <c r="B199" t="n">
-        <v>57737</v>
+        <v>91975</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20681,10 +20681,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>425596</v>
+        <v>425690</v>
       </c>
       <c r="R199" t="n">
-        <v>7049933</v>
+        <v>7050235</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20717,11 +20717,6 @@
       <c r="AA199" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -20748,10 +20743,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129633409</v>
+        <v>129633462</v>
       </c>
       <c r="B200" t="n">
-        <v>57737</v>
+        <v>91598</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20759,21 +20754,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20783,10 +20778,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>425616</v>
+        <v>425779</v>
       </c>
       <c r="R200" t="n">
-        <v>7050151</v>
+        <v>7050242</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20819,11 +20814,6 @@
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -20850,7 +20840,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129633437</v>
+        <v>129633400</v>
       </c>
       <c r="B201" t="n">
         <v>57737</v>
@@ -20885,10 +20875,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>425347</v>
+        <v>425596</v>
       </c>
       <c r="R201" t="n">
-        <v>7050132</v>
+        <v>7049933</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20925,7 +20915,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -20952,10 +20942,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129633470</v>
+        <v>129633409</v>
       </c>
       <c r="B202" t="n">
-        <v>91598</v>
+        <v>57737</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20963,21 +20953,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20987,10 +20977,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>425383</v>
+        <v>425616</v>
       </c>
       <c r="R202" t="n">
-        <v>7050135</v>
+        <v>7050151</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21023,6 +21013,11 @@
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21049,32 +21044,32 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129633475</v>
+        <v>129633437</v>
       </c>
       <c r="B203" t="n">
-        <v>91975</v>
+        <v>57737</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -21084,10 +21079,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>425690</v>
+        <v>425347</v>
       </c>
       <c r="R203" t="n">
-        <v>7050235</v>
+        <v>7050132</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21120,6 +21115,11 @@
       <c r="AA203" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21146,10 +21146,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129633452</v>
+        <v>129633469</v>
       </c>
       <c r="B204" t="n">
-        <v>57737</v>
+        <v>91598</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21157,21 +21157,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -21181,10 +21181,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>425230</v>
+        <v>425533</v>
       </c>
       <c r="R204" t="n">
-        <v>7049882</v>
+        <v>7050194</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21217,11 +21217,6 @@
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21248,10 +21243,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129633469</v>
+        <v>129633434</v>
       </c>
       <c r="B205" t="n">
-        <v>91598</v>
+        <v>57737</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21259,21 +21254,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -21283,10 +21278,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>425533</v>
+        <v>425344</v>
       </c>
       <c r="R205" t="n">
-        <v>7050194</v>
+        <v>7050202</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21319,6 +21314,11 @@
       <c r="AA205" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -21345,7 +21345,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129633434</v>
+        <v>129633431</v>
       </c>
       <c r="B206" t="n">
         <v>57737</v>
@@ -21380,10 +21380,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>425344</v>
+        <v>425451</v>
       </c>
       <c r="R206" t="n">
-        <v>7050202</v>
+        <v>7050183</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21447,7 +21447,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129633431</v>
+        <v>129633452</v>
       </c>
       <c r="B207" t="n">
         <v>57737</v>
@@ -21482,10 +21482,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>425451</v>
+        <v>425230</v>
       </c>
       <c r="R207" t="n">
-        <v>7050183</v>
+        <v>7049882</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21522,7 +21522,7 @@
       </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22467,32 +22467,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129672511</v>
+        <v>129672494</v>
       </c>
       <c r="B217" t="n">
-        <v>57841</v>
+        <v>79243</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>103031</v>
+        <v>1249</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22502,10 +22502,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>425324</v>
+        <v>425655</v>
       </c>
       <c r="R217" t="n">
-        <v>7049763</v>
+        <v>7049983</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22564,32 +22564,32 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129672494</v>
+        <v>129672511</v>
       </c>
       <c r="B218" t="n">
-        <v>79243</v>
+        <v>57841</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>1249</v>
+        <v>103031</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -22599,10 +22599,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>425655</v>
+        <v>425324</v>
       </c>
       <c r="R218" t="n">
-        <v>7049983</v>
+        <v>7049763</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23161,32 +23161,32 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129672484</v>
+        <v>129672480</v>
       </c>
       <c r="B224" t="n">
-        <v>78108</v>
+        <v>75068</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>314</v>
+        <v>6428</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -23196,10 +23196,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>425661</v>
+        <v>425403</v>
       </c>
       <c r="R224" t="n">
-        <v>7050268</v>
+        <v>7049803</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23242,6 +23242,11 @@
       </c>
       <c r="AG224" t="b">
         <v>0</v>
+      </c>
+      <c r="AO224" t="inlineStr">
+        <is>
+          <t>Grankvist</t>
+        </is>
       </c>
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
@@ -23258,10 +23263,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129672483</v>
+        <v>129672449</v>
       </c>
       <c r="B225" t="n">
-        <v>96020</v>
+        <v>75068</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23269,21 +23274,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>2809</v>
+        <v>6428</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23293,10 +23298,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>425601</v>
+        <v>425715</v>
       </c>
       <c r="R225" t="n">
-        <v>7050195</v>
+        <v>7050177</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23355,32 +23360,32 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129672467</v>
+        <v>129672505</v>
       </c>
       <c r="B226" t="n">
-        <v>79340</v>
+        <v>78097</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6459</v>
+        <v>228579</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23390,10 +23395,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>425491</v>
+        <v>425524</v>
       </c>
       <c r="R226" t="n">
-        <v>7049816</v>
+        <v>7049845</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23436,6 +23441,11 @@
       </c>
       <c r="AG226" t="b">
         <v>0</v>
+      </c>
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t>barken på gammal gran</t>
+        </is>
       </c>
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
@@ -23452,32 +23462,32 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129672480</v>
+        <v>129672484</v>
       </c>
       <c r="B227" t="n">
-        <v>75068</v>
+        <v>78108</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6428</v>
+        <v>314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23487,10 +23497,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>425403</v>
+        <v>425661</v>
       </c>
       <c r="R227" t="n">
-        <v>7049803</v>
+        <v>7050268</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23533,11 +23543,6 @@
       </c>
       <c r="AG227" t="b">
         <v>0</v>
-      </c>
-      <c r="AO227" t="inlineStr">
-        <is>
-          <t>Grankvist</t>
-        </is>
       </c>
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
@@ -23554,10 +23559,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129672449</v>
+        <v>129672483</v>
       </c>
       <c r="B228" t="n">
-        <v>75068</v>
+        <v>96020</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -23565,21 +23570,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6428</v>
+        <v>2809</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23589,10 +23594,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>425715</v>
+        <v>425601</v>
       </c>
       <c r="R228" t="n">
-        <v>7050177</v>
+        <v>7050195</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23651,32 +23656,32 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129672505</v>
+        <v>129672467</v>
       </c>
       <c r="B229" t="n">
-        <v>78097</v>
+        <v>79340</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>228579</v>
+        <v>6459</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23686,10 +23691,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>425524</v>
+        <v>425491</v>
       </c>
       <c r="R229" t="n">
-        <v>7049845</v>
+        <v>7049816</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23732,11 +23737,6 @@
       </c>
       <c r="AG229" t="b">
         <v>0</v>
-      </c>
-      <c r="AO229" t="inlineStr">
-        <is>
-          <t>barken på gammal gran</t>
-        </is>
       </c>
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
@@ -25494,32 +25494,32 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>129672453</v>
+        <v>129672490</v>
       </c>
       <c r="B248" t="n">
-        <v>79555</v>
+        <v>92320</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>1797</v>
+        <v>3298</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -25529,10 +25529,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>425710</v>
+        <v>425697</v>
       </c>
       <c r="R248" t="n">
-        <v>7050150</v>
+        <v>7050149</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25591,32 +25591,32 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>129672490</v>
+        <v>129672453</v>
       </c>
       <c r="B249" t="n">
-        <v>92320</v>
+        <v>79555</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>3298</v>
+        <v>1797</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -25626,10 +25626,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>425697</v>
+        <v>425710</v>
       </c>
       <c r="R249" t="n">
-        <v>7050149</v>
+        <v>7050150</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>

--- a/artfynd/A 47880-2025 artfynd.xlsx
+++ b/artfynd/A 47880-2025 artfynd.xlsx
@@ -1197,10 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129627370</v>
+        <v>129628998</v>
       </c>
       <c r="B7" t="n">
-        <v>78100</v>
+        <v>79558</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1208,21 +1208,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>1797</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>425453</v>
+        <v>425339</v>
       </c>
       <c r="R7" t="n">
-        <v>7049864</v>
+        <v>7049780</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>På grov gren på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,22 +1287,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129627377</v>
+        <v>129628961</v>
       </c>
       <c r="B8" t="n">
-        <v>91625</v>
+        <v>57740</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1310,19 +1310,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1330,10 +1334,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>425701</v>
+        <v>425479</v>
       </c>
       <c r="R8" t="n">
-        <v>7050250</v>
+        <v>7049837</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,7 +1374,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På granhögstubbe</t>
+          <t>Äldre ringhack på gammal levande gran i gammal granskog, även på rötter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1385,7 +1389,7 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1397,10 +1401,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129628998</v>
+        <v>129627370</v>
       </c>
       <c r="B9" t="n">
-        <v>79558</v>
+        <v>78100</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,21 +1412,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1797</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1432,10 +1436,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>425339</v>
+        <v>425453</v>
       </c>
       <c r="R9" t="n">
-        <v>7049780</v>
+        <v>7049864</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,7 +1476,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På grov gren på gammal levande gran i gammal granskog</t>
+          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1487,12 +1491,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1705,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129628961</v>
+        <v>129627377</v>
       </c>
       <c r="B12" t="n">
-        <v>57740</v>
+        <v>91625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,23 +1720,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>425479</v>
+        <v>425701</v>
       </c>
       <c r="R12" t="n">
-        <v>7049837</v>
+        <v>7050250</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gammal levande gran i gammal granskog, även på rötter</t>
+          <t>På granhögstubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,7 +1795,7 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -2426,7 +2426,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129628997</v>
+        <v>129627369</v>
       </c>
       <c r="B19" t="n">
         <v>79558</v>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>425393</v>
+        <v>425420</v>
       </c>
       <c r="R19" t="n">
-        <v>7049812</v>
+        <v>7049825</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,22 +2516,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129627369</v>
+        <v>129628954</v>
       </c>
       <c r="B20" t="n">
-        <v>79558</v>
+        <v>83058</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2539,21 +2539,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1797</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>425420</v>
+        <v>425469</v>
       </c>
       <c r="R20" t="n">
-        <v>7049825</v>
+        <v>7049817</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2618,44 +2618,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129627375</v>
+        <v>129628984</v>
       </c>
       <c r="B21" t="n">
-        <v>91601</v>
+        <v>80220</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>425697</v>
+        <v>425327</v>
       </c>
       <c r="R21" t="n">
-        <v>7050004</v>
+        <v>7049709</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2720,7 +2720,7 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -2732,56 +2732,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129627361</v>
+        <v>129628997</v>
       </c>
       <c r="B22" t="n">
-        <v>79246</v>
+        <v>79558</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1249</v>
+        <v>1797</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>425570</v>
+        <v>425393</v>
       </c>
       <c r="R22" t="n">
-        <v>7049933</v>
+        <v>7049812</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2818,7 +2807,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2827,26 +2816,25 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129629009</v>
+        <v>129627375</v>
       </c>
       <c r="B23" t="n">
         <v>91601</v>
@@ -2881,10 +2869,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>425707</v>
+        <v>425697</v>
       </c>
       <c r="R23" t="n">
-        <v>7050031</v>
+        <v>7050004</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2921,7 +2909,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2936,7 +2924,7 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -2948,45 +2936,56 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129628954</v>
+        <v>129627361</v>
       </c>
       <c r="B24" t="n">
-        <v>83058</v>
+        <v>79246</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>425469</v>
+        <v>425570</v>
       </c>
       <c r="R24" t="n">
-        <v>7049817</v>
+        <v>7049933</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,7 +3022,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3032,50 +3031,51 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129628984</v>
+        <v>129629009</v>
       </c>
       <c r="B25" t="n">
-        <v>80220</v>
+        <v>91601</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6461</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>425327</v>
+        <v>425707</v>
       </c>
       <c r="R25" t="n">
-        <v>7049709</v>
+        <v>7050031</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3981,45 +3981,56 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129627336</v>
+        <v>129627347</v>
       </c>
       <c r="B34" t="n">
-        <v>83058</v>
+        <v>92560</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>4769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>425710</v>
+        <v>425707</v>
       </c>
       <c r="R34" t="n">
-        <v>7050275</v>
+        <v>7050150</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4054,17 +4065,13 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4083,32 +4090,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129628956</v>
+        <v>129627337</v>
       </c>
       <c r="B35" t="n">
-        <v>83058</v>
+        <v>91569</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4118,10 +4125,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>425268</v>
+        <v>425649</v>
       </c>
       <c r="R35" t="n">
-        <v>7049748</v>
+        <v>7049974</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4156,37 +4163,31 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129628979</v>
+        <v>129627336</v>
       </c>
       <c r="B36" t="n">
         <v>83058</v>
@@ -4221,10 +4222,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>425716</v>
+        <v>425710</v>
       </c>
       <c r="R36" t="n">
-        <v>7050121</v>
+        <v>7050275</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4261,7 +4262,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>på gammal levande gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4276,44 +4277,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129628965</v>
+        <v>129628956</v>
       </c>
       <c r="B37" t="n">
-        <v>83056</v>
+        <v>83058</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6486</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4323,10 +4324,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>425510</v>
+        <v>425268</v>
       </c>
       <c r="R37" t="n">
-        <v>7049849</v>
+        <v>7049748</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4363,7 +4364,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande grov gran i gammal fuktig granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4372,6 +4373,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4390,10 +4392,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129628980</v>
+        <v>129628979</v>
       </c>
       <c r="B38" t="n">
-        <v>78100</v>
+        <v>83058</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4401,21 +4403,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4492,32 +4494,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129628982</v>
+        <v>129628980</v>
       </c>
       <c r="B39" t="n">
-        <v>79246</v>
+        <v>78100</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1249</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4527,10 +4529,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>425718</v>
+        <v>425716</v>
       </c>
       <c r="R39" t="n">
-        <v>7050119</v>
+        <v>7050121</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4567,7 +4569,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Två mycket stora bålar på grova grenar på gammal levande gran</t>
+          <t>på gammal levande gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4594,56 +4596,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129627347</v>
+        <v>129628982</v>
       </c>
       <c r="B40" t="n">
-        <v>92560</v>
+        <v>79246</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4769</v>
+        <v>1249</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>425707</v>
+        <v>425718</v>
       </c>
       <c r="R40" t="n">
-        <v>7050150</v>
+        <v>7050119</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4678,57 +4669,61 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Två mycket stora bålar på grova grenar på gammal levande gran</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129627337</v>
+        <v>129628971</v>
       </c>
       <c r="B41" t="n">
-        <v>91569</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4738,10 +4733,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>425649</v>
+        <v>425704</v>
       </c>
       <c r="R41" t="n">
-        <v>7049974</v>
+        <v>7050246</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4776,6 +4771,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>på gammal gran i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4788,44 +4788,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129628971</v>
+        <v>129628965</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>83056</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>425704</v>
+        <v>425510</v>
       </c>
       <c r="R42" t="n">
-        <v>7050246</v>
+        <v>7049849</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4875,7 +4875,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal levande grov gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5830,32 +5830,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129628948</v>
+        <v>129628996</v>
       </c>
       <c r="B52" t="n">
-        <v>97714</v>
+        <v>79558</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221063</v>
+        <v>1797</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>425719</v>
+        <v>425596</v>
       </c>
       <c r="R52" t="n">
-        <v>7050208</v>
+        <v>7049885</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På marken i källflöde i gammal granskog</t>
+          <t>På basen av gammal levande gran i gammal fuktig granskog i sluttning</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5932,32 +5932,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129628996</v>
+        <v>129628948</v>
       </c>
       <c r="B53" t="n">
-        <v>79558</v>
+        <v>97714</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1797</v>
+        <v>221063</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5967,10 +5967,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>425596</v>
+        <v>425719</v>
       </c>
       <c r="R53" t="n">
-        <v>7049885</v>
+        <v>7050208</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På basen av gammal levande gran i gammal fuktig granskog i sluttning</t>
+          <t>På marken i källflöde i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6136,10 +6136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129629026</v>
+        <v>129628966</v>
       </c>
       <c r="B55" t="n">
-        <v>83050</v>
+        <v>80193</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6147,21 +6147,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>425717</v>
+        <v>425256</v>
       </c>
       <c r="R55" t="n">
-        <v>7050119</v>
+        <v>7049723</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På ved i hålighet vid basen av gammal död gran, även gulnål</t>
+          <t>På bark på stam av levande gammal glasbjörk i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6238,45 +6238,56 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129629008</v>
+        <v>129627360</v>
       </c>
       <c r="B56" t="n">
-        <v>79168</v>
+        <v>79246</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>425267</v>
+        <v>425573</v>
       </c>
       <c r="R56" t="n">
-        <v>7049748</v>
+        <v>7049926</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6313,7 +6324,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På tunna kvistar på levande klen gammal gran i gammal granskog</t>
+          <t>långt ner på gammal gran, fuktigt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6322,28 +6333,29 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129628966</v>
+        <v>129629026</v>
       </c>
       <c r="B57" t="n">
-        <v>80193</v>
+        <v>83050</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6351,21 +6363,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6375,10 +6387,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>425256</v>
+        <v>425717</v>
       </c>
       <c r="R57" t="n">
-        <v>7049723</v>
+        <v>7050119</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6415,7 +6427,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal glasbjörk i gammal granskog</t>
+          <t>På ved i hålighet vid basen av gammal död gran, även gulnål</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6442,10 +6454,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129628974</v>
+        <v>129629008</v>
       </c>
       <c r="B58" t="n">
-        <v>83063</v>
+        <v>79168</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6453,21 +6465,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1467</v>
+        <v>283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6477,10 +6489,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>425457</v>
+        <v>425267</v>
       </c>
       <c r="R58" t="n">
-        <v>7049826</v>
+        <v>7049748</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6517,7 +6529,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran</t>
+          <t>På tunna kvistar på levande klen gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6544,56 +6556,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129627360</v>
+        <v>129628974</v>
       </c>
       <c r="B59" t="n">
-        <v>79246</v>
+        <v>83063</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1249</v>
+        <v>1467</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>425573</v>
+        <v>425457</v>
       </c>
       <c r="R59" t="n">
-        <v>7049926</v>
+        <v>7049826</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6630,7 +6631,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>långt ner på gammal gran, fuktigt</t>
+          <t>På bark vid basen av gammal levande gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6639,19 +6640,18 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7270,32 +7270,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129628989</v>
+        <v>129629004</v>
       </c>
       <c r="B66" t="n">
-        <v>83058</v>
+        <v>96228</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>2682</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kärrkammossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Helodium blandowii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7305,10 +7305,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>425724</v>
+        <v>425685</v>
       </c>
       <c r="R66" t="n">
-        <v>7050035</v>
+        <v>7050259</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>på gran i gammal granskog</t>
+          <t>På marken i rikkärr</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7372,10 +7372,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129628985</v>
+        <v>129627379</v>
       </c>
       <c r="B67" t="n">
-        <v>83058</v>
+        <v>79087</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7383,21 +7383,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7407,10 +7407,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>425529</v>
+        <v>425501</v>
       </c>
       <c r="R67" t="n">
-        <v>7049841</v>
+        <v>7049848</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal sälg i gammal granskog</t>
+          <t>100 bålar</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7462,7 +7462,7 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
@@ -7474,32 +7474,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129629004</v>
+        <v>129628989</v>
       </c>
       <c r="B68" t="n">
-        <v>96228</v>
+        <v>83058</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2682</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kärrkammossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Helodium blandowii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>425685</v>
+        <v>425724</v>
       </c>
       <c r="R68" t="n">
-        <v>7050259</v>
+        <v>7050035</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På marken i rikkärr</t>
+          <t>på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7576,10 +7576,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129627379</v>
+        <v>129628985</v>
       </c>
       <c r="B69" t="n">
-        <v>79087</v>
+        <v>83058</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7587,21 +7587,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7611,10 +7611,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>425501</v>
+        <v>425529</v>
       </c>
       <c r="R69" t="n">
-        <v>7049848</v>
+        <v>7049841</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>100 bålar</t>
+          <t>På bark på stam av död gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7666,7 +7666,7 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
@@ -10045,32 +10045,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129628978</v>
+        <v>129628970</v>
       </c>
       <c r="B93" t="n">
-        <v>79087</v>
+        <v>96035</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>2813</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10080,10 +10080,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>425716</v>
+        <v>425698</v>
       </c>
       <c r="R93" t="n">
-        <v>7050121</v>
+        <v>7050160</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>på gammal levande gran</t>
+          <t>På marken i fuktstråk i gammal granskog</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10147,32 +10147,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129628970</v>
+        <v>129628978</v>
       </c>
       <c r="B94" t="n">
-        <v>96035</v>
+        <v>79087</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2813</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10182,10 +10182,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>425698</v>
+        <v>425716</v>
       </c>
       <c r="R94" t="n">
-        <v>7050160</v>
+        <v>7050121</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10222,7 +10222,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På marken i fuktstråk i gammal granskog</t>
+          <t>på gammal levande gran</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10249,32 +10249,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129628952</v>
+        <v>129628963</v>
       </c>
       <c r="B95" t="n">
-        <v>78100</v>
+        <v>92560</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228579</v>
+        <v>4769</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10284,10 +10284,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>425660</v>
+        <v>425275</v>
       </c>
       <c r="R95" t="n">
-        <v>7050271</v>
+        <v>7049745</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10351,32 +10351,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129628963</v>
+        <v>129628952</v>
       </c>
       <c r="B96" t="n">
-        <v>92560</v>
+        <v>78100</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4769</v>
+        <v>228579</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10386,10 +10386,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>425275</v>
+        <v>425660</v>
       </c>
       <c r="R96" t="n">
-        <v>7049745</v>
+        <v>7050271</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10563,10 +10563,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129629033</v>
+        <v>129628953</v>
       </c>
       <c r="B98" t="n">
-        <v>78100</v>
+        <v>83058</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10574,21 +10574,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>425685</v>
+        <v>425660</v>
       </c>
       <c r="R98" t="n">
-        <v>7050259</v>
+        <v>7050271</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10638,7 +10638,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>på gammal levande gran i gammal granskog vid rikkärr vid sjö</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10665,32 +10665,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129628953</v>
+        <v>129629029</v>
       </c>
       <c r="B99" t="n">
-        <v>83058</v>
+        <v>83041</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10700,10 +10700,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>425660</v>
+        <v>425332</v>
       </c>
       <c r="R99" t="n">
-        <v>7050271</v>
+        <v>7049768</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På bark på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10767,32 +10767,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129629029</v>
+        <v>129629033</v>
       </c>
       <c r="B100" t="n">
-        <v>83041</v>
+        <v>78100</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6439</v>
+        <v>228579</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10802,10 +10802,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>425332</v>
+        <v>425685</v>
       </c>
       <c r="R100" t="n">
-        <v>7049768</v>
+        <v>7050259</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>På bark på björkhögstubbe i gammal granskog</t>
+          <t>på gammal levande gran i gammal granskog vid rikkärr vid sjö</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13271,32 +13271,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129633460</v>
+        <v>129633389</v>
       </c>
       <c r="B125" t="n">
-        <v>91601</v>
+        <v>92323</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13306,10 +13306,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>425741</v>
+        <v>425870</v>
       </c>
       <c r="R125" t="n">
-        <v>7050015</v>
+        <v>7050232</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13368,7 +13368,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129633459</v>
+        <v>129633460</v>
       </c>
       <c r="B126" t="n">
         <v>91601</v>
@@ -13403,10 +13403,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>425702</v>
+        <v>425741</v>
       </c>
       <c r="R126" t="n">
-        <v>7050011</v>
+        <v>7050015</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13465,32 +13465,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129633389</v>
+        <v>129633459</v>
       </c>
       <c r="B127" t="n">
-        <v>92323</v>
+        <v>91601</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>425870</v>
+        <v>425702</v>
       </c>
       <c r="R127" t="n">
-        <v>7050232</v>
+        <v>7050011</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13664,32 +13664,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129633471</v>
+        <v>129633385</v>
       </c>
       <c r="B129" t="n">
-        <v>91601</v>
+        <v>92323</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13699,10 +13699,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>425534</v>
+        <v>425773</v>
       </c>
       <c r="R129" t="n">
-        <v>7050039</v>
+        <v>7050160</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13761,7 +13761,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129633466</v>
+        <v>129633471</v>
       </c>
       <c r="B130" t="n">
         <v>91601</v>
@@ -13796,10 +13796,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>426016</v>
+        <v>425534</v>
       </c>
       <c r="R130" t="n">
-        <v>7050154</v>
+        <v>7050039</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13858,10 +13858,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129633439</v>
+        <v>129633466</v>
       </c>
       <c r="B131" t="n">
-        <v>57740</v>
+        <v>91601</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13869,21 +13869,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13893,10 +13893,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>425357</v>
+        <v>426016</v>
       </c>
       <c r="R131" t="n">
-        <v>7050155</v>
+        <v>7050154</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13929,11 +13929,6 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13960,7 +13955,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129633447</v>
+        <v>129633404</v>
       </c>
       <c r="B132" t="n">
         <v>57740</v>
@@ -13995,10 +13990,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>425526</v>
+        <v>425682</v>
       </c>
       <c r="R132" t="n">
-        <v>7050117</v>
+        <v>7050073</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14062,7 +14057,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129633413</v>
+        <v>129633439</v>
       </c>
       <c r="B133" t="n">
         <v>57740</v>
@@ -14097,10 +14092,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>425870</v>
+        <v>425357</v>
       </c>
       <c r="R133" t="n">
-        <v>7050230</v>
+        <v>7050155</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14164,32 +14159,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129633385</v>
+        <v>129633447</v>
       </c>
       <c r="B134" t="n">
-        <v>92323</v>
+        <v>57740</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14199,10 +14194,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>425773</v>
+        <v>425526</v>
       </c>
       <c r="R134" t="n">
-        <v>7050160</v>
+        <v>7050117</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14235,6 +14230,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14261,7 +14261,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129633404</v>
+        <v>129633413</v>
       </c>
       <c r="B135" t="n">
         <v>57740</v>
@@ -14296,10 +14296,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>425682</v>
+        <v>425870</v>
       </c>
       <c r="R135" t="n">
-        <v>7050073</v>
+        <v>7050230</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14664,45 +14664,49 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129633416</v>
+        <v>129627372</v>
       </c>
       <c r="B139" t="n">
-        <v>57740</v>
+        <v>95454</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>2412</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Stor-grässjön s, Jmt</t>
+          <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>425828</v>
+        <v>425708</v>
       </c>
       <c r="R139" t="n">
-        <v>7050054</v>
+        <v>7050205</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14739,7 +14743,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>på marken i kärr</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14748,28 +14752,29 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129627372</v>
+        <v>129633394</v>
       </c>
       <c r="B140" t="n">
-        <v>95454</v>
+        <v>92323</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14777,38 +14782,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2412</v>
+        <v>3298</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
+          <t>Stor-grässjön s, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>425708</v>
+        <v>425325</v>
       </c>
       <c r="R140" t="n">
-        <v>7050205</v>
+        <v>7049857</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14843,37 +14844,31 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>på marken i kärr</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129633394</v>
+        <v>129633386</v>
       </c>
       <c r="B141" t="n">
         <v>92323</v>
@@ -14908,10 +14903,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>425325</v>
+        <v>425587</v>
       </c>
       <c r="R141" t="n">
-        <v>7049857</v>
+        <v>7050138</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14970,32 +14965,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129633386</v>
+        <v>129633421</v>
       </c>
       <c r="B142" t="n">
-        <v>92323</v>
+        <v>57740</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15005,10 +15000,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>425587</v>
+        <v>425262</v>
       </c>
       <c r="R142" t="n">
-        <v>7050138</v>
+        <v>7049782</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15041,6 +15036,11 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15067,7 +15067,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129633421</v>
+        <v>129633415</v>
       </c>
       <c r="B143" t="n">
         <v>57740</v>
@@ -15102,10 +15102,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>425262</v>
+        <v>426074</v>
       </c>
       <c r="R143" t="n">
-        <v>7049782</v>
+        <v>7050193</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15142,7 +15142,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15169,7 +15169,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129633415</v>
+        <v>129633416</v>
       </c>
       <c r="B144" t="n">
         <v>57740</v>
@@ -15204,10 +15204,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>426074</v>
+        <v>425828</v>
       </c>
       <c r="R144" t="n">
-        <v>7050193</v>
+        <v>7050054</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15244,7 +15244,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16262,32 +16262,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129633383</v>
+        <v>129633463</v>
       </c>
       <c r="B155" t="n">
-        <v>92323</v>
+        <v>91601</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16297,10 +16297,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>425676</v>
+        <v>425838</v>
       </c>
       <c r="R155" t="n">
-        <v>7050147</v>
+        <v>7050241</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16456,32 +16456,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129633405</v>
+        <v>129633383</v>
       </c>
       <c r="B157" t="n">
-        <v>57740</v>
+        <v>92323</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16491,10 +16491,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>425721</v>
+        <v>425676</v>
       </c>
       <c r="R157" t="n">
-        <v>7050005</v>
+        <v>7050147</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16527,11 +16527,6 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16558,32 +16553,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129633446</v>
+        <v>129633388</v>
       </c>
       <c r="B158" t="n">
-        <v>57740</v>
+        <v>92323</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16593,10 +16588,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>425520</v>
+        <v>425864</v>
       </c>
       <c r="R158" t="n">
-        <v>7050128</v>
+        <v>7050235</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16629,11 +16624,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16660,32 +16650,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129633388</v>
+        <v>129633405</v>
       </c>
       <c r="B159" t="n">
-        <v>92323</v>
+        <v>57740</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16695,10 +16685,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>425864</v>
+        <v>425721</v>
       </c>
       <c r="R159" t="n">
-        <v>7050235</v>
+        <v>7050005</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16731,6 +16721,11 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16757,10 +16752,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129633463</v>
+        <v>129633446</v>
       </c>
       <c r="B160" t="n">
-        <v>91601</v>
+        <v>57740</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16768,21 +16763,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16792,10 +16787,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>425838</v>
+        <v>425520</v>
       </c>
       <c r="R160" t="n">
-        <v>7050241</v>
+        <v>7050128</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16828,6 +16823,11 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19253,10 +19253,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129633423</v>
+        <v>129633455</v>
       </c>
       <c r="B185" t="n">
-        <v>57740</v>
+        <v>80193</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19264,21 +19264,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19288,10 +19288,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>425400</v>
+        <v>425628</v>
       </c>
       <c r="R185" t="n">
-        <v>7049888</v>
+        <v>7050057</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19324,11 +19324,6 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19355,7 +19350,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129633417</v>
+        <v>129633423</v>
       </c>
       <c r="B186" t="n">
         <v>57740</v>
@@ -19390,10 +19385,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>425822</v>
+        <v>425400</v>
       </c>
       <c r="R186" t="n">
-        <v>7050023</v>
+        <v>7049888</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19457,10 +19452,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129633455</v>
+        <v>129633417</v>
       </c>
       <c r="B187" t="n">
-        <v>80193</v>
+        <v>57740</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19468,21 +19463,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19492,10 +19487,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>425628</v>
+        <v>425822</v>
       </c>
       <c r="R187" t="n">
-        <v>7050057</v>
+        <v>7050023</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19528,6 +19523,11 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -23161,32 +23161,32 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129672484</v>
+        <v>129672467</v>
       </c>
       <c r="B224" t="n">
-        <v>78111</v>
+        <v>79343</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>314</v>
+        <v>6459</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -23196,10 +23196,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>425661</v>
+        <v>425491</v>
       </c>
       <c r="R224" t="n">
-        <v>7050268</v>
+        <v>7049816</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23258,32 +23258,32 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129672483</v>
+        <v>129672505</v>
       </c>
       <c r="B225" t="n">
-        <v>96023</v>
+        <v>78100</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>2809</v>
+        <v>228579</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23293,10 +23293,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>425601</v>
+        <v>425524</v>
       </c>
       <c r="R225" t="n">
-        <v>7050195</v>
+        <v>7049845</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23339,6 +23339,11 @@
       </c>
       <c r="AG225" t="b">
         <v>0</v>
+      </c>
+      <c r="AO225" t="inlineStr">
+        <is>
+          <t>barken på gammal gran</t>
+        </is>
       </c>
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
@@ -23355,32 +23360,32 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129672480</v>
+        <v>129672484</v>
       </c>
       <c r="B226" t="n">
-        <v>75071</v>
+        <v>78111</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6428</v>
+        <v>314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23390,10 +23395,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>425403</v>
+        <v>425661</v>
       </c>
       <c r="R226" t="n">
-        <v>7049803</v>
+        <v>7050268</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23436,11 +23441,6 @@
       </c>
       <c r="AG226" t="b">
         <v>0</v>
-      </c>
-      <c r="AO226" t="inlineStr">
-        <is>
-          <t>Grankvist</t>
-        </is>
       </c>
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
@@ -23457,10 +23457,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129672449</v>
+        <v>129672483</v>
       </c>
       <c r="B227" t="n">
-        <v>75071</v>
+        <v>96023</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23468,21 +23468,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6428</v>
+        <v>2809</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23492,10 +23492,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>425715</v>
+        <v>425601</v>
       </c>
       <c r="R227" t="n">
-        <v>7050177</v>
+        <v>7050195</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23554,10 +23554,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129672467</v>
+        <v>129672480</v>
       </c>
       <c r="B228" t="n">
-        <v>79343</v>
+        <v>75071</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -23565,21 +23565,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6459</v>
+        <v>6428</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23589,10 +23589,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>425491</v>
+        <v>425403</v>
       </c>
       <c r="R228" t="n">
-        <v>7049816</v>
+        <v>7049803</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23635,6 +23635,11 @@
       </c>
       <c r="AG228" t="b">
         <v>0</v>
+      </c>
+      <c r="AO228" t="inlineStr">
+        <is>
+          <t>Grankvist</t>
+        </is>
       </c>
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
@@ -23651,32 +23656,32 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129672505</v>
+        <v>129672449</v>
       </c>
       <c r="B229" t="n">
-        <v>78100</v>
+        <v>75071</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>228579</v>
+        <v>6428</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23686,10 +23691,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>425524</v>
+        <v>425715</v>
       </c>
       <c r="R229" t="n">
-        <v>7049845</v>
+        <v>7050177</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23732,11 +23737,6 @@
       </c>
       <c r="AG229" t="b">
         <v>0</v>
-      </c>
-      <c r="AO229" t="inlineStr">
-        <is>
-          <t>barken på gammal gran</t>
-        </is>
       </c>
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
@@ -25494,32 +25494,32 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>129672490</v>
+        <v>129672453</v>
       </c>
       <c r="B248" t="n">
-        <v>92323</v>
+        <v>79558</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>3298</v>
+        <v>1797</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -25529,10 +25529,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>425697</v>
+        <v>425710</v>
       </c>
       <c r="R248" t="n">
-        <v>7050149</v>
+        <v>7050150</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25591,32 +25591,32 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>129672453</v>
+        <v>129672490</v>
       </c>
       <c r="B249" t="n">
-        <v>79558</v>
+        <v>92323</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>1797</v>
+        <v>3298</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -25626,10 +25626,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>425710</v>
+        <v>425697</v>
       </c>
       <c r="R249" t="n">
-        <v>7050150</v>
+        <v>7050149</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25883,32 +25883,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>129672451</v>
+        <v>129672507</v>
       </c>
       <c r="B252" t="n">
-        <v>92560</v>
+        <v>79168</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>4769</v>
+        <v>283</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25918,10 +25918,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>425710</v>
+        <v>425450</v>
       </c>
       <c r="R252" t="n">
-        <v>7050150</v>
+        <v>7049825</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25980,7 +25980,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>129672507</v>
+        <v>129672506</v>
       </c>
       <c r="B253" t="n">
         <v>79168</v>
@@ -26015,10 +26015,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>425450</v>
+        <v>425480</v>
       </c>
       <c r="R253" t="n">
-        <v>7049825</v>
+        <v>7049813</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26077,32 +26077,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>129672506</v>
+        <v>129672451</v>
       </c>
       <c r="B254" t="n">
-        <v>79168</v>
+        <v>92560</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>283</v>
+        <v>4769</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26112,10 +26112,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>425480</v>
+        <v>425710</v>
       </c>
       <c r="R254" t="n">
-        <v>7049813</v>
+        <v>7050150</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>

--- a/artfynd/A 47880-2025 artfynd.xlsx
+++ b/artfynd/A 47880-2025 artfynd.xlsx
@@ -1197,10 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129628998</v>
+        <v>129627370</v>
       </c>
       <c r="B7" t="n">
-        <v>79558</v>
+        <v>78100</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1208,21 +1208,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1797</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>425339</v>
+        <v>425453</v>
       </c>
       <c r="R7" t="n">
-        <v>7049780</v>
+        <v>7049864</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På grov gren på gammal levande gran i gammal granskog</t>
+          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,22 +1287,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129628961</v>
+        <v>129627377</v>
       </c>
       <c r="B8" t="n">
-        <v>57740</v>
+        <v>91625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1310,23 +1310,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1334,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>425479</v>
+        <v>425701</v>
       </c>
       <c r="R8" t="n">
-        <v>7049837</v>
+        <v>7050250</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,7 +1370,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gammal levande gran i gammal granskog, även på rötter</t>
+          <t>På granhögstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,7 +1385,7 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1401,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129627370</v>
+        <v>129628998</v>
       </c>
       <c r="B9" t="n">
-        <v>78100</v>
+        <v>79558</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1412,21 +1408,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>1797</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1436,10 +1432,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>425453</v>
+        <v>425339</v>
       </c>
       <c r="R9" t="n">
-        <v>7049864</v>
+        <v>7049780</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,7 +1472,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>På grov gren på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,12 +1487,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1709,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129627377</v>
+        <v>129628961</v>
       </c>
       <c r="B12" t="n">
-        <v>91625</v>
+        <v>57740</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1720,19 +1716,23 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>425701</v>
+        <v>425479</v>
       </c>
       <c r="R12" t="n">
-        <v>7050250</v>
+        <v>7049837</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På granhögstubbe</t>
+          <t>Äldre ringhack på gammal levande gran i gammal granskog, även på rötter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,7 +1795,7 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -2426,7 +2426,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129627369</v>
+        <v>129628997</v>
       </c>
       <c r="B19" t="n">
         <v>79558</v>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>425420</v>
+        <v>425393</v>
       </c>
       <c r="R19" t="n">
-        <v>7049825</v>
+        <v>7049812</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,22 +2516,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129628954</v>
+        <v>129627369</v>
       </c>
       <c r="B20" t="n">
-        <v>83058</v>
+        <v>79558</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2539,21 +2539,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>1797</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>425469</v>
+        <v>425420</v>
       </c>
       <c r="R20" t="n">
-        <v>7049817</v>
+        <v>7049825</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2618,44 +2618,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129628984</v>
+        <v>129627375</v>
       </c>
       <c r="B21" t="n">
-        <v>80220</v>
+        <v>91601</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>425327</v>
+        <v>425697</v>
       </c>
       <c r="R21" t="n">
-        <v>7049709</v>
+        <v>7050004</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2720,7 +2720,7 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -2732,45 +2732,56 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129628997</v>
+        <v>129627361</v>
       </c>
       <c r="B22" t="n">
-        <v>79558</v>
+        <v>79246</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1797</v>
+        <v>1249</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>425393</v>
+        <v>425570</v>
       </c>
       <c r="R22" t="n">
-        <v>7049812</v>
+        <v>7049933</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2807,7 +2818,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2816,25 +2827,26 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129627375</v>
+        <v>129629009</v>
       </c>
       <c r="B23" t="n">
         <v>91601</v>
@@ -2869,10 +2881,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>425697</v>
+        <v>425707</v>
       </c>
       <c r="R23" t="n">
-        <v>7050004</v>
+        <v>7050031</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2909,7 +2921,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2924,7 +2936,7 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -2936,56 +2948,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129627361</v>
+        <v>129628954</v>
       </c>
       <c r="B24" t="n">
-        <v>79246</v>
+        <v>83058</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1249</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>425570</v>
+        <v>425469</v>
       </c>
       <c r="R24" t="n">
-        <v>7049933</v>
+        <v>7049817</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3022,7 +3023,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3031,51 +3032,50 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129629009</v>
+        <v>129628984</v>
       </c>
       <c r="B25" t="n">
-        <v>91601</v>
+        <v>80220</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>425707</v>
+        <v>425327</v>
       </c>
       <c r="R25" t="n">
-        <v>7050031</v>
+        <v>7049709</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3254,53 +3254,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129627363</v>
+        <v>129627342</v>
       </c>
       <c r="B27" t="n">
-        <v>79246</v>
+        <v>92323</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1249</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>425428</v>
+        <v>425473</v>
       </c>
       <c r="R27" t="n">
         <v>7049830</v>
@@ -3340,7 +3329,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>vid västsluttning och vattenkälla</t>
+          <t>på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3368,45 +3357,56 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129628988</v>
+        <v>129627363</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>79246</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>425724</v>
+        <v>425428</v>
       </c>
       <c r="R28" t="n">
-        <v>7050035</v>
+        <v>7049830</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>på gran i gammal granskog</t>
+          <t>vid västsluttning och vattenkälla</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3452,50 +3452,51 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129629025</v>
+        <v>129628988</v>
       </c>
       <c r="B29" t="n">
-        <v>83041</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3505,10 +3506,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>425717</v>
+        <v>425724</v>
       </c>
       <c r="R29" t="n">
-        <v>7050119</v>
+        <v>7050035</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3545,7 +3546,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På ved i hålighet vid basen av gammal död gran</t>
+          <t>på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3878,10 +3879,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129627342</v>
+        <v>129629025</v>
       </c>
       <c r="B33" t="n">
-        <v>92323</v>
+        <v>83041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3889,21 +3890,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3298</v>
+        <v>6439</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3913,10 +3914,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>425473</v>
+        <v>425717</v>
       </c>
       <c r="R33" t="n">
-        <v>7049830</v>
+        <v>7050119</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3953,7 +3954,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>på gran i gammal granskog</t>
+          <t>På ved i hålighet vid basen av gammal död gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3962,75 +3963,63 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129627347</v>
+        <v>129627336</v>
       </c>
       <c r="B34" t="n">
-        <v>92560</v>
+        <v>83058</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4769</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>425707</v>
+        <v>425710</v>
       </c>
       <c r="R34" t="n">
-        <v>7050150</v>
+        <v>7050275</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4065,13 +4054,17 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4090,32 +4083,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129627337</v>
+        <v>129628956</v>
       </c>
       <c r="B35" t="n">
-        <v>91569</v>
+        <v>83058</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4125,10 +4118,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>425649</v>
+        <v>425268</v>
       </c>
       <c r="R35" t="n">
-        <v>7049974</v>
+        <v>7049748</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4163,31 +4156,37 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627336</v>
+        <v>129628979</v>
       </c>
       <c r="B36" t="n">
         <v>83058</v>
@@ -4222,10 +4221,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>425710</v>
+        <v>425716</v>
       </c>
       <c r="R36" t="n">
-        <v>7050275</v>
+        <v>7050121</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4262,7 +4261,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>på gammal levande gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4277,44 +4276,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129628956</v>
+        <v>129628965</v>
       </c>
       <c r="B37" t="n">
-        <v>83058</v>
+        <v>83056</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>6486</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4324,10 +4323,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>425268</v>
+        <v>425510</v>
       </c>
       <c r="R37" t="n">
-        <v>7049748</v>
+        <v>7049849</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4364,7 +4363,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal levande grov gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4373,7 +4372,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4392,10 +4390,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129628979</v>
+        <v>129628980</v>
       </c>
       <c r="B38" t="n">
-        <v>83058</v>
+        <v>78100</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4403,21 +4401,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4494,32 +4492,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129628980</v>
+        <v>129628982</v>
       </c>
       <c r="B39" t="n">
-        <v>78100</v>
+        <v>79246</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>1249</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4529,10 +4527,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>425716</v>
+        <v>425718</v>
       </c>
       <c r="R39" t="n">
-        <v>7050121</v>
+        <v>7050119</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4569,7 +4567,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>på gammal levande gran</t>
+          <t>Två mycket stora bålar på grova grenar på gammal levande gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4596,45 +4594,56 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129628982</v>
+        <v>129627347</v>
       </c>
       <c r="B40" t="n">
-        <v>79246</v>
+        <v>92560</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1249</v>
+        <v>4769</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>425718</v>
+        <v>425707</v>
       </c>
       <c r="R40" t="n">
-        <v>7050119</v>
+        <v>7050150</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4669,61 +4678,57 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Två mycket stora bålar på grova grenar på gammal levande gran</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129628971</v>
+        <v>129627337</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>91569</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4733,10 +4738,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>425704</v>
+        <v>425649</v>
       </c>
       <c r="R41" t="n">
-        <v>7050246</v>
+        <v>7049974</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4771,11 +4776,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>på gammal gran i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4788,44 +4788,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129628965</v>
+        <v>129628971</v>
       </c>
       <c r="B42" t="n">
-        <v>83056</v>
+        <v>79087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>425510</v>
+        <v>425704</v>
       </c>
       <c r="R42" t="n">
-        <v>7049849</v>
+        <v>7050246</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4875,7 +4875,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal levande grov gran i gammal fuktig granskog</t>
+          <t>på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -7979,32 +7979,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129627371</v>
+        <v>129629003</v>
       </c>
       <c r="B73" t="n">
-        <v>78446</v>
+        <v>78100</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>498</v>
+        <v>228579</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>425692</v>
+        <v>425395</v>
       </c>
       <c r="R73" t="n">
-        <v>7050251</v>
+        <v>7049812</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På gammal gran vid ett rikkärr</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8069,44 +8069,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129628993</v>
+        <v>129627371</v>
       </c>
       <c r="B74" t="n">
-        <v>79558</v>
+        <v>78446</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1797</v>
+        <v>498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>425721</v>
+        <v>425692</v>
       </c>
       <c r="R74" t="n">
-        <v>7050017</v>
+        <v>7050251</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran vid ett rikkärr</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8171,44 +8171,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129628959</v>
+        <v>129628993</v>
       </c>
       <c r="B75" t="n">
-        <v>92323</v>
+        <v>79558</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3298</v>
+        <v>1797</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>425626</v>
+        <v>425721</v>
       </c>
       <c r="R75" t="n">
-        <v>7050243</v>
+        <v>7050017</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8258,7 +8258,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8285,56 +8285,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129627364</v>
+        <v>129628959</v>
       </c>
       <c r="B76" t="n">
-        <v>79246</v>
+        <v>92323</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1249</v>
+        <v>3298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>425392</v>
+        <v>425626</v>
       </c>
       <c r="R76" t="n">
-        <v>7049820</v>
+        <v>7050243</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8371,7 +8360,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8380,64 +8369,74 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129629003</v>
+        <v>129627364</v>
       </c>
       <c r="B77" t="n">
-        <v>78100</v>
+        <v>79246</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228579</v>
+        <v>1249</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>425395</v>
+        <v>425392</v>
       </c>
       <c r="R77" t="n">
-        <v>7049812</v>
+        <v>7049820</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8474,7 +8473,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8483,18 +8482,19 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -10563,10 +10563,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129628953</v>
+        <v>129629033</v>
       </c>
       <c r="B98" t="n">
-        <v>83058</v>
+        <v>78100</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10574,21 +10574,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>425660</v>
+        <v>425685</v>
       </c>
       <c r="R98" t="n">
-        <v>7050271</v>
+        <v>7050259</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10638,7 +10638,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>på gammal levande gran i gammal granskog vid rikkärr vid sjö</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10665,32 +10665,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129629029</v>
+        <v>129628953</v>
       </c>
       <c r="B99" t="n">
-        <v>83041</v>
+        <v>83058</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10700,10 +10700,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>425332</v>
+        <v>425660</v>
       </c>
       <c r="R99" t="n">
-        <v>7049768</v>
+        <v>7050271</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>På bark på björkhögstubbe i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10767,32 +10767,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129629033</v>
+        <v>129629029</v>
       </c>
       <c r="B100" t="n">
-        <v>78100</v>
+        <v>83041</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228579</v>
+        <v>6439</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10802,10 +10802,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>425685</v>
+        <v>425332</v>
       </c>
       <c r="R100" t="n">
-        <v>7050259</v>
+        <v>7049768</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>på gammal levande gran i gammal granskog vid rikkärr vid sjö</t>
+          <t>På bark på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11175,10 +11175,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129629012</v>
+        <v>129628990</v>
       </c>
       <c r="B104" t="n">
-        <v>91601</v>
+        <v>78100</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11186,21 +11186,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1108</v>
+        <v>228579</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11210,10 +11210,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>425698</v>
+        <v>425724</v>
       </c>
       <c r="R104" t="n">
-        <v>7049997</v>
+        <v>7050035</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>På död och levande gammal gran i gammal granskog</t>
+          <t>på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11277,10 +11277,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129628991</v>
+        <v>129629012</v>
       </c>
       <c r="B105" t="n">
-        <v>79558</v>
+        <v>91601</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11288,21 +11288,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1797</v>
+        <v>1108</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11312,10 +11312,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>425724</v>
+        <v>425698</v>
       </c>
       <c r="R105" t="n">
-        <v>7050035</v>
+        <v>7049997</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På två gamla granar i gammal granskog</t>
+          <t>På död och levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11379,7 +11379,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129627367</v>
+        <v>129628991</v>
       </c>
       <c r="B106" t="n">
         <v>79558</v>
@@ -11414,10 +11414,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>425618</v>
+        <v>425724</v>
       </c>
       <c r="R106" t="n">
-        <v>7049902</v>
+        <v>7050035</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På två gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11469,22 +11469,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129628990</v>
+        <v>129627367</v>
       </c>
       <c r="B107" t="n">
-        <v>78100</v>
+        <v>79558</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11492,21 +11492,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228579</v>
+        <v>1797</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11516,10 +11516,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>425724</v>
+        <v>425618</v>
       </c>
       <c r="R107" t="n">
-        <v>7050035</v>
+        <v>7049902</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11556,7 +11556,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>på gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11571,12 +11571,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -13664,32 +13664,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129633385</v>
+        <v>129633471</v>
       </c>
       <c r="B129" t="n">
-        <v>92323</v>
+        <v>91601</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13699,10 +13699,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>425773</v>
+        <v>425534</v>
       </c>
       <c r="R129" t="n">
-        <v>7050160</v>
+        <v>7050039</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13761,7 +13761,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129633471</v>
+        <v>129633466</v>
       </c>
       <c r="B130" t="n">
         <v>91601</v>
@@ -13796,10 +13796,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>425534</v>
+        <v>426016</v>
       </c>
       <c r="R130" t="n">
-        <v>7050039</v>
+        <v>7050154</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13858,10 +13858,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129633466</v>
+        <v>129633439</v>
       </c>
       <c r="B131" t="n">
-        <v>91601</v>
+        <v>57740</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13869,21 +13869,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13893,10 +13893,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>426016</v>
+        <v>425357</v>
       </c>
       <c r="R131" t="n">
-        <v>7050154</v>
+        <v>7050155</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13929,6 +13929,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13955,7 +13960,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129633404</v>
+        <v>129633447</v>
       </c>
       <c r="B132" t="n">
         <v>57740</v>
@@ -13990,10 +13995,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>425682</v>
+        <v>425526</v>
       </c>
       <c r="R132" t="n">
-        <v>7050073</v>
+        <v>7050117</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14057,7 +14062,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129633439</v>
+        <v>129633413</v>
       </c>
       <c r="B133" t="n">
         <v>57740</v>
@@ -14092,10 +14097,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>425357</v>
+        <v>425870</v>
       </c>
       <c r="R133" t="n">
-        <v>7050155</v>
+        <v>7050230</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14159,32 +14164,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129633447</v>
+        <v>129633385</v>
       </c>
       <c r="B134" t="n">
-        <v>57740</v>
+        <v>92323</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14194,10 +14199,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>425526</v>
+        <v>425773</v>
       </c>
       <c r="R134" t="n">
-        <v>7050117</v>
+        <v>7050160</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14230,11 +14235,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14261,7 +14261,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129633413</v>
+        <v>129633404</v>
       </c>
       <c r="B135" t="n">
         <v>57740</v>
@@ -14296,10 +14296,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>425870</v>
+        <v>425682</v>
       </c>
       <c r="R135" t="n">
-        <v>7050230</v>
+        <v>7050073</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14363,10 +14363,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129633468</v>
+        <v>129633419</v>
       </c>
       <c r="B136" t="n">
-        <v>91601</v>
+        <v>57740</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14374,21 +14374,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14398,10 +14398,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>425549</v>
+        <v>425609</v>
       </c>
       <c r="R136" t="n">
-        <v>7050165</v>
+        <v>7049867</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14434,6 +14434,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14460,7 +14465,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129633419</v>
+        <v>129633403</v>
       </c>
       <c r="B137" t="n">
         <v>57740</v>
@@ -14495,10 +14500,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>425609</v>
+        <v>425668</v>
       </c>
       <c r="R137" t="n">
-        <v>7049867</v>
+        <v>7050116</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14535,7 +14540,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14562,10 +14567,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129633403</v>
+        <v>129633468</v>
       </c>
       <c r="B138" t="n">
-        <v>57740</v>
+        <v>91601</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14573,21 +14578,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14597,10 +14602,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>425668</v>
+        <v>425549</v>
       </c>
       <c r="R138" t="n">
-        <v>7050116</v>
+        <v>7050165</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14633,11 +14638,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14664,49 +14664,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129627372</v>
+        <v>129633416</v>
       </c>
       <c r="B139" t="n">
-        <v>95454</v>
+        <v>57740</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2412</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
+          <t>Stor-grässjön s, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>425708</v>
+        <v>425828</v>
       </c>
       <c r="R139" t="n">
-        <v>7050205</v>
+        <v>7050054</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14743,7 +14739,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>på marken i kärr</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14752,29 +14748,28 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129633394</v>
+        <v>129627372</v>
       </c>
       <c r="B140" t="n">
-        <v>92323</v>
+        <v>95454</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14782,34 +14777,38 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3298</v>
+        <v>2412</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Stor-grässjön s, Jmt</t>
+          <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>425325</v>
+        <v>425708</v>
       </c>
       <c r="R140" t="n">
-        <v>7049857</v>
+        <v>7050205</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14844,31 +14843,37 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>på marken i kärr</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129633386</v>
+        <v>129633394</v>
       </c>
       <c r="B141" t="n">
         <v>92323</v>
@@ -14903,10 +14908,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>425587</v>
+        <v>425325</v>
       </c>
       <c r="R141" t="n">
-        <v>7050138</v>
+        <v>7049857</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14965,32 +14970,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129633421</v>
+        <v>129633386</v>
       </c>
       <c r="B142" t="n">
-        <v>57740</v>
+        <v>92323</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15000,10 +15005,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>425262</v>
+        <v>425587</v>
       </c>
       <c r="R142" t="n">
-        <v>7049782</v>
+        <v>7050138</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15036,11 +15041,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15067,7 +15067,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129633415</v>
+        <v>129633421</v>
       </c>
       <c r="B143" t="n">
         <v>57740</v>
@@ -15102,10 +15102,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>426074</v>
+        <v>425262</v>
       </c>
       <c r="R143" t="n">
-        <v>7050193</v>
+        <v>7049782</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15142,7 +15142,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15169,7 +15169,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129633416</v>
+        <v>129633415</v>
       </c>
       <c r="B144" t="n">
         <v>57740</v>
@@ -15204,10 +15204,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>425828</v>
+        <v>426074</v>
       </c>
       <c r="R144" t="n">
-        <v>7050054</v>
+        <v>7050193</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15244,7 +15244,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16854,32 +16854,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129633392</v>
+        <v>129633450</v>
       </c>
       <c r="B161" t="n">
-        <v>92323</v>
+        <v>57740</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16889,10 +16889,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>425789</v>
+        <v>425517</v>
       </c>
       <c r="R161" t="n">
-        <v>7050048</v>
+        <v>7050099</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16925,6 +16925,11 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16951,7 +16956,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129633450</v>
+        <v>129633427</v>
       </c>
       <c r="B162" t="n">
         <v>57740</v>
@@ -16986,10 +16991,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>425517</v>
+        <v>425572</v>
       </c>
       <c r="R162" t="n">
-        <v>7050099</v>
+        <v>7049987</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17026,7 +17031,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17053,32 +17058,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129633427</v>
+        <v>129633392</v>
       </c>
       <c r="B163" t="n">
-        <v>57740</v>
+        <v>92323</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17088,10 +17093,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>425572</v>
+        <v>425789</v>
       </c>
       <c r="R163" t="n">
-        <v>7049987</v>
+        <v>7050048</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17124,11 +17129,6 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -20549,32 +20549,32 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129633470</v>
+        <v>129633475</v>
       </c>
       <c r="B198" t="n">
-        <v>91601</v>
+        <v>91978</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1108</v>
+        <v>2063</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20584,10 +20584,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>425383</v>
+        <v>425690</v>
       </c>
       <c r="R198" t="n">
-        <v>7050135</v>
+        <v>7050235</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20646,7 +20646,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129633462</v>
+        <v>129633470</v>
       </c>
       <c r="B199" t="n">
         <v>91601</v>
@@ -20681,10 +20681,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>425779</v>
+        <v>425383</v>
       </c>
       <c r="R199" t="n">
-        <v>7050242</v>
+        <v>7050135</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20743,32 +20743,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129633475</v>
+        <v>129633462</v>
       </c>
       <c r="B200" t="n">
-        <v>91978</v>
+        <v>91601</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>2063</v>
+        <v>1108</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20778,10 +20778,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>425690</v>
+        <v>425779</v>
       </c>
       <c r="R200" t="n">
-        <v>7050235</v>
+        <v>7050242</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20840,7 +20840,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129633400</v>
+        <v>129633437</v>
       </c>
       <c r="B201" t="n">
         <v>57740</v>
@@ -20875,10 +20875,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>425596</v>
+        <v>425347</v>
       </c>
       <c r="R201" t="n">
-        <v>7049933</v>
+        <v>7050132</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20915,7 +20915,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -20942,7 +20942,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129633409</v>
+        <v>129633400</v>
       </c>
       <c r="B202" t="n">
         <v>57740</v>
@@ -20977,10 +20977,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>425616</v>
+        <v>425596</v>
       </c>
       <c r="R202" t="n">
-        <v>7050151</v>
+        <v>7049933</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21017,7 +21017,7 @@
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21044,7 +21044,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129633437</v>
+        <v>129633409</v>
       </c>
       <c r="B203" t="n">
         <v>57740</v>
@@ -21079,10 +21079,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>425347</v>
+        <v>425616</v>
       </c>
       <c r="R203" t="n">
-        <v>7050132</v>
+        <v>7050151</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21119,7 +21119,7 @@
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21967,32 +21967,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129672486</v>
+        <v>129672514</v>
       </c>
       <c r="B212" t="n">
-        <v>96023</v>
+        <v>83058</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22002,10 +22002,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>425724</v>
+        <v>425292</v>
       </c>
       <c r="R212" t="n">
-        <v>7050188</v>
+        <v>7049741</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22064,32 +22064,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129672472</v>
+        <v>129672499</v>
       </c>
       <c r="B213" t="n">
-        <v>75192</v>
+        <v>83058</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>1776</v>
+        <v>6440</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22099,10 +22099,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>425341</v>
+        <v>425535</v>
       </c>
       <c r="R213" t="n">
-        <v>7049761</v>
+        <v>7049926</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22145,21 +22145,6 @@
       </c>
       <c r="AG213" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ213" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK213" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO213" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
@@ -22176,32 +22161,32 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129672514</v>
+        <v>129672486</v>
       </c>
       <c r="B214" t="n">
-        <v>83058</v>
+        <v>96023</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6440</v>
+        <v>2809</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22211,10 +22196,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>425292</v>
+        <v>425724</v>
       </c>
       <c r="R214" t="n">
-        <v>7049741</v>
+        <v>7050188</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22273,32 +22258,32 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129672499</v>
+        <v>129672472</v>
       </c>
       <c r="B215" t="n">
-        <v>83058</v>
+        <v>75192</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6440</v>
+        <v>1776</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -22308,10 +22293,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>425535</v>
+        <v>425341</v>
       </c>
       <c r="R215" t="n">
-        <v>7049926</v>
+        <v>7049761</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22354,6 +22339,21 @@
       </c>
       <c r="AG215" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO215" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
@@ -25688,32 +25688,32 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>129672447</v>
+        <v>129672481</v>
       </c>
       <c r="B250" t="n">
-        <v>75192</v>
+        <v>97043</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>1776</v>
+        <v>53</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -25723,10 +25723,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>425702</v>
+        <v>425594</v>
       </c>
       <c r="R250" t="n">
-        <v>7050232</v>
+        <v>7050152</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25767,7 +25767,6 @@
       <c r="AE250" t="b">
         <v>0</v>
       </c>
-      <c r="AF250" t="inlineStr"/>
       <c r="AG250" t="b">
         <v>0</v>
       </c>
@@ -25786,32 +25785,32 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>129672481</v>
+        <v>129672447</v>
       </c>
       <c r="B251" t="n">
-        <v>97043</v>
+        <v>75192</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>53</v>
+        <v>1776</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -25821,10 +25820,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>425594</v>
+        <v>425702</v>
       </c>
       <c r="R251" t="n">
-        <v>7050152</v>
+        <v>7050232</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25865,6 +25864,7 @@
       <c r="AE251" t="b">
         <v>0</v>
       </c>
+      <c r="AF251" t="inlineStr"/>
       <c r="AG251" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47880-2025 artfynd.xlsx
+++ b/artfynd/A 47880-2025 artfynd.xlsx
@@ -11586,7 +11586,7 @@
         <v>129633479</v>
       </c>
       <c r="B108" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>129633458</v>
       </c>
       <c r="B110" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129633408</v>
+        <v>129633424</v>
       </c>
       <c r="B111" t="n">
         <v>57740</v>
@@ -11910,10 +11910,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>425784</v>
+        <v>425413</v>
       </c>
       <c r="R111" t="n">
-        <v>7050165</v>
+        <v>7049880</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12079,7 +12079,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129633442</v>
+        <v>129633408</v>
       </c>
       <c r="B113" t="n">
         <v>57740</v>
@@ -12114,10 +12114,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>425406</v>
+        <v>425784</v>
       </c>
       <c r="R113" t="n">
-        <v>7050149</v>
+        <v>7050165</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12181,7 +12181,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129633424</v>
+        <v>129633442</v>
       </c>
       <c r="B114" t="n">
         <v>57740</v>
@@ -12216,10 +12216,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>425413</v>
+        <v>425406</v>
       </c>
       <c r="R114" t="n">
-        <v>7049880</v>
+        <v>7050149</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12286,7 +12286,7 @@
         <v>129633478</v>
       </c>
       <c r="B115" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129633440</v>
+        <v>129633397</v>
       </c>
       <c r="B116" t="n">
         <v>57740</v>
@@ -12411,10 +12411,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>425382</v>
+        <v>425248</v>
       </c>
       <c r="R116" t="n">
-        <v>7050178</v>
+        <v>7049758</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12451,7 +12451,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12478,7 +12478,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129633397</v>
+        <v>129633402</v>
       </c>
       <c r="B117" t="n">
         <v>57740</v>
@@ -12513,10 +12513,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>425248</v>
+        <v>425645</v>
       </c>
       <c r="R117" t="n">
-        <v>7049758</v>
+        <v>7050096</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12553,7 +12553,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12580,7 +12580,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129633402</v>
+        <v>129633440</v>
       </c>
       <c r="B118" t="n">
         <v>57740</v>
@@ -12615,10 +12615,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>425645</v>
+        <v>425382</v>
       </c>
       <c r="R118" t="n">
-        <v>7050096</v>
+        <v>7050178</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12655,7 +12655,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12685,7 +12685,7 @@
         <v>129633456</v>
       </c>
       <c r="B119" t="n">
-        <v>79246</v>
+        <v>79247</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12779,10 +12779,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129633477</v>
+        <v>129633435</v>
       </c>
       <c r="B120" t="n">
-        <v>91625</v>
+        <v>57740</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12790,19 +12790,23 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -12810,10 +12814,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>425690</v>
+        <v>425324</v>
       </c>
       <c r="R120" t="n">
-        <v>7050235</v>
+        <v>7050192</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12846,6 +12850,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12872,10 +12881,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129633476</v>
+        <v>129633445</v>
       </c>
       <c r="B121" t="n">
-        <v>91625</v>
+        <v>57740</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12883,19 +12892,23 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -12903,10 +12916,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>425617</v>
+        <v>425490</v>
       </c>
       <c r="R121" t="n">
-        <v>7050214</v>
+        <v>7050129</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12939,6 +12952,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13067,10 +13085,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129633435</v>
+        <v>129633476</v>
       </c>
       <c r="B123" t="n">
-        <v>57740</v>
+        <v>91626</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13078,23 +13096,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13102,10 +13116,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>425324</v>
+        <v>425617</v>
       </c>
       <c r="R123" t="n">
-        <v>7050192</v>
+        <v>7050214</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13138,11 +13152,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13169,10 +13178,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129633445</v>
+        <v>129633477</v>
       </c>
       <c r="B124" t="n">
-        <v>57740</v>
+        <v>91626</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13180,23 +13189,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13204,10 +13209,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>425490</v>
+        <v>425690</v>
       </c>
       <c r="R124" t="n">
-        <v>7050129</v>
+        <v>7050235</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13240,11 +13245,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13271,32 +13271,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129633389</v>
+        <v>129633420</v>
       </c>
       <c r="B125" t="n">
-        <v>92323</v>
+        <v>57740</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13306,10 +13306,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>425870</v>
+        <v>425481</v>
       </c>
       <c r="R125" t="n">
-        <v>7050232</v>
+        <v>7049835</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13342,6 +13342,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13368,32 +13373,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129633460</v>
+        <v>129633389</v>
       </c>
       <c r="B126" t="n">
-        <v>91601</v>
+        <v>92324</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13403,10 +13408,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>425741</v>
+        <v>425870</v>
       </c>
       <c r="R126" t="n">
-        <v>7050015</v>
+        <v>7050232</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13465,10 +13470,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129633459</v>
+        <v>129633460</v>
       </c>
       <c r="B127" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13500,10 +13505,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>425702</v>
+        <v>425741</v>
       </c>
       <c r="R127" t="n">
-        <v>7050011</v>
+        <v>7050015</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13562,10 +13567,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129633420</v>
+        <v>129633459</v>
       </c>
       <c r="B128" t="n">
-        <v>57740</v>
+        <v>91602</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13573,21 +13578,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13597,10 +13602,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>425481</v>
+        <v>425702</v>
       </c>
       <c r="R128" t="n">
-        <v>7049835</v>
+        <v>7050011</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13633,11 +13638,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13664,10 +13664,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129633471</v>
+        <v>129633413</v>
       </c>
       <c r="B129" t="n">
-        <v>91601</v>
+        <v>57740</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13675,21 +13675,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13699,10 +13699,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>425534</v>
+        <v>425870</v>
       </c>
       <c r="R129" t="n">
-        <v>7050039</v>
+        <v>7050230</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13735,6 +13735,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13761,10 +13766,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129633466</v>
+        <v>129633447</v>
       </c>
       <c r="B130" t="n">
-        <v>91601</v>
+        <v>57740</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13772,21 +13777,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13796,10 +13801,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>426016</v>
+        <v>425526</v>
       </c>
       <c r="R130" t="n">
-        <v>7050154</v>
+        <v>7050117</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13832,6 +13837,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13858,7 +13868,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129633439</v>
+        <v>129633404</v>
       </c>
       <c r="B131" t="n">
         <v>57740</v>
@@ -13893,10 +13903,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>425357</v>
+        <v>425682</v>
       </c>
       <c r="R131" t="n">
-        <v>7050155</v>
+        <v>7050073</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13960,7 +13970,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129633447</v>
+        <v>129633439</v>
       </c>
       <c r="B132" t="n">
         <v>57740</v>
@@ -13995,10 +14005,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>425526</v>
+        <v>425357</v>
       </c>
       <c r="R132" t="n">
-        <v>7050117</v>
+        <v>7050155</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14062,32 +14072,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129633413</v>
+        <v>129633385</v>
       </c>
       <c r="B133" t="n">
-        <v>57740</v>
+        <v>92324</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14097,10 +14107,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>425870</v>
+        <v>425773</v>
       </c>
       <c r="R133" t="n">
-        <v>7050230</v>
+        <v>7050160</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14133,11 +14143,6 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14164,32 +14169,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129633385</v>
+        <v>129633471</v>
       </c>
       <c r="B134" t="n">
-        <v>92323</v>
+        <v>91602</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14199,10 +14204,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>425773</v>
+        <v>425534</v>
       </c>
       <c r="R134" t="n">
-        <v>7050160</v>
+        <v>7050039</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14261,10 +14266,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129633404</v>
+        <v>129633466</v>
       </c>
       <c r="B135" t="n">
-        <v>57740</v>
+        <v>91602</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14272,21 +14277,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14296,10 +14301,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>425682</v>
+        <v>426016</v>
       </c>
       <c r="R135" t="n">
-        <v>7050073</v>
+        <v>7050154</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14332,11 +14337,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14363,7 +14363,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129633419</v>
+        <v>129633403</v>
       </c>
       <c r="B136" t="n">
         <v>57740</v>
@@ -14398,10 +14398,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>425609</v>
+        <v>425668</v>
       </c>
       <c r="R136" t="n">
-        <v>7049867</v>
+        <v>7050116</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14438,7 +14438,7 @@
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14465,7 +14465,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129633403</v>
+        <v>129633419</v>
       </c>
       <c r="B137" t="n">
         <v>57740</v>
@@ -14500,10 +14500,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>425668</v>
+        <v>425609</v>
       </c>
       <c r="R137" t="n">
-        <v>7050116</v>
+        <v>7049867</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14570,7 +14570,7 @@
         <v>129633468</v>
       </c>
       <c r="B138" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14664,45 +14664,49 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129633416</v>
+        <v>129627372</v>
       </c>
       <c r="B139" t="n">
-        <v>57740</v>
+        <v>95455</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>2412</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Stor-grässjön s, Jmt</t>
+          <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>425828</v>
+        <v>425708</v>
       </c>
       <c r="R139" t="n">
-        <v>7050054</v>
+        <v>7050205</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14739,7 +14743,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>på marken i kärr</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14748,67 +14752,64 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129627372</v>
+        <v>129633416</v>
       </c>
       <c r="B140" t="n">
-        <v>95454</v>
+        <v>57740</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2412</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Djupsjöberget, NV-sluttning öster om Abborrtjärnen, S. om Stor-Grässjön, Jmt</t>
+          <t>Stor-grässjön s, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>425708</v>
+        <v>425828</v>
       </c>
       <c r="R140" t="n">
-        <v>7050205</v>
+        <v>7050054</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14845,7 +14846,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>på marken i kärr</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14854,51 +14855,50 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129633394</v>
+        <v>129633415</v>
       </c>
       <c r="B141" t="n">
-        <v>92323</v>
+        <v>57740</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14908,10 +14908,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>425325</v>
+        <v>426074</v>
       </c>
       <c r="R141" t="n">
-        <v>7049857</v>
+        <v>7050193</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14944,6 +14944,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14970,32 +14975,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129633386</v>
+        <v>129633436</v>
       </c>
       <c r="B142" t="n">
-        <v>92323</v>
+        <v>57740</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15005,10 +15010,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>425587</v>
+        <v>425329</v>
       </c>
       <c r="R142" t="n">
-        <v>7050138</v>
+        <v>7050182</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15041,6 +15046,11 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15169,32 +15179,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129633415</v>
+        <v>129633394</v>
       </c>
       <c r="B144" t="n">
-        <v>57740</v>
+        <v>92324</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15204,10 +15214,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>426074</v>
+        <v>425325</v>
       </c>
       <c r="R144" t="n">
-        <v>7050193</v>
+        <v>7049857</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15240,11 +15250,6 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15271,32 +15276,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129633436</v>
+        <v>129633386</v>
       </c>
       <c r="B145" t="n">
-        <v>57740</v>
+        <v>92324</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15306,10 +15311,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>425329</v>
+        <v>425587</v>
       </c>
       <c r="R145" t="n">
-        <v>7050182</v>
+        <v>7050138</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15342,11 +15347,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15373,32 +15373,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129633483</v>
+        <v>129633457</v>
       </c>
       <c r="B146" t="n">
-        <v>89004</v>
+        <v>79247</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>510</v>
+        <v>1249</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15408,10 +15408,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>425789</v>
+        <v>425579</v>
       </c>
       <c r="R146" t="n">
-        <v>7050109</v>
+        <v>7049866</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15470,7 +15470,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129633429</v>
+        <v>129633449</v>
       </c>
       <c r="B147" t="n">
         <v>57740</v>
@@ -15505,10 +15505,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>425508</v>
+        <v>425515</v>
       </c>
       <c r="R147" t="n">
-        <v>7050208</v>
+        <v>7050097</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15572,7 +15572,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129633449</v>
+        <v>129633429</v>
       </c>
       <c r="B148" t="n">
         <v>57740</v>
@@ -15607,10 +15607,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>425515</v>
+        <v>425508</v>
       </c>
       <c r="R148" t="n">
-        <v>7050097</v>
+        <v>7050208</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15677,7 +15677,7 @@
         <v>129633396</v>
       </c>
       <c r="B149" t="n">
-        <v>92323</v>
+        <v>92324</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15771,32 +15771,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129633457</v>
+        <v>129633483</v>
       </c>
       <c r="B150" t="n">
-        <v>79246</v>
+        <v>89005</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1249</v>
+        <v>510</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15806,10 +15806,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>425579</v>
+        <v>425789</v>
       </c>
       <c r="R150" t="n">
-        <v>7049866</v>
+        <v>7050109</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15871,7 +15871,7 @@
         <v>129633393</v>
       </c>
       <c r="B151" t="n">
-        <v>92323</v>
+        <v>92324</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15965,10 +15965,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129633448</v>
+        <v>129633481</v>
       </c>
       <c r="B152" t="n">
-        <v>57740</v>
+        <v>91626</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15976,23 +15976,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
@@ -16000,10 +15996,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>425518</v>
+        <v>425411</v>
       </c>
       <c r="R152" t="n">
-        <v>7050117</v>
+        <v>7050144</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16036,11 +16032,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16067,7 +16058,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129633426</v>
+        <v>129633448</v>
       </c>
       <c r="B153" t="n">
         <v>57740</v>
@@ -16102,10 +16093,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>425567</v>
+        <v>425518</v>
       </c>
       <c r="R153" t="n">
-        <v>7049949</v>
+        <v>7050117</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16142,7 +16133,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16169,10 +16160,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129633481</v>
+        <v>129633426</v>
       </c>
       <c r="B154" t="n">
-        <v>91625</v>
+        <v>57740</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16180,19 +16171,23 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
@@ -16200,10 +16195,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>425411</v>
+        <v>425567</v>
       </c>
       <c r="R154" t="n">
-        <v>7050144</v>
+        <v>7049949</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16236,6 +16231,11 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16265,7 +16265,7 @@
         <v>129633463</v>
       </c>
       <c r="B155" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>129633461</v>
       </c>
       <c r="B156" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16456,32 +16456,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129633383</v>
+        <v>129633405</v>
       </c>
       <c r="B157" t="n">
-        <v>92323</v>
+        <v>57740</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16491,10 +16491,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>425676</v>
+        <v>425721</v>
       </c>
       <c r="R157" t="n">
-        <v>7050147</v>
+        <v>7050005</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16527,6 +16527,11 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16553,32 +16558,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129633388</v>
+        <v>129633446</v>
       </c>
       <c r="B158" t="n">
-        <v>92323</v>
+        <v>57740</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16588,10 +16593,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>425864</v>
+        <v>425520</v>
       </c>
       <c r="R158" t="n">
-        <v>7050235</v>
+        <v>7050128</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16624,6 +16629,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16650,32 +16660,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129633405</v>
+        <v>129633383</v>
       </c>
       <c r="B159" t="n">
-        <v>57740</v>
+        <v>92324</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16685,10 +16695,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>425721</v>
+        <v>425676</v>
       </c>
       <c r="R159" t="n">
-        <v>7050005</v>
+        <v>7050147</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16721,11 +16731,6 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16752,32 +16757,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129633446</v>
+        <v>129633388</v>
       </c>
       <c r="B160" t="n">
-        <v>57740</v>
+        <v>92324</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16787,10 +16792,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>425520</v>
+        <v>425864</v>
       </c>
       <c r="R160" t="n">
-        <v>7050128</v>
+        <v>7050235</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16823,11 +16828,6 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16854,7 +16854,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129633450</v>
+        <v>129633427</v>
       </c>
       <c r="B161" t="n">
         <v>57740</v>
@@ -16889,10 +16889,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>425517</v>
+        <v>425572</v>
       </c>
       <c r="R161" t="n">
-        <v>7050099</v>
+        <v>7049987</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16929,7 +16929,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16956,7 +16956,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129633427</v>
+        <v>129633450</v>
       </c>
       <c r="B162" t="n">
         <v>57740</v>
@@ -16991,10 +16991,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>425572</v>
+        <v>425517</v>
       </c>
       <c r="R162" t="n">
-        <v>7049987</v>
+        <v>7050099</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17031,7 +17031,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17061,7 +17061,7 @@
         <v>129633392</v>
       </c>
       <c r="B163" t="n">
-        <v>92323</v>
+        <v>92324</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17155,32 +17155,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129633384</v>
+        <v>129633443</v>
       </c>
       <c r="B164" t="n">
-        <v>92323</v>
+        <v>57740</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17190,10 +17190,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>425714</v>
+        <v>425412</v>
       </c>
       <c r="R164" t="n">
-        <v>7050012</v>
+        <v>7050156</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17226,6 +17226,11 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17252,10 +17257,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129633387</v>
+        <v>129633384</v>
       </c>
       <c r="B165" t="n">
-        <v>92323</v>
+        <v>92324</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17287,10 +17292,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>425585</v>
+        <v>425714</v>
       </c>
       <c r="R165" t="n">
-        <v>7050158</v>
+        <v>7050012</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17349,32 +17354,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129633443</v>
+        <v>129633387</v>
       </c>
       <c r="B166" t="n">
-        <v>57740</v>
+        <v>92324</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17384,10 +17389,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>425412</v>
+        <v>425585</v>
       </c>
       <c r="R166" t="n">
-        <v>7050156</v>
+        <v>7050158</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17420,11 +17425,6 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17451,10 +17451,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129633484</v>
+        <v>129633473</v>
       </c>
       <c r="B167" t="n">
-        <v>89004</v>
+        <v>91602</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17462,21 +17462,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17486,10 +17486,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>425629</v>
+        <v>425218</v>
       </c>
       <c r="R167" t="n">
-        <v>7050220</v>
+        <v>7049873</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17548,10 +17548,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129633480</v>
+        <v>129633484</v>
       </c>
       <c r="B168" t="n">
-        <v>91625</v>
+        <v>89005</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17559,19 +17559,23 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr"/>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
@@ -17579,10 +17583,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>425454</v>
+        <v>425629</v>
       </c>
       <c r="R168" t="n">
-        <v>7050178</v>
+        <v>7050220</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17641,10 +17645,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129633473</v>
+        <v>129633480</v>
       </c>
       <c r="B169" t="n">
-        <v>91601</v>
+        <v>91626</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17652,23 +17656,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
@@ -17676,10 +17676,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>425218</v>
+        <v>425454</v>
       </c>
       <c r="R169" t="n">
-        <v>7049873</v>
+        <v>7050178</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17738,10 +17738,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129633453</v>
+        <v>129633451</v>
       </c>
       <c r="B170" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17749,16 +17749,16 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -17773,10 +17773,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>426018</v>
+        <v>425266</v>
       </c>
       <c r="R170" t="n">
-        <v>7050201</v>
+        <v>7049914</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17813,7 +17813,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17942,10 +17942,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129633451</v>
+        <v>129633453</v>
       </c>
       <c r="B172" t="n">
-        <v>57740</v>
+        <v>57737</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17953,16 +17953,16 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -17977,10 +17977,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>425266</v>
+        <v>426018</v>
       </c>
       <c r="R172" t="n">
-        <v>7049914</v>
+        <v>7050201</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18044,32 +18044,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129633395</v>
+        <v>129633472</v>
       </c>
       <c r="B173" t="n">
-        <v>92323</v>
+        <v>91602</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18079,10 +18079,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>425561</v>
+        <v>425559</v>
       </c>
       <c r="R173" t="n">
-        <v>7050121</v>
+        <v>7050001</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18141,32 +18141,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129633472</v>
+        <v>129633395</v>
       </c>
       <c r="B174" t="n">
-        <v>91601</v>
+        <v>92324</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18176,10 +18176,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>425559</v>
+        <v>425561</v>
       </c>
       <c r="R174" t="n">
-        <v>7050001</v>
+        <v>7050121</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18238,7 +18238,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129633425</v>
+        <v>129633412</v>
       </c>
       <c r="B175" t="n">
         <v>57740</v>
@@ -18273,10 +18273,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>425535</v>
+        <v>425867</v>
       </c>
       <c r="R175" t="n">
-        <v>7049914</v>
+        <v>7050236</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18340,7 +18340,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129633412</v>
+        <v>129633425</v>
       </c>
       <c r="B176" t="n">
         <v>57740</v>
@@ -18375,10 +18375,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>425867</v>
+        <v>425535</v>
       </c>
       <c r="R176" t="n">
-        <v>7050236</v>
+        <v>7049914</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18445,7 +18445,7 @@
         <v>129633390</v>
       </c>
       <c r="B177" t="n">
-        <v>92323</v>
+        <v>92324</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18641,10 +18641,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129633410</v>
+        <v>129633455</v>
       </c>
       <c r="B179" t="n">
-        <v>57740</v>
+        <v>80194</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18652,21 +18652,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18676,10 +18676,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>425574</v>
+        <v>425628</v>
       </c>
       <c r="R179" t="n">
-        <v>7050154</v>
+        <v>7050057</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18712,11 +18712,6 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -18743,7 +18738,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129633430</v>
+        <v>129633407</v>
       </c>
       <c r="B180" t="n">
         <v>57740</v>
@@ -18778,10 +18773,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>425506</v>
+        <v>425770</v>
       </c>
       <c r="R180" t="n">
-        <v>7050201</v>
+        <v>7050089</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18818,7 +18813,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -18845,7 +18840,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129633438</v>
+        <v>129633441</v>
       </c>
       <c r="B181" t="n">
         <v>57740</v>
@@ -18880,10 +18875,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>425374</v>
+        <v>425396</v>
       </c>
       <c r="R181" t="n">
-        <v>7050144</v>
+        <v>7050117</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18920,7 +18915,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -18947,7 +18942,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129633398</v>
+        <v>129633417</v>
       </c>
       <c r="B182" t="n">
         <v>57740</v>
@@ -18982,10 +18977,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>425512</v>
+        <v>425822</v>
       </c>
       <c r="R182" t="n">
-        <v>7049868</v>
+        <v>7050023</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19022,7 +19017,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19049,7 +19044,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129633441</v>
+        <v>129633438</v>
       </c>
       <c r="B183" t="n">
         <v>57740</v>
@@ -19084,10 +19079,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>425396</v>
+        <v>425374</v>
       </c>
       <c r="R183" t="n">
-        <v>7050117</v>
+        <v>7050144</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19124,7 +19119,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19151,7 +19146,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129633407</v>
+        <v>129633430</v>
       </c>
       <c r="B184" t="n">
         <v>57740</v>
@@ -19186,10 +19181,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>425770</v>
+        <v>425506</v>
       </c>
       <c r="R184" t="n">
-        <v>7050089</v>
+        <v>7050201</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19226,7 +19221,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19253,10 +19248,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129633455</v>
+        <v>129633398</v>
       </c>
       <c r="B185" t="n">
-        <v>80193</v>
+        <v>57740</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19264,21 +19259,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19288,10 +19283,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>425628</v>
+        <v>425512</v>
       </c>
       <c r="R185" t="n">
-        <v>7050057</v>
+        <v>7049868</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19324,6 +19319,11 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19452,7 +19452,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129633417</v>
+        <v>129633410</v>
       </c>
       <c r="B187" t="n">
         <v>57740</v>
@@ -19487,10 +19487,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>425822</v>
+        <v>425574</v>
       </c>
       <c r="R187" t="n">
-        <v>7050023</v>
+        <v>7050154</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19527,7 +19527,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19554,10 +19554,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129633433</v>
+        <v>129633485</v>
       </c>
       <c r="B188" t="n">
-        <v>57740</v>
+        <v>89005</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19565,21 +19565,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19589,10 +19589,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>425345</v>
+        <v>425211</v>
       </c>
       <c r="R188" t="n">
-        <v>7050197</v>
+        <v>7049786</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19625,11 +19625,6 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -19656,10 +19651,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129633401</v>
+        <v>129633467</v>
       </c>
       <c r="B189" t="n">
-        <v>57740</v>
+        <v>91602</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19667,21 +19662,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19691,10 +19686,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>425620</v>
+        <v>425215</v>
       </c>
       <c r="R189" t="n">
-        <v>7049978</v>
+        <v>7049827</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19727,11 +19722,6 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -19758,10 +19748,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129633418</v>
+        <v>129633482</v>
       </c>
       <c r="B190" t="n">
-        <v>57740</v>
+        <v>89005</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19769,21 +19759,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19793,10 +19783,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>425785</v>
+        <v>425677</v>
       </c>
       <c r="R190" t="n">
-        <v>7050033</v>
+        <v>7050049</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19829,11 +19819,6 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -19860,10 +19845,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129633432</v>
+        <v>129633474</v>
       </c>
       <c r="B191" t="n">
-        <v>57740</v>
+        <v>91620</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19871,21 +19856,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19895,10 +19880,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>425434</v>
+        <v>425916</v>
       </c>
       <c r="R191" t="n">
-        <v>7050220</v>
+        <v>7050154</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19931,11 +19916,6 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -19962,7 +19942,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129633422</v>
+        <v>129633433</v>
       </c>
       <c r="B192" t="n">
         <v>57740</v>
@@ -19997,10 +19977,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>425222</v>
+        <v>425345</v>
       </c>
       <c r="R192" t="n">
-        <v>7049839</v>
+        <v>7050197</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20064,10 +20044,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129633485</v>
+        <v>129633422</v>
       </c>
       <c r="B193" t="n">
-        <v>89004</v>
+        <v>57740</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20075,21 +20055,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20099,10 +20079,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>425211</v>
+        <v>425222</v>
       </c>
       <c r="R193" t="n">
-        <v>7049786</v>
+        <v>7049839</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20135,6 +20115,11 @@
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20161,10 +20146,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129633482</v>
+        <v>129633401</v>
       </c>
       <c r="B194" t="n">
-        <v>89004</v>
+        <v>57740</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20172,21 +20157,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20196,10 +20181,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>425677</v>
+        <v>425620</v>
       </c>
       <c r="R194" t="n">
-        <v>7050049</v>
+        <v>7049978</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20232,6 +20217,11 @@
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20258,32 +20248,32 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129633391</v>
+        <v>129633432</v>
       </c>
       <c r="B195" t="n">
-        <v>92323</v>
+        <v>57740</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20293,10 +20283,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>426028</v>
+        <v>425434</v>
       </c>
       <c r="R195" t="n">
-        <v>7050169</v>
+        <v>7050220</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20329,6 +20319,11 @@
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20355,10 +20350,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129633474</v>
+        <v>129633418</v>
       </c>
       <c r="B196" t="n">
-        <v>91619</v>
+        <v>57740</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20366,21 +20361,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20390,10 +20385,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>425916</v>
+        <v>425785</v>
       </c>
       <c r="R196" t="n">
-        <v>7050154</v>
+        <v>7050033</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20426,6 +20421,11 @@
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20452,32 +20452,32 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129633467</v>
+        <v>129633391</v>
       </c>
       <c r="B197" t="n">
-        <v>91601</v>
+        <v>92324</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20487,10 +20487,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>425215</v>
+        <v>426028</v>
       </c>
       <c r="R197" t="n">
-        <v>7049827</v>
+        <v>7050169</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20552,7 +20552,7 @@
         <v>129633475</v>
       </c>
       <c r="B198" t="n">
-        <v>91978</v>
+        <v>91979</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>129633470</v>
       </c>
       <c r="B199" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>129633462</v>
       </c>
       <c r="B200" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20840,7 +20840,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129633437</v>
+        <v>129633409</v>
       </c>
       <c r="B201" t="n">
         <v>57740</v>
@@ -20875,10 +20875,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>425347</v>
+        <v>425616</v>
       </c>
       <c r="R201" t="n">
-        <v>7050132</v>
+        <v>7050151</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20915,7 +20915,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -20942,7 +20942,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129633400</v>
+        <v>129633437</v>
       </c>
       <c r="B202" t="n">
         <v>57740</v>
@@ -20977,10 +20977,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>425596</v>
+        <v>425347</v>
       </c>
       <c r="R202" t="n">
-        <v>7049933</v>
+        <v>7050132</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21017,7 +21017,7 @@
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21044,7 +21044,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129633409</v>
+        <v>129633400</v>
       </c>
       <c r="B203" t="n">
         <v>57740</v>
@@ -21079,10 +21079,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>425616</v>
+        <v>425596</v>
       </c>
       <c r="R203" t="n">
-        <v>7050151</v>
+        <v>7049933</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21119,7 +21119,7 @@
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21149,7 +21149,7 @@
         <v>129633469</v>
       </c>
       <c r="B204" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21243,7 +21243,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129633434</v>
+        <v>129633431</v>
       </c>
       <c r="B205" t="n">
         <v>57740</v>
@@ -21278,10 +21278,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>425344</v>
+        <v>425451</v>
       </c>
       <c r="R205" t="n">
-        <v>7050202</v>
+        <v>7050183</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21345,7 +21345,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129633431</v>
+        <v>129633434</v>
       </c>
       <c r="B206" t="n">
         <v>57740</v>
@@ -21380,10 +21380,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>425451</v>
+        <v>425344</v>
       </c>
       <c r="R206" t="n">
-        <v>7050183</v>
+        <v>7050202</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21552,7 +21552,7 @@
         <v>129672509</v>
       </c>
       <c r="B208" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>129672492</v>
       </c>
       <c r="B209" t="n">
-        <v>79246</v>
+        <v>79247</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -21758,10 +21758,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129672503</v>
+        <v>129672510</v>
       </c>
       <c r="B210" t="n">
-        <v>83058</v>
+        <v>80193</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21769,21 +21769,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21793,10 +21793,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>425559</v>
+        <v>425350</v>
       </c>
       <c r="R210" t="n">
-        <v>7049854</v>
+        <v>7049796</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21839,6 +21839,21 @@
       </c>
       <c r="AG210" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO210" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
@@ -21855,10 +21870,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129672510</v>
+        <v>129672503</v>
       </c>
       <c r="B211" t="n">
-        <v>80192</v>
+        <v>83059</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21866,21 +21881,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21890,10 +21905,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>425350</v>
+        <v>425559</v>
       </c>
       <c r="R211" t="n">
-        <v>7049796</v>
+        <v>7049854</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21936,21 +21951,6 @@
       </c>
       <c r="AG211" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ211" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK211" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO211" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
@@ -21967,32 +21967,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129672514</v>
+        <v>129672472</v>
       </c>
       <c r="B212" t="n">
-        <v>83058</v>
+        <v>75192</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6440</v>
+        <v>1776</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22002,10 +22002,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>425292</v>
+        <v>425341</v>
       </c>
       <c r="R212" t="n">
-        <v>7049741</v>
+        <v>7049761</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22048,6 +22048,21 @@
       </c>
       <c r="AG212" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO212" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
@@ -22064,32 +22079,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129672499</v>
+        <v>129672486</v>
       </c>
       <c r="B213" t="n">
-        <v>83058</v>
+        <v>96024</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6440</v>
+        <v>2809</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22099,10 +22114,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>425535</v>
+        <v>425724</v>
       </c>
       <c r="R213" t="n">
-        <v>7049926</v>
+        <v>7050188</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22161,32 +22176,32 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129672486</v>
+        <v>129672514</v>
       </c>
       <c r="B214" t="n">
-        <v>96023</v>
+        <v>83059</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22196,10 +22211,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>425724</v>
+        <v>425292</v>
       </c>
       <c r="R214" t="n">
-        <v>7050188</v>
+        <v>7049741</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22258,32 +22273,32 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129672472</v>
+        <v>129672499</v>
       </c>
       <c r="B215" t="n">
-        <v>75192</v>
+        <v>83059</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1776</v>
+        <v>6440</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -22293,10 +22308,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>425341</v>
+        <v>425535</v>
       </c>
       <c r="R215" t="n">
-        <v>7049761</v>
+        <v>7049926</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22339,21 +22354,6 @@
       </c>
       <c r="AG215" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ215" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK215" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO215" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
@@ -22373,7 +22373,7 @@
         <v>129672458</v>
       </c>
       <c r="B216" t="n">
-        <v>97138</v>
+        <v>97139</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22470,7 +22470,7 @@
         <v>129672494</v>
       </c>
       <c r="B217" t="n">
-        <v>79246</v>
+        <v>79247</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -22661,32 +22661,32 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129672468</v>
+        <v>129672502</v>
       </c>
       <c r="B219" t="n">
-        <v>79343</v>
+        <v>79169</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6459</v>
+        <v>283</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -22696,10 +22696,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>425444</v>
+        <v>425572</v>
       </c>
       <c r="R219" t="n">
-        <v>7049814</v>
+        <v>7049859</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22758,10 +22758,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129672502</v>
+        <v>129672487</v>
       </c>
       <c r="B220" t="n">
-        <v>79168</v>
+        <v>97044</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22769,21 +22769,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>283</v>
+        <v>53</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22793,10 +22793,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>425572</v>
+        <v>425724</v>
       </c>
       <c r="R220" t="n">
-        <v>7049859</v>
+        <v>7050188</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22855,32 +22855,32 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129672487</v>
+        <v>129672468</v>
       </c>
       <c r="B221" t="n">
-        <v>97043</v>
+        <v>79344</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>53</v>
+        <v>6459</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -22890,10 +22890,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>425724</v>
+        <v>425444</v>
       </c>
       <c r="R221" t="n">
-        <v>7050188</v>
+        <v>7049814</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22955,7 +22955,7 @@
         <v>129672452</v>
       </c>
       <c r="B222" t="n">
-        <v>96035</v>
+        <v>96036</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>129672473</v>
       </c>
       <c r="B223" t="n">
-        <v>83063</v>
+        <v>83064</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23161,10 +23161,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129672467</v>
+        <v>129672483</v>
       </c>
       <c r="B224" t="n">
-        <v>79343</v>
+        <v>96024</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23172,21 +23172,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6459</v>
+        <v>2809</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -23196,10 +23196,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>425491</v>
+        <v>425601</v>
       </c>
       <c r="R224" t="n">
-        <v>7049816</v>
+        <v>7050195</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23258,32 +23258,32 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129672505</v>
+        <v>129672467</v>
       </c>
       <c r="B225" t="n">
-        <v>78100</v>
+        <v>79344</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>228579</v>
+        <v>6459</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23293,10 +23293,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>425524</v>
+        <v>425491</v>
       </c>
       <c r="R225" t="n">
-        <v>7049845</v>
+        <v>7049816</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23339,11 +23339,6 @@
       </c>
       <c r="AG225" t="b">
         <v>0</v>
-      </c>
-      <c r="AO225" t="inlineStr">
-        <is>
-          <t>barken på gammal gran</t>
-        </is>
       </c>
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
@@ -23360,32 +23355,32 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129672484</v>
+        <v>129672480</v>
       </c>
       <c r="B226" t="n">
-        <v>78111</v>
+        <v>75071</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>314</v>
+        <v>6428</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23395,10 +23390,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>425661</v>
+        <v>425403</v>
       </c>
       <c r="R226" t="n">
-        <v>7050268</v>
+        <v>7049803</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23441,6 +23436,11 @@
       </c>
       <c r="AG226" t="b">
         <v>0</v>
+      </c>
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t>Grankvist</t>
+        </is>
       </c>
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
@@ -23457,10 +23457,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129672483</v>
+        <v>129672449</v>
       </c>
       <c r="B227" t="n">
-        <v>96023</v>
+        <v>75071</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23468,21 +23468,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>2809</v>
+        <v>6428</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23492,10 +23492,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>425601</v>
+        <v>425715</v>
       </c>
       <c r="R227" t="n">
-        <v>7050195</v>
+        <v>7050177</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23554,32 +23554,32 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129672480</v>
+        <v>129672505</v>
       </c>
       <c r="B228" t="n">
-        <v>75071</v>
+        <v>78100</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6428</v>
+        <v>228579</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23589,10 +23589,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>425403</v>
+        <v>425524</v>
       </c>
       <c r="R228" t="n">
-        <v>7049803</v>
+        <v>7049845</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23638,7 +23638,7 @@
       </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>Grankvist</t>
+          <t>barken på gammal gran</t>
         </is>
       </c>
       <c r="AT228" t="inlineStr"/>
@@ -23656,32 +23656,32 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129672449</v>
+        <v>129672484</v>
       </c>
       <c r="B229" t="n">
-        <v>75071</v>
+        <v>78111</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6428</v>
+        <v>314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23691,10 +23691,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>425715</v>
+        <v>425661</v>
       </c>
       <c r="R229" t="n">
-        <v>7050177</v>
+        <v>7050268</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23756,7 +23756,7 @@
         <v>129672513</v>
       </c>
       <c r="B230" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>129672471</v>
       </c>
       <c r="B231" t="n">
-        <v>79168</v>
+        <v>79169</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -23947,32 +23947,32 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129672454</v>
+        <v>129672501</v>
       </c>
       <c r="B232" t="n">
-        <v>79246</v>
+        <v>75071</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>1249</v>
+        <v>6428</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -23982,10 +23982,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>425708</v>
+        <v>425575</v>
       </c>
       <c r="R232" t="n">
-        <v>7050134</v>
+        <v>7049870</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24044,32 +24044,32 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129672475</v>
+        <v>129672454</v>
       </c>
       <c r="B233" t="n">
-        <v>82924</v>
+        <v>79247</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>1312</v>
+        <v>1249</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24079,10 +24079,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>425309</v>
+        <v>425708</v>
       </c>
       <c r="R233" t="n">
-        <v>7049722</v>
+        <v>7050134</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24141,10 +24141,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>129672508</v>
+        <v>129672475</v>
       </c>
       <c r="B234" t="n">
-        <v>79558</v>
+        <v>82925</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -24152,21 +24152,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>1797</v>
+        <v>1312</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -24176,10 +24176,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>425439</v>
+        <v>425309</v>
       </c>
       <c r="R234" t="n">
-        <v>7049810</v>
+        <v>7049722</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24238,32 +24238,32 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>129672501</v>
+        <v>129672508</v>
       </c>
       <c r="B235" t="n">
-        <v>75071</v>
+        <v>79559</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6428</v>
+        <v>1797</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -24273,10 +24273,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>425575</v>
+        <v>425439</v>
       </c>
       <c r="R235" t="n">
-        <v>7049870</v>
+        <v>7049810</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24335,32 +24335,32 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>129672478</v>
+        <v>129672455</v>
       </c>
       <c r="B236" t="n">
-        <v>96023</v>
+        <v>82925</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>2809</v>
+        <v>1312</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -24370,10 +24370,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>425257</v>
+        <v>425732</v>
       </c>
       <c r="R236" t="n">
-        <v>7049744</v>
+        <v>7050091</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24432,32 +24432,32 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>129672455</v>
+        <v>129672478</v>
       </c>
       <c r="B237" t="n">
-        <v>82924</v>
+        <v>96024</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>1312</v>
+        <v>2809</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -24467,10 +24467,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>425732</v>
+        <v>425257</v>
       </c>
       <c r="R237" t="n">
-        <v>7050091</v>
+        <v>7049744</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24532,7 +24532,7 @@
         <v>129672446</v>
       </c>
       <c r="B238" t="n">
-        <v>79559</v>
+        <v>79560</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>129672460</v>
       </c>
       <c r="B239" t="n">
-        <v>96023</v>
+        <v>96024</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>129672495</v>
       </c>
       <c r="B240" t="n">
-        <v>79558</v>
+        <v>79559</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>129672488</v>
       </c>
       <c r="B241" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24912,10 +24912,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129672485</v>
+        <v>129672512</v>
       </c>
       <c r="B242" t="n">
-        <v>83058</v>
+        <v>83064</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24923,21 +24923,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -24947,10 +24947,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>425724</v>
+        <v>425315</v>
       </c>
       <c r="R242" t="n">
-        <v>7050188</v>
+        <v>7049749</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25009,10 +25009,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129672512</v>
+        <v>129672485</v>
       </c>
       <c r="B243" t="n">
-        <v>83063</v>
+        <v>83059</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25020,21 +25020,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25044,10 +25044,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>425315</v>
+        <v>425724</v>
       </c>
       <c r="R243" t="n">
-        <v>7049749</v>
+        <v>7050188</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25109,7 +25109,7 @@
         <v>129672464</v>
       </c>
       <c r="B244" t="n">
-        <v>95647</v>
+        <v>95648</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>129672469</v>
       </c>
       <c r="B246" t="n">
-        <v>79558</v>
+        <v>79559</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>129672489</v>
       </c>
       <c r="B247" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25494,32 +25494,32 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>129672453</v>
+        <v>129672490</v>
       </c>
       <c r="B248" t="n">
-        <v>79558</v>
+        <v>92324</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>1797</v>
+        <v>3298</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -25529,10 +25529,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>425710</v>
+        <v>425697</v>
       </c>
       <c r="R248" t="n">
-        <v>7050150</v>
+        <v>7050149</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25591,32 +25591,32 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>129672490</v>
+        <v>129672453</v>
       </c>
       <c r="B249" t="n">
-        <v>92323</v>
+        <v>79559</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>3298</v>
+        <v>1797</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -25626,10 +25626,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>425697</v>
+        <v>425710</v>
       </c>
       <c r="R249" t="n">
-        <v>7050149</v>
+        <v>7050150</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25688,32 +25688,32 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>129672481</v>
+        <v>129672447</v>
       </c>
       <c r="B250" t="n">
-        <v>97043</v>
+        <v>75192</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>53</v>
+        <v>1776</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -25723,10 +25723,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>425594</v>
+        <v>425702</v>
       </c>
       <c r="R250" t="n">
-        <v>7050152</v>
+        <v>7050232</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25767,6 +25767,7 @@
       <c r="AE250" t="b">
         <v>0</v>
       </c>
+      <c r="AF250" t="inlineStr"/>
       <c r="AG250" t="b">
         <v>0</v>
       </c>
@@ -25785,32 +25786,32 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>129672447</v>
+        <v>129672481</v>
       </c>
       <c r="B251" t="n">
-        <v>75192</v>
+        <v>97044</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1776</v>
+        <v>53</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -25820,10 +25821,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>425702</v>
+        <v>425594</v>
       </c>
       <c r="R251" t="n">
-        <v>7050232</v>
+        <v>7050152</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25864,7 +25865,6 @@
       <c r="AE251" t="b">
         <v>0</v>
       </c>
-      <c r="AF251" t="inlineStr"/>
       <c r="AG251" t="b">
         <v>0</v>
       </c>
@@ -25883,32 +25883,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>129672507</v>
+        <v>129672451</v>
       </c>
       <c r="B252" t="n">
-        <v>79168</v>
+        <v>92561</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>283</v>
+        <v>4769</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25918,10 +25918,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>425450</v>
+        <v>425710</v>
       </c>
       <c r="R252" t="n">
-        <v>7049825</v>
+        <v>7050150</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25983,7 +25983,7 @@
         <v>129672506</v>
       </c>
       <c r="B253" t="n">
-        <v>79168</v>
+        <v>79169</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -26077,32 +26077,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>129672451</v>
+        <v>129672507</v>
       </c>
       <c r="B254" t="n">
-        <v>92560</v>
+        <v>79169</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>4769</v>
+        <v>283</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26112,10 +26112,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>425710</v>
+        <v>425450</v>
       </c>
       <c r="R254" t="n">
-        <v>7050150</v>
+        <v>7049825</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26271,32 +26271,32 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>129672491</v>
+        <v>129672466</v>
       </c>
       <c r="B256" t="n">
-        <v>79343</v>
+        <v>79247</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6459</v>
+        <v>1249</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26306,10 +26306,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>425740</v>
+        <v>425505</v>
       </c>
       <c r="R256" t="n">
-        <v>7050084</v>
+        <v>7049842</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26368,32 +26368,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>129672466</v>
+        <v>129672491</v>
       </c>
       <c r="B257" t="n">
-        <v>79246</v>
+        <v>79344</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>1249</v>
+        <v>6459</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -26403,10 +26403,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>425505</v>
+        <v>425740</v>
       </c>
       <c r="R257" t="n">
-        <v>7049842</v>
+        <v>7050084</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>

--- a/artfynd/A 47880-2025 artfynd.xlsx
+++ b/artfynd/A 47880-2025 artfynd.xlsx
@@ -25883,32 +25883,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>129672451</v>
+        <v>129672506</v>
       </c>
       <c r="B252" t="n">
-        <v>92561</v>
+        <v>79169</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>4769</v>
+        <v>283</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25918,10 +25918,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>425710</v>
+        <v>425480</v>
       </c>
       <c r="R252" t="n">
-        <v>7050150</v>
+        <v>7049813</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25980,7 +25980,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>129672506</v>
+        <v>129672507</v>
       </c>
       <c r="B253" t="n">
         <v>79169</v>
@@ -26015,10 +26015,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>425480</v>
+        <v>425450</v>
       </c>
       <c r="R253" t="n">
-        <v>7049813</v>
+        <v>7049825</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26077,32 +26077,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>129672507</v>
+        <v>129672451</v>
       </c>
       <c r="B254" t="n">
-        <v>79169</v>
+        <v>92561</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>283</v>
+        <v>4769</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26112,10 +26112,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>425450</v>
+        <v>425710</v>
       </c>
       <c r="R254" t="n">
-        <v>7049825</v>
+        <v>7050150</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>

--- a/artfynd/A 47880-2025 artfynd.xlsx
+++ b/artfynd/A 47880-2025 artfynd.xlsx
@@ -22952,32 +22952,32 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129672452</v>
+        <v>129672473</v>
       </c>
       <c r="B222" t="n">
-        <v>96036</v>
+        <v>83064</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>2813</v>
+        <v>1467</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -22987,10 +22987,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>425710</v>
+        <v>425341</v>
       </c>
       <c r="R222" t="n">
-        <v>7050150</v>
+        <v>7049761</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23033,6 +23033,21 @@
       </c>
       <c r="AG222" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ222" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK222" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO222" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
@@ -23049,32 +23064,32 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129672473</v>
+        <v>129672452</v>
       </c>
       <c r="B223" t="n">
-        <v>83064</v>
+        <v>96036</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>1467</v>
+        <v>2813</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -23084,10 +23099,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>425341</v>
+        <v>425710</v>
       </c>
       <c r="R223" t="n">
-        <v>7049761</v>
+        <v>7050150</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23130,21 +23145,6 @@
       </c>
       <c r="AG223" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ223" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK223" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO223" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
@@ -23355,32 +23355,32 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129672480</v>
+        <v>129672484</v>
       </c>
       <c r="B226" t="n">
-        <v>75071</v>
+        <v>78111</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6428</v>
+        <v>314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23390,10 +23390,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>425403</v>
+        <v>425661</v>
       </c>
       <c r="R226" t="n">
-        <v>7049803</v>
+        <v>7050268</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23436,11 +23436,6 @@
       </c>
       <c r="AG226" t="b">
         <v>0</v>
-      </c>
-      <c r="AO226" t="inlineStr">
-        <is>
-          <t>Grankvist</t>
-        </is>
       </c>
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
@@ -23457,7 +23452,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129672449</v>
+        <v>129672480</v>
       </c>
       <c r="B227" t="n">
         <v>75071</v>
@@ -23492,10 +23487,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>425715</v>
+        <v>425403</v>
       </c>
       <c r="R227" t="n">
-        <v>7050177</v>
+        <v>7049803</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23538,6 +23533,11 @@
       </c>
       <c r="AG227" t="b">
         <v>0</v>
+      </c>
+      <c r="AO227" t="inlineStr">
+        <is>
+          <t>Grankvist</t>
+        </is>
       </c>
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
@@ -23554,32 +23554,32 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129672505</v>
+        <v>129672449</v>
       </c>
       <c r="B228" t="n">
-        <v>78100</v>
+        <v>75071</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>228579</v>
+        <v>6428</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23589,10 +23589,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>425524</v>
+        <v>425715</v>
       </c>
       <c r="R228" t="n">
-        <v>7049845</v>
+        <v>7050177</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23635,11 +23635,6 @@
       </c>
       <c r="AG228" t="b">
         <v>0</v>
-      </c>
-      <c r="AO228" t="inlineStr">
-        <is>
-          <t>barken på gammal gran</t>
-        </is>
       </c>
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
@@ -23656,10 +23651,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129672484</v>
+        <v>129672505</v>
       </c>
       <c r="B229" t="n">
-        <v>78111</v>
+        <v>78100</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23667,21 +23662,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>314</v>
+        <v>228579</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23691,10 +23686,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>425661</v>
+        <v>425524</v>
       </c>
       <c r="R229" t="n">
-        <v>7050268</v>
+        <v>7049845</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23737,6 +23732,11 @@
       </c>
       <c r="AG229" t="b">
         <v>0</v>
+      </c>
+      <c r="AO229" t="inlineStr">
+        <is>
+          <t>barken på gammal gran</t>
+        </is>
       </c>
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">

--- a/artfynd/A 47880-2025 artfynd.xlsx
+++ b/artfynd/A 47880-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY270"/>
+  <dimension ref="A1:AZ270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672481</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672487</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627373</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627374</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629007</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629008</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672471</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1570,6 +1615,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672502</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1667,6 +1717,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672506</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1764,6 +1819,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672507</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1866,6 +1926,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629024</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1968,6 +2033,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629026</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2070,6 +2140,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629027</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2172,6 +2247,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629030</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2274,6 +2354,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628986</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2376,6 +2461,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628987</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2478,6 +2568,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629028</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2580,6 +2675,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628949</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2677,6 +2777,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672484</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2779,6 +2884,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627371</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2876,6 +2986,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633482</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2973,6 +3088,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633483</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3070,6 +3190,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633484</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3167,6 +3292,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633485</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3269,6 +3399,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627375</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3371,6 +3506,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627376</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3473,6 +3613,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629009</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3575,6 +3720,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629012</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3677,6 +3827,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629014</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3779,6 +3934,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629015</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3876,6 +4036,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633458</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3973,6 +4138,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633459</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4070,6 +4240,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633460</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4167,6 +4342,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633461</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4264,6 +4444,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633462</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4361,6 +4546,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633463</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4458,6 +4648,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633465</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4555,6 +4750,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633466</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4652,6 +4852,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633467</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4749,6 +4954,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633468</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4846,6 +5056,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633469</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4943,6 +5158,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633470</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5040,6 +5260,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633471</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5137,6 +5362,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633472</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5234,6 +5464,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633473</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5336,6 +5571,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628957</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5438,6 +5678,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628958</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5540,6 +5785,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629019</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5637,6 +5887,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633474</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5746,6 +6001,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627354</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5855,6 +6115,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627355</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5964,6 +6229,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627356</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6078,6 +6348,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627357</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6192,6 +6467,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627358</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6306,6 +6586,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627359</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6420,6 +6705,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627360</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6534,6 +6824,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627361</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6648,6 +6943,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627362</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6762,6 +7062,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627363</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6876,6 +7181,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627364</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6978,6 +7288,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628981</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7080,6 +7395,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628982</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7182,6 +7502,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628983</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7279,6 +7604,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633456</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7376,6 +7706,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633457</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7473,6 +7808,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672454</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7570,6 +7910,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672466</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7667,6 +8012,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672492</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7764,6 +8114,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672494</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7861,6 +8216,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672496</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7963,6 +8323,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627380</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8065,6 +8430,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627381</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8162,6 +8532,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672455</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8259,6 +8634,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672475</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8356,6 +8736,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672497</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8458,6 +8843,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628973</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8560,6 +8950,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628974</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8672,6 +9067,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672473</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8769,6 +9169,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672512</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8871,6 +9276,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627392</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8973,6 +9383,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629034</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9075,6 +9490,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629035</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9172,6 +9592,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672444</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9270,6 +9695,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672447</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9382,6 +9812,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672472</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9484,6 +9919,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627367</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9586,6 +10026,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627369</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9688,6 +10133,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628991</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9790,6 +10240,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628993</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9892,6 +10347,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628994</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9994,6 +10454,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628995</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10096,6 +10561,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628996</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10198,6 +10668,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628997</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10300,6 +10775,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628998</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10402,6 +10882,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629011</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10499,6 +10984,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672453</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10596,6 +11086,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672462</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10693,6 +11188,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672469</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10790,6 +11290,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672495</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10887,6 +11392,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672508</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10984,6 +11494,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672458</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11081,6 +11596,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633475</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11193,6 +11713,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129611565</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11295,6 +11820,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627351</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11397,6 +11927,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627353</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11499,6 +12034,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628966</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11596,6 +12136,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633455</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11708,6 +12253,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672509</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11805,6 +12355,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672464</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11912,6 +12467,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627372</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12014,6 +12574,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629004</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12111,6 +12676,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672460</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12208,6 +12778,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672478</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12305,6 +12880,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672483</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12402,6 +12982,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672486</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12504,6 +13089,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628970</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12601,6 +13191,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672452</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12703,6 +13298,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627338</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12800,6 +13400,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627339</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12897,6 +13502,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627341</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13000,6 +13610,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627342</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13102,6 +13717,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628959</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13199,6 +13819,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633383</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13296,6 +13921,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633384</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13393,6 +14023,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633385</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13490,6 +14125,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633386</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13587,6 +14227,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633387</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13684,6 +14329,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633388</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13781,6 +14431,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633389</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13878,6 +14533,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633390</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13975,6 +14635,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633391</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14072,6 +14737,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633392</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14169,6 +14839,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633393</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14266,6 +14941,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633394</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14363,6 +15043,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633395</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14460,6 +15145,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633396</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14557,6 +15247,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672490</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14666,6 +15361,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627347</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14768,6 +15468,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628963</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14865,6 +15570,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672451</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14962,6 +15672,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627337</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15059,6 +15774,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672488</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15175,6 +15895,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129611822</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15277,6 +16002,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627378</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15379,6 +16109,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627379</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15481,6 +16216,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628971</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15583,6 +16323,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628975</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15685,6 +16430,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628978</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15787,6 +16537,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628988</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15889,6 +16644,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628992</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16003,6 +16763,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629020</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16105,6 +16870,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629021</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16207,6 +16977,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629022</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16304,6 +17079,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672489</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16401,6 +17181,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672513</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16503,6 +17288,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628976</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16605,6 +17395,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628977</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16702,6 +17497,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672449</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16804,6 +17604,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672480</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16901,6 +17706,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672493</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16998,6 +17808,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672501</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17100,6 +17915,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629025</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17202,6 +18022,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629029</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17304,6 +18129,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627336</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17406,6 +18236,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628953</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17508,6 +18343,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628954</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17611,6 +18451,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628956</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17713,6 +18558,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628979</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17815,6 +18665,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628985</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17917,6 +18772,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628989</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18014,6 +18874,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672485</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18111,6 +18976,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672498</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18208,6 +19078,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672499</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18305,6 +19180,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672503</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18402,6 +19282,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672514</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18514,6 +19399,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672510</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18616,6 +19506,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629032</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18713,6 +19608,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672467</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18810,6 +19710,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672468</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18907,6 +19812,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672491</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19014,6 +19924,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129611522</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19121,6 +20036,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129611596</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19218,6 +20138,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627365</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19315,6 +20240,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627366</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19417,6 +20347,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628984</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -19519,6 +20454,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627349</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19621,6 +20561,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628964</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19723,6 +20668,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628965</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19825,6 +20775,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629010</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19927,6 +20882,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633453</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -20037,6 +20997,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627343</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -20139,6 +21104,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628961</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -20241,6 +21211,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633397</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20343,6 +21318,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633398</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20445,6 +21425,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633399</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20547,6 +21532,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633400</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -20649,6 +21639,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633401</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20751,6 +21746,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633402</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20853,6 +21853,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633403</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -20955,6 +21960,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633404</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -21057,6 +22067,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633405</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -21159,6 +22174,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633407</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -21261,6 +22281,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633408</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -21363,6 +22388,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633409</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -21465,6 +22495,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633410</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -21567,6 +22602,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633411</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -21669,6 +22709,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633412</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21771,6 +22816,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633413</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21873,6 +22923,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633414</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -21975,6 +23030,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633415</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -22077,6 +23137,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633416</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -22179,6 +23244,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633417</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -22281,6 +23351,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633418</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -22383,6 +23458,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633419</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -22485,6 +23565,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633420</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -22587,6 +23672,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633421</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -22689,6 +23779,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633422</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -22791,6 +23886,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633423</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -22893,6 +23993,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633424</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -22995,6 +24100,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633425</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -23097,6 +24207,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633426</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -23199,6 +24314,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633427</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -23301,6 +24421,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633428</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -23403,6 +24528,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633429</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -23505,6 +24635,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633430</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -23607,6 +24742,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633431</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -23709,6 +24849,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633432</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -23811,6 +24956,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633433</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -23913,6 +25063,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633434</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -24015,6 +25170,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633435</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -24117,6 +25277,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633436</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -24219,6 +25384,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633437</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -24321,6 +25491,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633438</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -24423,6 +25598,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633439</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -24525,6 +25705,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633440</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -24627,6 +25812,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633441</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -24729,6 +25919,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633442</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -24831,6 +26026,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633443</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -24933,6 +26133,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633444</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -25035,6 +26240,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633445</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -25137,6 +26347,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633446</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -25239,6 +26454,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633447</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -25341,6 +26561,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633448</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -25443,6 +26668,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633449</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -25545,6 +26775,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633450</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -25647,6 +26882,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633451</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -25749,6 +26989,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129633452</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -25861,6 +27106,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129611584</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -25970,6 +27220,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627346</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -26075,6 +27330,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627345</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -26172,6 +27432,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672511</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -26274,6 +27539,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628948</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -26376,6 +27646,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628999</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -26497,6 +27772,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629031</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -26609,6 +27889,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672474</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -26711,6 +27996,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627370</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -26813,6 +28103,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628952</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -26915,6 +28210,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628955</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -27017,6 +28317,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628980</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -27119,6 +28424,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628990</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -27221,6 +28531,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629003</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -27323,6 +28638,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129629033</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -27425,6 +28745,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672505</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -27530,6 +28855,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129628951</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -27622,6 +28952,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672445</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -27729,6 +29064,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672456</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -27821,6 +29161,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672446</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -27929,8 +29274,284 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129672470</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>